--- a/backend/data/With_PGs_infos_completed.xlsx
+++ b/backend/data/With_PGs_infos_completed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AFC\church-planting-map\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759CBB78-2618-4EF8-BA62-F87FFB5F21BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CB753E-EBE9-4FE5-AE03-7313A454F0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="485">
   <si>
     <t>Date</t>
   </si>
@@ -1474,6 +1474,12 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>JP ROP3</t>
+  </si>
+  <si>
+    <t>JP PG ID</t>
   </si>
 </sst>
 </file>
@@ -1483,7 +1489,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1872,25 +1878,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:AL81"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.75"/>
   <cols>
-    <col min="11" max="11" width="13.81640625" customWidth="1"/>
-    <col min="14" max="14" width="26" customWidth="1"/>
-    <col min="15" max="15" width="22" customWidth="1"/>
-    <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" customWidth="1"/>
+    <col min="16" max="16" width="26" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
     <col min="18" max="18" width="16" customWidth="1"/>
-    <col min="19" max="19" width="24" customWidth="1"/>
-    <col min="20" max="20" width="30" customWidth="1"/>
-    <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="23" max="23" width="26" customWidth="1"/>
-    <col min="24" max="26" width="10" customWidth="1"/>
-    <col min="27" max="27" width="60" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="24" customWidth="1"/>
+    <col min="22" max="22" width="30" customWidth="1"/>
+    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
+    <col min="25" max="25" width="26" customWidth="1"/>
+    <col min="26" max="28" width="10" customWidth="1"/>
+    <col min="29" max="29" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:38">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1919,61 +1925,65 @@
         <v>8</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
       <c r="AD1" s="6"/>
       <c r="AE1" s="6"/>
       <c r="AF1" s="6"/>
@@ -1981,8 +1991,10 @@
       <c r="AH1" s="6"/>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="6"/>
+      <c r="AK1" s="6"/>
+      <c r="AL1" s="6"/>
     </row>
-    <row r="2" spans="1:36" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:38" ht="73.75">
       <c r="A2" s="1">
         <v>46203</v>
       </c>
@@ -2010,54 +2022,56 @@
       <c r="I2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3">
+        <v>104831</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="8" t="s">
+      <c r="O2" s="3"/>
+      <c r="P2" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="Q2" s="8" t="s">
         <v>33</v>
       </c>
       <c r="R2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="T2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="U2" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="T2" s="8" t="s">
+      <c r="V2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="W2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V2" s="8" t="s">
+      <c r="X2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="W2" s="8" t="s">
+      <c r="Y2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8" t="s">
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="8"/>
+      <c r="AB2" s="8"/>
+      <c r="AC2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
@@ -2065,8 +2079,10 @@
       <c r="AH2" s="4"/>
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
+      <c r="AK2" s="4"/>
+      <c r="AL2" s="4"/>
     </row>
-    <row r="3" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:38" ht="44.25">
       <c r="A3" s="1">
         <v>46203</v>
       </c>
@@ -2094,60 +2110,62 @@
       <c r="I3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="3"/>
+      <c r="K3" s="3">
+        <v>100198</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="P3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="Q3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="R3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="S3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="T3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="U3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="V3" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="W3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V3" s="8" t="s">
+      <c r="X3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W3" s="8" t="s">
+      <c r="Y3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="8">
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="8">
         <v>6.8263122000000003</v>
       </c>
-      <c r="Z3" s="8">
+      <c r="AB3" s="8">
         <v>10.1854561</v>
       </c>
-      <c r="AA3" s="8" t="s">
+      <c r="AC3" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
@@ -2155,8 +2173,10 @@
       <c r="AH3" s="4"/>
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
+      <c r="AK3" s="4"/>
+      <c r="AL3" s="4"/>
     </row>
-    <row r="4" spans="1:36" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:38" ht="73.75">
       <c r="A4" s="1">
         <v>46203</v>
       </c>
@@ -2184,60 +2204,64 @@
       <c r="I4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="3">
+        <v>15655</v>
+      </c>
+      <c r="K4" s="3">
+        <v>110311</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="S4" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="T4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S4" s="8" t="s">
+      <c r="U4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="T4" s="8" t="s">
+      <c r="V4" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="U4" s="8" t="s">
+      <c r="W4" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V4" s="8" t="s">
+      <c r="X4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="W4" s="8" t="s">
+      <c r="Y4" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="8">
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="8">
         <v>12.0831175</v>
       </c>
-      <c r="Z4" s="8">
+      <c r="AB4" s="8">
         <v>15.019126200000001</v>
       </c>
-      <c r="AA4" s="8" t="s">
+      <c r="AC4" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
@@ -2245,8 +2269,10 @@
       <c r="AH4" s="4"/>
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
+      <c r="AK4" s="4"/>
+      <c r="AL4" s="4"/>
     </row>
-    <row r="5" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:38" ht="29.5">
       <c r="A5" s="1">
         <v>46203</v>
       </c>
@@ -2274,60 +2300,64 @@
       <c r="I5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="3">
+        <v>11781</v>
+      </c>
+      <c r="K5" s="3">
+        <v>103088</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="P5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="Q5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="R5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="S5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="T5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="8" t="s">
+      <c r="U5" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="T5" s="8" t="s">
+      <c r="V5" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="8" t="s">
+      <c r="W5" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V5" s="8" t="s">
+      <c r="X5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W5" s="8" t="s">
+      <c r="Y5" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="8">
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="8">
         <v>6.0045045000000004</v>
       </c>
-      <c r="Z5" s="8">
+      <c r="AB5" s="8">
         <v>10.214104000000001</v>
       </c>
-      <c r="AA5" s="8" t="s">
+      <c r="AC5" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
@@ -2335,8 +2365,10 @@
       <c r="AH5" s="4"/>
       <c r="AI5" s="4"/>
       <c r="AJ5" s="4"/>
+      <c r="AK5" s="4"/>
+      <c r="AL5" s="4"/>
     </row>
-    <row r="6" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:38" ht="44.25">
       <c r="A6" s="1">
         <v>46203</v>
       </c>
@@ -2364,58 +2396,62 @@
       <c r="I6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="3">
+        <v>13291</v>
+      </c>
+      <c r="K6" s="3">
+        <v>107171</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M6" s="3"/>
-      <c r="N6" s="8" t="s">
+      <c r="O6" s="3"/>
+      <c r="P6" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="Q6" s="8" t="s">
         <v>33</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S6" s="8" t="s">
         <v>33</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U6" s="8" t="s">
         <v>33</v>
       </c>
       <c r="V6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="W6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="X6" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W6" s="8" t="s">
+      <c r="Y6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="8" t="s">
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="Z6" s="8" t="s">
+      <c r="AB6" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="AA6" s="8" t="s">
+      <c r="AC6" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
@@ -2423,8 +2459,10 @@
       <c r="AH6" s="4"/>
       <c r="AI6" s="4"/>
       <c r="AJ6" s="4"/>
+      <c r="AK6" s="4"/>
+      <c r="AL6" s="4"/>
     </row>
-    <row r="7" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:38" ht="44.25">
       <c r="A7" s="1">
         <v>46203</v>
       </c>
@@ -2452,60 +2490,64 @@
       <c r="I7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="3">
+        <v>10632</v>
+      </c>
+      <c r="K7" s="3">
+        <v>100941</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="N7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="O7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="P7" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="Q7" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="R7" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="S7" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R7" s="8" t="s">
+      <c r="T7" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S7" s="8" t="s">
+      <c r="U7" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="T7" s="8" t="s">
+      <c r="V7" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="U7" s="8" t="s">
+      <c r="W7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V7" s="8" t="s">
+      <c r="X7" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W7" s="8" t="s">
+      <c r="Y7" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="8">
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="8">
         <v>10.25075</v>
       </c>
-      <c r="Z7" s="8">
+      <c r="AB7" s="8">
         <v>13.51033</v>
       </c>
-      <c r="AA7" s="8" t="s">
+      <c r="AC7" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
@@ -2513,8 +2555,10 @@
       <c r="AH7" s="4"/>
       <c r="AI7" s="4"/>
       <c r="AJ7" s="4"/>
+      <c r="AK7" s="4"/>
+      <c r="AL7" s="4"/>
     </row>
-    <row r="8" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:38" ht="44.25">
       <c r="A8" s="1">
         <v>46203</v>
       </c>
@@ -2542,60 +2586,64 @@
       <c r="I8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="3">
+        <v>10632</v>
+      </c>
+      <c r="K8" s="3">
+        <v>100941</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="P8" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="O8" s="8" t="s">
+      <c r="Q8" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="R8" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="8" t="s">
+      <c r="S8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R8" s="8" t="s">
+      <c r="T8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S8" s="8" t="s">
+      <c r="U8" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="T8" s="8" t="s">
+      <c r="V8" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="U8" s="8" t="s">
+      <c r="W8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V8" s="8" t="s">
+      <c r="X8" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="W8" s="8" t="s">
+      <c r="Y8" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="8">
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="8">
         <v>10.25075</v>
       </c>
-      <c r="Z8" s="8">
+      <c r="AB8" s="8">
         <v>13.51033</v>
       </c>
-      <c r="AA8" s="8" t="s">
+      <c r="AC8" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
@@ -2603,8 +2651,10 @@
       <c r="AH8" s="4"/>
       <c r="AI8" s="4"/>
       <c r="AJ8" s="4"/>
+      <c r="AK8" s="4"/>
+      <c r="AL8" s="4"/>
     </row>
-    <row r="9" spans="1:36" ht="59" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:38" ht="59">
       <c r="A9" s="1">
         <v>46203</v>
       </c>
@@ -2632,60 +2682,64 @@
       <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="3">
+        <v>10632</v>
+      </c>
+      <c r="K9" s="3">
+        <v>100941</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="N9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="O9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="P9" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="Q9" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="R9" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="S9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R9" s="8" t="s">
+      <c r="T9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S9" s="8" t="s">
+      <c r="U9" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="T9" s="8" t="s">
+      <c r="V9" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="U9" s="8" t="s">
+      <c r="W9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V9" s="8" t="s">
+      <c r="X9" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="W9" s="8" t="s">
+      <c r="Y9" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="8">
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="8">
         <v>10.25075</v>
       </c>
-      <c r="Z9" s="8">
+      <c r="AB9" s="8">
         <v>13.51033</v>
       </c>
-      <c r="AA9" s="8" t="s">
+      <c r="AC9" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="AB9" s="4"/>
-      <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
@@ -2693,8 +2747,10 @@
       <c r="AH9" s="4"/>
       <c r="AI9" s="4"/>
       <c r="AJ9" s="4"/>
+      <c r="AK9" s="4"/>
+      <c r="AL9" s="4"/>
     </row>
-    <row r="10" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:38" ht="44.25">
       <c r="A10" s="1">
         <v>46203</v>
       </c>
@@ -2722,60 +2778,60 @@
       <c r="I10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="3" t="s">
+      <c r="M10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="O10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="N10" s="8" t="s">
+      <c r="P10" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="O10" s="8" t="s">
+      <c r="Q10" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="R10" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="Q10" s="8" t="s">
+      <c r="S10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R10" s="8" t="s">
+      <c r="T10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="8" t="s">
+      <c r="U10" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="T10" s="8" t="s">
+      <c r="V10" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="U10" s="8" t="s">
+      <c r="W10" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V10" s="8" t="s">
+      <c r="X10" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W10" s="8" t="s">
+      <c r="Y10" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="8">
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="8">
         <v>6.0338079999999996</v>
       </c>
-      <c r="Z10" s="8">
+      <c r="AB10" s="8">
         <v>10.579231</v>
       </c>
-      <c r="AA10" s="8" t="s">
+      <c r="AC10" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
@@ -2783,8 +2839,10 @@
       <c r="AH10" s="4"/>
       <c r="AI10" s="4"/>
       <c r="AJ10" s="4"/>
+      <c r="AK10" s="4"/>
+      <c r="AL10" s="4"/>
     </row>
-    <row r="11" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:38" ht="29.5">
       <c r="A11" s="1">
         <v>46203</v>
       </c>
@@ -2812,60 +2870,64 @@
       <c r="I11" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="3">
+        <v>15397</v>
+      </c>
+      <c r="K11" s="3">
+        <v>110825</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="3" t="s">
+      <c r="M11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="O11" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="P11" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="Q11" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="P11" s="8" t="s">
+      <c r="R11" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="Q11" s="8" t="s">
+      <c r="S11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R11" s="8" t="s">
+      <c r="T11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S11" s="8" t="s">
+      <c r="U11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="T11" s="8" t="s">
+      <c r="V11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="U11" s="8" t="s">
+      <c r="W11" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V11" s="8" t="s">
+      <c r="X11" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W11" s="8" t="s">
+      <c r="Y11" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="8">
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="8">
         <v>5.8382170999999996</v>
       </c>
-      <c r="Z11" s="8">
+      <c r="AB11" s="8">
         <v>9.8887873000000006</v>
       </c>
-      <c r="AA11" s="8" t="s">
+      <c r="AC11" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="AB11" s="4"/>
-      <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
@@ -2873,8 +2935,10 @@
       <c r="AH11" s="4"/>
       <c r="AI11" s="4"/>
       <c r="AJ11" s="4"/>
+      <c r="AK11" s="4"/>
+      <c r="AL11" s="4"/>
     </row>
-    <row r="12" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:38" ht="44.25">
       <c r="A12" s="1">
         <v>46203</v>
       </c>
@@ -2902,60 +2966,64 @@
       <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="3">
+        <v>19007</v>
+      </c>
+      <c r="K12" s="3">
+        <v>116642</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L12" s="3" t="s">
+      <c r="M12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="O12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="P12" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="Q12" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="P12" s="8" t="s">
+      <c r="R12" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="S12" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="R12" s="8" t="s">
+      <c r="T12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S12" s="8" t="s">
+      <c r="U12" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="T12" s="8" t="s">
+      <c r="V12" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="U12" s="8" t="s">
+      <c r="W12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V12" s="8" t="s">
+      <c r="X12" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W12" s="8" t="s">
+      <c r="Y12" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="8">
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="8">
         <v>3.8689866999999998</v>
       </c>
-      <c r="Z12" s="8">
+      <c r="AB12" s="8">
         <v>11.521334400000001</v>
       </c>
-      <c r="AA12" s="8" t="s">
+      <c r="AC12" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
@@ -2963,8 +3031,10 @@
       <c r="AH12" s="4"/>
       <c r="AI12" s="4"/>
       <c r="AJ12" s="4"/>
+      <c r="AK12" s="4"/>
+      <c r="AL12" s="4"/>
     </row>
-    <row r="13" spans="1:36" ht="59" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:38" ht="59">
       <c r="A13" s="1">
         <v>46203</v>
       </c>
@@ -2992,60 +3062,64 @@
       <c r="I13" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="3">
+        <v>11558</v>
+      </c>
+      <c r="K13" s="3">
+        <v>102609</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L13" s="3" t="s">
+      <c r="M13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="O13" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="N13" s="8" t="s">
+      <c r="P13" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="O13" s="8" t="s">
+      <c r="Q13" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="P13" s="8" t="s">
+      <c r="R13" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="Q13" s="8" t="s">
+      <c r="S13" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R13" s="8" t="s">
+      <c r="T13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S13" s="8" t="s">
+      <c r="U13" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="T13" s="8" t="s">
+      <c r="V13" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="U13" s="8" t="s">
+      <c r="W13" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V13" s="8">
+      <c r="X13" s="8">
         <v>2026</v>
       </c>
-      <c r="W13" s="8" t="s">
+      <c r="Y13" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="8">
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="8">
         <v>7.3211535999999997</v>
       </c>
-      <c r="Z13" s="8">
+      <c r="AB13" s="8">
         <v>13.587821399999999</v>
       </c>
-      <c r="AA13" s="8" t="s">
+      <c r="AC13" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
@@ -3053,8 +3127,10 @@
       <c r="AH13" s="4"/>
       <c r="AI13" s="4"/>
       <c r="AJ13" s="4"/>
+      <c r="AK13" s="4"/>
+      <c r="AL13" s="4"/>
     </row>
-    <row r="14" spans="1:36" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:38" ht="73.75">
       <c r="A14" s="1">
         <v>46203</v>
       </c>
@@ -3082,58 +3158,62 @@
       <c r="I14" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="3">
+        <v>11846</v>
+      </c>
+      <c r="K14" s="3">
+        <v>103273</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="N14" s="8" t="s">
+      <c r="P14" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="O14" s="8" t="s">
+      <c r="Q14" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="P14" s="8" t="s">
+      <c r="R14" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="Q14" s="8" t="s">
+      <c r="S14" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R14" s="8" t="s">
+      <c r="T14" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S14" s="8" t="s">
+      <c r="U14" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="T14" s="8" t="s">
+      <c r="V14" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="U14" s="8" t="s">
+      <c r="W14" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V14" s="8" t="s">
+      <c r="X14" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W14" s="8"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="8">
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="8">
         <v>7.3211535999999997</v>
       </c>
-      <c r="Z14" s="8">
+      <c r="AB14" s="8">
         <v>13.587821399999999</v>
       </c>
-      <c r="AA14" s="8" t="s">
+      <c r="AC14" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="AB14" s="4"/>
-      <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
@@ -3141,8 +3221,10 @@
       <c r="AH14" s="4"/>
       <c r="AI14" s="4"/>
       <c r="AJ14" s="4"/>
+      <c r="AK14" s="4"/>
+      <c r="AL14" s="4"/>
     </row>
-    <row r="15" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:38" ht="44.25">
       <c r="A15" s="1">
         <v>46203</v>
       </c>
@@ -3170,56 +3252,60 @@
       <c r="I15" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="3">
+        <v>11187</v>
+      </c>
+      <c r="K15" s="3">
+        <v>102997</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L15" s="3" t="s">
+      <c r="M15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M15" s="3"/>
-      <c r="N15" s="8" t="s">
+      <c r="O15" s="3"/>
+      <c r="P15" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="Q15" s="8" t="s">
         <v>33</v>
       </c>
       <c r="R15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="T15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S15" s="8" t="s">
+      <c r="U15" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T15" s="8" t="s">
+      <c r="V15" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="U15" s="8" t="s">
+      <c r="W15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V15" s="8" t="s">
+      <c r="X15" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="W15" s="8"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="8" t="s">
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="Z15" s="8" t="s">
+      <c r="AB15" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="AA15" s="8" t="s">
+      <c r="AC15" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="AB15" s="4"/>
-      <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
@@ -3227,8 +3313,10 @@
       <c r="AH15" s="4"/>
       <c r="AI15" s="4"/>
       <c r="AJ15" s="4"/>
+      <c r="AK15" s="4"/>
+      <c r="AL15" s="4"/>
     </row>
-    <row r="16" spans="1:36" ht="59" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:38" ht="59">
       <c r="A16" s="1">
         <v>46203</v>
       </c>
@@ -3256,60 +3344,64 @@
       <c r="I16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" s="3">
+        <v>11774</v>
+      </c>
+      <c r="K16" s="3">
+        <v>103079</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="M16" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="N16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="O16" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="N16" s="8" t="s">
+      <c r="P16" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="O16" s="8" t="s">
+      <c r="Q16" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="P16" s="8" t="s">
+      <c r="R16" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="Q16" s="8" t="s">
+      <c r="S16" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R16" s="8" t="s">
+      <c r="T16" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S16" s="8" t="s">
+      <c r="U16" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="T16" s="8" t="s">
+      <c r="V16" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="U16" s="8" t="s">
+      <c r="W16" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V16" s="8" t="s">
+      <c r="X16" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="W16" s="8" t="s">
+      <c r="Y16" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="8">
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="8">
         <v>10.6033083</v>
       </c>
-      <c r="Z16" s="8">
+      <c r="AB16" s="8">
         <v>14.328162499999999</v>
       </c>
-      <c r="AA16" s="8" t="s">
+      <c r="AC16" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="AB16" s="4"/>
-      <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
@@ -3317,8 +3409,10 @@
       <c r="AH16" s="4"/>
       <c r="AI16" s="4"/>
       <c r="AJ16" s="4"/>
+      <c r="AK16" s="4"/>
+      <c r="AL16" s="4"/>
     </row>
-    <row r="17" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:38" ht="29.5">
       <c r="A17" s="1">
         <v>46203</v>
       </c>
@@ -3346,60 +3440,64 @@
       <c r="I17" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="J17" s="3">
+        <v>11846</v>
+      </c>
+      <c r="K17" s="3">
+        <v>103273</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L17" s="3" t="s">
+      <c r="M17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="O17" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="N17" s="8" t="s">
+      <c r="P17" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="O17" s="8" t="s">
+      <c r="Q17" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="P17" s="8" t="s">
+      <c r="R17" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="Q17" s="8" t="s">
+      <c r="S17" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R17" s="8" t="s">
+      <c r="T17" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S17" s="8" t="s">
+      <c r="U17" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="T17" s="8" t="s">
+      <c r="V17" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="U17" s="8" t="s">
+      <c r="W17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V17" s="8" t="s">
+      <c r="X17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W17" s="8" t="s">
+      <c r="Y17" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="8">
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="8">
         <v>7.2786650000000002</v>
       </c>
-      <c r="Z17" s="8">
+      <c r="AB17" s="8">
         <v>13.5462694</v>
       </c>
-      <c r="AA17" s="8" t="s">
+      <c r="AC17" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="AB17" s="4"/>
-      <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
@@ -3407,8 +3505,10 @@
       <c r="AH17" s="4"/>
       <c r="AI17" s="4"/>
       <c r="AJ17" s="4"/>
+      <c r="AK17" s="4"/>
+      <c r="AL17" s="4"/>
     </row>
-    <row r="18" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:38" ht="29.5">
       <c r="A18" s="1">
         <v>46203</v>
       </c>
@@ -3436,58 +3536,62 @@
       <c r="I18" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="3">
+        <v>11926</v>
+      </c>
+      <c r="K18" s="3">
+        <v>103442</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" s="3" t="s">
+      <c r="M18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M18" s="3"/>
-      <c r="N18" s="8" t="s">
+      <c r="O18" s="3"/>
+      <c r="P18" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="Q18" s="8" t="s">
         <v>33</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S18" s="8" t="s">
         <v>33</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U18" s="8" t="s">
         <v>33</v>
       </c>
       <c r="V18" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="W18" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="X18" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W18" s="8" t="s">
+      <c r="Y18" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="8" t="s">
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="Z18" s="8" t="s">
+      <c r="AB18" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="AA18" s="8" t="s">
+      <c r="AC18" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
@@ -3495,8 +3599,10 @@
       <c r="AH18" s="4"/>
       <c r="AI18" s="4"/>
       <c r="AJ18" s="4"/>
+      <c r="AK18" s="4"/>
+      <c r="AL18" s="4"/>
     </row>
-    <row r="19" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:38" ht="29.5">
       <c r="A19" s="1">
         <v>46203</v>
       </c>
@@ -3524,60 +3630,64 @@
       <c r="I19" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="J19" s="3">
+        <v>15014</v>
+      </c>
+      <c r="K19" s="3">
+        <v>109445</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" s="3" t="s">
+      <c r="M19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M19" s="3" t="s">
+      <c r="O19" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="N19" s="8" t="s">
+      <c r="P19" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="O19" s="8" t="s">
+      <c r="Q19" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="P19" s="8" t="s">
+      <c r="R19" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="Q19" s="8" t="s">
+      <c r="S19" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R19" s="8" t="s">
+      <c r="T19" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S19" s="8" t="s">
+      <c r="U19" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="T19" s="8" t="s">
+      <c r="V19" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="U19" s="8" t="s">
+      <c r="W19" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V19" s="8" t="s">
+      <c r="X19" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W19" s="8" t="s">
+      <c r="Y19" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="8">
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="8">
         <v>10.4014393</v>
       </c>
-      <c r="Z19" s="8">
+      <c r="AB19" s="8">
         <v>14.4425653</v>
       </c>
-      <c r="AA19" s="8" t="s">
+      <c r="AC19" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="AB19" s="4"/>
-      <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
       <c r="AF19" s="4"/>
@@ -3585,8 +3695,10 @@
       <c r="AH19" s="4"/>
       <c r="AI19" s="4"/>
       <c r="AJ19" s="4"/>
+      <c r="AK19" s="4"/>
+      <c r="AL19" s="4"/>
     </row>
-    <row r="20" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:38" ht="29.5">
       <c r="A20" s="1">
         <v>46203</v>
       </c>
@@ -3614,60 +3726,64 @@
       <c r="I20" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="3">
+        <v>12509</v>
+      </c>
+      <c r="K20" s="3">
+        <v>104605</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="N20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="O20" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="N20" s="8" t="s">
+      <c r="P20" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="O20" s="8" t="s">
+      <c r="Q20" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="P20" s="8" t="s">
+      <c r="R20" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="Q20" s="8" t="s">
+      <c r="S20" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R20" s="8" t="s">
+      <c r="T20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S20" s="8" t="s">
+      <c r="U20" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="T20" s="8" t="s">
+      <c r="V20" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="U20" s="8" t="s">
+      <c r="W20" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="V20" s="8" t="s">
+      <c r="X20" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W20" s="8" t="s">
+      <c r="Y20" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="8">
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="8">
         <v>11.0484452</v>
       </c>
-      <c r="Z20" s="8">
+      <c r="AB20" s="8">
         <v>14.1342835</v>
       </c>
-      <c r="AA20" s="8" t="s">
+      <c r="AC20" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="AB20" s="4"/>
-      <c r="AC20" s="4"/>
       <c r="AD20" s="4"/>
       <c r="AE20" s="4"/>
       <c r="AF20" s="4"/>
@@ -3675,8 +3791,10 @@
       <c r="AH20" s="4"/>
       <c r="AI20" s="4"/>
       <c r="AJ20" s="4"/>
+      <c r="AK20" s="4"/>
+      <c r="AL20" s="4"/>
     </row>
-    <row r="21" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:38" ht="29.5">
       <c r="A21" s="1">
         <v>46203</v>
       </c>
@@ -3704,60 +3822,64 @@
       <c r="I21" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="3">
+        <v>12517</v>
+      </c>
+      <c r="K21" s="3">
+        <v>104619</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L21" s="3" t="s">
+      <c r="M21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="N21" s="8" t="s">
+      <c r="P21" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="O21" s="8" t="s">
+      <c r="Q21" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="P21" s="8" t="s">
+      <c r="R21" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Q21" s="8" t="s">
+      <c r="S21" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R21" s="8" t="s">
+      <c r="T21" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S21" s="8" t="s">
+      <c r="U21" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="T21" s="8" t="s">
+      <c r="V21" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="U21" s="8" t="s">
+      <c r="W21" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V21" s="8" t="s">
+      <c r="X21" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W21" s="8" t="s">
+      <c r="Y21" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="8">
+      <c r="Z21" s="4"/>
+      <c r="AA21" s="8">
         <v>10.74103</v>
       </c>
-      <c r="Z21" s="8">
+      <c r="AB21" s="8">
         <v>13.798742000000001</v>
       </c>
-      <c r="AA21" s="8" t="s">
+      <c r="AC21" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="AB21" s="4"/>
-      <c r="AC21" s="4"/>
       <c r="AD21" s="4"/>
       <c r="AE21" s="4"/>
       <c r="AF21" s="4"/>
@@ -3765,8 +3887,10 @@
       <c r="AH21" s="4"/>
       <c r="AI21" s="4"/>
       <c r="AJ21" s="4"/>
+      <c r="AK21" s="4"/>
+      <c r="AL21" s="4"/>
     </row>
-    <row r="22" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:38" ht="29.5">
       <c r="A22" s="1">
         <v>46203</v>
       </c>
@@ -3794,60 +3918,64 @@
       <c r="I22" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="3">
+        <v>12517</v>
+      </c>
+      <c r="K22" s="3">
+        <v>104619</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="N22" s="8" t="s">
+      <c r="P22" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="O22" s="8" t="s">
+      <c r="Q22" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="P22" s="8" t="s">
+      <c r="R22" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Q22" s="8" t="s">
+      <c r="S22" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R22" s="8" t="s">
+      <c r="T22" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S22" s="8" t="s">
+      <c r="U22" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="T22" s="8" t="s">
+      <c r="V22" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="U22" s="8" t="s">
+      <c r="W22" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V22" s="8" t="s">
+      <c r="X22" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="W22" s="8" t="s">
+      <c r="Y22" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="8" t="s">
+      <c r="Z22" s="4"/>
+      <c r="AA22" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="Z22" s="8" t="s">
+      <c r="AB22" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="AA22" s="8" t="s">
+      <c r="AC22" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="AB22" s="4"/>
-      <c r="AC22" s="4"/>
       <c r="AD22" s="4"/>
       <c r="AE22" s="4"/>
       <c r="AF22" s="4"/>
@@ -3855,8 +3983,10 @@
       <c r="AH22" s="4"/>
       <c r="AI22" s="4"/>
       <c r="AJ22" s="4"/>
+      <c r="AK22" s="4"/>
+      <c r="AL22" s="4"/>
     </row>
-    <row r="23" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:38" ht="29.5">
       <c r="A23" s="1">
         <v>46203</v>
       </c>
@@ -3884,60 +4014,64 @@
       <c r="I23" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J23" s="3">
+        <v>10166</v>
+      </c>
+      <c r="K23" s="3">
+        <v>100086</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="M23" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="N23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="O23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="N23" s="8" t="s">
+      <c r="P23" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="O23" s="8" t="s">
+      <c r="Q23" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="P23" s="8" t="s">
+      <c r="R23" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="Q23" s="8" t="s">
+      <c r="S23" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R23" s="8" t="s">
+      <c r="T23" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S23" s="8" t="s">
+      <c r="U23" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="T23" s="8" t="s">
+      <c r="V23" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="U23" s="8" t="s">
+      <c r="W23" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V23" s="8" t="s">
+      <c r="X23" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="W23" s="8" t="s">
+      <c r="Y23" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="X23" s="4"/>
-      <c r="Y23" s="8">
+      <c r="Z23" s="4"/>
+      <c r="AA23" s="8">
         <v>11.780627000000001</v>
       </c>
-      <c r="Z23" s="8">
+      <c r="AB23" s="8">
         <v>15.103911999999999</v>
       </c>
-      <c r="AA23" s="8" t="s">
+      <c r="AC23" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="AB23" s="4"/>
-      <c r="AC23" s="4"/>
       <c r="AD23" s="4"/>
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
@@ -3945,8 +4079,10 @@
       <c r="AH23" s="4"/>
       <c r="AI23" s="4"/>
       <c r="AJ23" s="4"/>
+      <c r="AK23" s="4"/>
+      <c r="AL23" s="4"/>
     </row>
-    <row r="24" spans="1:36" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:38" ht="73.75">
       <c r="A24" s="1">
         <v>46203</v>
       </c>
@@ -3974,60 +4110,64 @@
       <c r="I24" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="J24" s="3">
+        <v>12778</v>
+      </c>
+      <c r="K24" s="3">
+        <v>105185</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L24" s="3" t="s">
+      <c r="M24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="O24" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="N24" s="8" t="s">
+      <c r="P24" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="O24" s="8" t="s">
+      <c r="Q24" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="P24" s="8" t="s">
+      <c r="R24" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="Q24" s="8" t="s">
+      <c r="S24" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R24" s="8" t="s">
+      <c r="T24" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S24" s="8" t="s">
+      <c r="U24" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="T24" s="8" t="s">
+      <c r="V24" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="U24" s="8" t="s">
+      <c r="W24" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V24" s="8" t="s">
+      <c r="X24" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="W24" s="8" t="s">
+      <c r="Y24" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="X24" s="4"/>
-      <c r="Y24" s="8" t="s">
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="Z24" s="8" t="s">
+      <c r="AB24" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="AA24" s="8" t="s">
+      <c r="AC24" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="AB24" s="4"/>
-      <c r="AC24" s="4"/>
       <c r="AD24" s="4"/>
       <c r="AE24" s="4"/>
       <c r="AF24" s="4"/>
@@ -4035,8 +4175,10 @@
       <c r="AH24" s="4"/>
       <c r="AI24" s="4"/>
       <c r="AJ24" s="4"/>
+      <c r="AK24" s="4"/>
+      <c r="AL24" s="4"/>
     </row>
-    <row r="25" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:38" ht="29.5">
       <c r="A25" s="1">
         <v>46203</v>
       </c>
@@ -4064,58 +4206,62 @@
       <c r="I25" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="J25" s="3">
+        <v>15614</v>
+      </c>
+      <c r="K25" s="3">
+        <v>110241</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L25" s="3" t="s">
+      <c r="M25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M25" s="3"/>
-      <c r="N25" s="8" t="s">
+      <c r="O25" s="3"/>
+      <c r="P25" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="O25" s="8" t="s">
+      <c r="Q25" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="P25" s="8" t="s">
+      <c r="R25" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="Q25" s="8" t="s">
+      <c r="S25" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="R25" s="8" t="s">
+      <c r="T25" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S25" s="8" t="s">
+      <c r="U25" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="T25" s="8" t="s">
+      <c r="V25" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="U25" s="8" t="s">
+      <c r="W25" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V25" s="8" t="s">
+      <c r="X25" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W25" s="8" t="s">
+      <c r="Y25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="X25" s="4"/>
-      <c r="Y25" s="8">
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="8">
         <v>9.0574802000000005</v>
       </c>
-      <c r="Z25" s="8">
+      <c r="AB25" s="8">
         <v>13.6653588</v>
       </c>
-      <c r="AA25" s="8" t="s">
+      <c r="AC25" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AB25" s="4"/>
-      <c r="AC25" s="4"/>
       <c r="AD25" s="4"/>
       <c r="AE25" s="4"/>
       <c r="AF25" s="4"/>
@@ -4123,8 +4269,10 @@
       <c r="AH25" s="4"/>
       <c r="AI25" s="4"/>
       <c r="AJ25" s="4"/>
+      <c r="AK25" s="4"/>
+      <c r="AL25" s="4"/>
     </row>
-    <row r="26" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:38" ht="44.25">
       <c r="A26" s="1">
         <v>46203</v>
       </c>
@@ -4152,60 +4300,64 @@
       <c r="I26" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="J26" s="3">
+        <v>13193</v>
+      </c>
+      <c r="K26" s="3">
+        <v>105977</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L26" s="3" t="s">
+      <c r="M26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M26" s="3" t="s">
+      <c r="O26" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="N26" s="8" t="s">
+      <c r="P26" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="O26" s="8" t="s">
+      <c r="Q26" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P26" s="8" t="s">
+      <c r="R26" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="Q26" s="8" t="s">
+      <c r="S26" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R26" s="8" t="s">
+      <c r="T26" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S26" s="8" t="s">
+      <c r="U26" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="T26" s="8" t="s">
+      <c r="V26" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="U26" s="8" t="s">
+      <c r="W26" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V26" s="8" t="s">
+      <c r="X26" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="W26" s="8" t="s">
+      <c r="Y26" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="8" t="s">
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="Z26" s="8" t="s">
+      <c r="AB26" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="AA26" s="8" t="s">
+      <c r="AC26" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="AB26" s="4"/>
-      <c r="AC26" s="4"/>
       <c r="AD26" s="4"/>
       <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
@@ -4213,8 +4365,10 @@
       <c r="AH26" s="4"/>
       <c r="AI26" s="4"/>
       <c r="AJ26" s="4"/>
+      <c r="AK26" s="4"/>
+      <c r="AL26" s="4"/>
     </row>
-    <row r="27" spans="1:36" ht="59" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:38" ht="59">
       <c r="A27" s="1">
         <v>46203</v>
       </c>
@@ -4242,60 +4396,64 @@
       <c r="I27" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="J27" s="3">
+        <v>13201</v>
+      </c>
+      <c r="K27" s="3">
+        <v>106001</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L27" s="3" t="s">
+      <c r="M27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M27" s="3" t="s">
+      <c r="O27" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="N27" s="8" t="s">
+      <c r="P27" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="O27" s="8" t="s">
+      <c r="Q27" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="P27" s="8" t="s">
+      <c r="R27" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Q27" s="8" t="s">
+      <c r="S27" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R27" s="8" t="s">
+      <c r="T27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S27" s="8" t="s">
+      <c r="U27" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="T27" s="8" t="s">
+      <c r="V27" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="U27" s="8" t="s">
+      <c r="W27" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V27" s="8" t="s">
+      <c r="X27" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W27" s="8" t="s">
+      <c r="Y27" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="X27" s="4"/>
-      <c r="Y27" s="8">
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="8">
         <v>10.74103</v>
       </c>
-      <c r="Z27" s="8">
+      <c r="AB27" s="8">
         <v>13.798742000000001</v>
       </c>
-      <c r="AA27" s="8" t="s">
+      <c r="AC27" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="AB27" s="4"/>
-      <c r="AC27" s="4"/>
       <c r="AD27" s="4"/>
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
@@ -4303,8 +4461,10 @@
       <c r="AH27" s="4"/>
       <c r="AI27" s="4"/>
       <c r="AJ27" s="4"/>
+      <c r="AK27" s="4"/>
+      <c r="AL27" s="4"/>
     </row>
-    <row r="28" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:38" ht="44.25">
       <c r="A28" s="1">
         <v>46203</v>
       </c>
@@ -4332,60 +4492,64 @@
       <c r="I28" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="J28" s="3">
+        <v>13487</v>
+      </c>
+      <c r="K28" s="3">
+        <v>106228</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="K28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L28" s="3" t="s">
+      <c r="M28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M28" s="3" t="s">
+      <c r="O28" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="N28" s="8" t="s">
+      <c r="P28" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="O28" s="8" t="s">
+      <c r="Q28" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="P28" s="8" t="s">
+      <c r="R28" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="Q28" s="8" t="s">
+      <c r="S28" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R28" s="8" t="s">
+      <c r="T28" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S28" s="8" t="s">
+      <c r="U28" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="T28" s="8" t="s">
+      <c r="V28" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="U28" s="8" t="s">
+      <c r="W28" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="V28" s="8" t="s">
+      <c r="X28" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="W28" s="8" t="s">
+      <c r="Y28" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="8">
+      <c r="Z28" s="4"/>
+      <c r="AA28" s="8">
         <v>11.0484452</v>
       </c>
-      <c r="Z28" s="8">
+      <c r="AB28" s="8">
         <v>14.1342835</v>
       </c>
-      <c r="AA28" s="8" t="s">
+      <c r="AC28" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="AB28" s="4"/>
-      <c r="AC28" s="4"/>
       <c r="AD28" s="4"/>
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
@@ -4393,8 +4557,10 @@
       <c r="AH28" s="4"/>
       <c r="AI28" s="4"/>
       <c r="AJ28" s="4"/>
+      <c r="AK28" s="4"/>
+      <c r="AL28" s="4"/>
     </row>
-    <row r="29" spans="1:36" ht="59" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:38" ht="59">
       <c r="A29" s="1">
         <v>46203</v>
       </c>
@@ -4422,60 +4588,64 @@
       <c r="I29" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="J29" s="3">
+        <v>13560</v>
+      </c>
+      <c r="K29" s="3">
+        <v>106369</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="N29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="O29" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="N29" s="8" t="s">
+      <c r="P29" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="O29" s="8" t="s">
+      <c r="Q29" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="P29" s="8" t="s">
+      <c r="R29" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="Q29" s="8" t="s">
+      <c r="S29" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R29" s="8" t="s">
+      <c r="T29" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S29" s="8" t="s">
+      <c r="U29" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="T29" s="8" t="s">
+      <c r="V29" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="U29" s="8" t="s">
+      <c r="W29" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V29" s="8" t="s">
+      <c r="X29" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W29" s="8" t="s">
+      <c r="Y29" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="X29" s="4"/>
-      <c r="Y29" s="8">
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="8">
         <v>12.0831175</v>
       </c>
-      <c r="Z29" s="8">
+      <c r="AB29" s="8">
         <v>15.019126200000001</v>
       </c>
-      <c r="AA29" s="8" t="s">
+      <c r="AC29" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="AB29" s="4"/>
-      <c r="AC29" s="4"/>
       <c r="AD29" s="4"/>
       <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
@@ -4483,8 +4653,10 @@
       <c r="AH29" s="4"/>
       <c r="AI29" s="4"/>
       <c r="AJ29" s="4"/>
+      <c r="AK29" s="4"/>
+      <c r="AL29" s="4"/>
     </row>
-    <row r="30" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:38" ht="29.5">
       <c r="A30" s="1">
         <v>46203</v>
       </c>
@@ -4512,60 +4684,64 @@
       <c r="I30" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="J30" s="3">
+        <v>13581</v>
+      </c>
+      <c r="K30" s="3">
+        <v>106395</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="K30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L30" s="3" t="s">
+      <c r="M30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M30" s="3" t="s">
+      <c r="O30" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="N30" s="8" t="s">
+      <c r="P30" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="O30" s="8" t="s">
+      <c r="Q30" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="P30" s="8" t="s">
+      <c r="R30" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="Q30" s="8" t="s">
+      <c r="S30" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R30" s="8" t="s">
+      <c r="T30" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S30" s="8" t="s">
+      <c r="U30" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="T30" s="8" t="s">
+      <c r="V30" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U30" s="8" t="s">
+      <c r="W30" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V30" s="8" t="s">
+      <c r="X30" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W30" s="8" t="s">
+      <c r="Y30" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="8">
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="8">
         <v>4.8673555000000004</v>
       </c>
-      <c r="Z30" s="8">
+      <c r="AB30" s="8">
         <v>11.156444</v>
       </c>
-      <c r="AA30" s="8" t="s">
+      <c r="AC30" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="AB30" s="4"/>
-      <c r="AC30" s="4"/>
       <c r="AD30" s="4"/>
       <c r="AE30" s="4"/>
       <c r="AF30" s="4"/>
@@ -4573,8 +4749,10 @@
       <c r="AH30" s="4"/>
       <c r="AI30" s="4"/>
       <c r="AJ30" s="4"/>
+      <c r="AK30" s="4"/>
+      <c r="AL30" s="4"/>
     </row>
-    <row r="31" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:38" ht="29.5">
       <c r="A31" s="1">
         <v>46203</v>
       </c>
@@ -4602,60 +4780,64 @@
       <c r="I31" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J31" s="3">
+        <v>11774</v>
+      </c>
+      <c r="K31" s="3">
+        <v>103079</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="M31" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="L31" s="3" t="s">
+      <c r="N31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M31" s="3" t="s">
+      <c r="O31" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="N31" s="8" t="s">
+      <c r="P31" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="O31" s="8" t="s">
+      <c r="Q31" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="P31" s="8" t="s">
+      <c r="R31" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="Q31" s="8" t="s">
+      <c r="S31" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R31" s="8" t="s">
+      <c r="T31" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S31" s="8" t="s">
+      <c r="U31" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="T31" s="8" t="s">
+      <c r="V31" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="U31" s="8" t="s">
+      <c r="W31" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V31" s="8" t="s">
+      <c r="X31" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W31" s="8" t="s">
+      <c r="Y31" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="8">
+      <c r="Z31" s="4"/>
+      <c r="AA31" s="8">
         <v>4.8673555000000004</v>
       </c>
-      <c r="Z31" s="8">
+      <c r="AB31" s="8">
         <v>11.156444</v>
       </c>
-      <c r="AA31" s="8" t="s">
+      <c r="AC31" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="AB31" s="4"/>
-      <c r="AC31" s="4"/>
       <c r="AD31" s="4"/>
       <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
@@ -4663,8 +4845,10 @@
       <c r="AH31" s="4"/>
       <c r="AI31" s="4"/>
       <c r="AJ31" s="4"/>
+      <c r="AK31" s="4"/>
+      <c r="AL31" s="4"/>
     </row>
-    <row r="32" spans="1:36" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:38" ht="59">
       <c r="A32" s="1">
         <v>46203</v>
       </c>
@@ -4692,60 +4876,64 @@
       <c r="I32" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="J32" s="3">
+        <v>13642</v>
+      </c>
+      <c r="K32" s="3">
+        <v>106494</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L32" s="3" t="s">
+      <c r="M32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M32" s="3" t="s">
+      <c r="O32" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="N32" s="8" t="s">
+      <c r="P32" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="O32" s="8" t="s">
+      <c r="Q32" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="P32" s="8" t="s">
+      <c r="R32" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="Q32" s="8" t="s">
+      <c r="S32" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R32" s="8" t="s">
+      <c r="T32" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S32" s="8" t="s">
+      <c r="U32" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="T32" s="8" t="s">
+      <c r="V32" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="U32" s="8" t="s">
+      <c r="W32" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="V32" s="8" t="s">
+      <c r="X32" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W32" s="8" t="s">
+      <c r="Y32" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="8">
+      <c r="Z32" s="4"/>
+      <c r="AA32" s="8">
         <v>6.5172122999999997</v>
       </c>
-      <c r="Z32" s="8">
+      <c r="AB32" s="8">
         <v>14.294787899999999</v>
       </c>
-      <c r="AA32" s="8" t="s">
+      <c r="AC32" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="AB32" s="4"/>
-      <c r="AC32" s="4"/>
       <c r="AD32" s="4"/>
       <c r="AE32" s="4"/>
       <c r="AF32" s="4"/>
@@ -4753,8 +4941,10 @@
       <c r="AH32" s="4"/>
       <c r="AI32" s="4"/>
       <c r="AJ32" s="4"/>
+      <c r="AK32" s="4"/>
+      <c r="AL32" s="4"/>
     </row>
-    <row r="33" spans="1:36" ht="88.5" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:38" ht="88.5">
       <c r="A33" s="1">
         <v>46203</v>
       </c>
@@ -4782,58 +4972,62 @@
       <c r="I33" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="J33" s="3">
+        <v>13676</v>
+      </c>
+      <c r="K33" s="3">
+        <v>106547</v>
+      </c>
+      <c r="L33" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L33" s="3" t="s">
+      <c r="M33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M33" s="3"/>
-      <c r="N33" s="8" t="s">
+      <c r="O33" s="3"/>
+      <c r="P33" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="O33" s="8" t="s">
+      <c r="Q33" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="P33" s="8" t="s">
+      <c r="R33" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q33" s="8" t="s">
+      <c r="S33" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R33" s="8" t="s">
+      <c r="T33" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S33" s="8" t="s">
+      <c r="U33" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="T33" s="8" t="s">
+      <c r="V33" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="U33" s="8" t="s">
+      <c r="W33" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V33" s="8" t="s">
+      <c r="X33" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W33" s="8" t="s">
+      <c r="Y33" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="8">
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="8">
         <v>5.7961640000000001</v>
       </c>
-      <c r="Z33" s="8">
+      <c r="AB33" s="8">
         <v>10.162518</v>
       </c>
-      <c r="AA33" s="8" t="s">
+      <c r="AC33" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AB33" s="4"/>
-      <c r="AC33" s="4"/>
       <c r="AD33" s="4"/>
       <c r="AE33" s="4"/>
       <c r="AF33" s="4"/>
@@ -4841,8 +5035,10 @@
       <c r="AH33" s="4"/>
       <c r="AI33" s="4"/>
       <c r="AJ33" s="4"/>
+      <c r="AK33" s="4"/>
+      <c r="AL33" s="4"/>
     </row>
-    <row r="34" spans="1:36" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:38" ht="73.75">
       <c r="A34" s="1">
         <v>46203</v>
       </c>
@@ -4870,60 +5066,64 @@
       <c r="I34" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="J34" s="3">
+        <v>13760</v>
+      </c>
+      <c r="K34" s="3">
+        <v>106702</v>
+      </c>
+      <c r="L34" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="K34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L34" s="3" t="s">
+      <c r="M34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M34" s="3" t="s">
+      <c r="O34" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="N34" s="8" t="s">
+      <c r="P34" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="O34" s="8" t="s">
+      <c r="Q34" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="P34" s="8" t="s">
+      <c r="R34" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Q34" s="8" t="s">
+      <c r="S34" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R34" s="8" t="s">
+      <c r="T34" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S34" s="8" t="s">
+      <c r="U34" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="T34" s="8" t="s">
+      <c r="V34" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="U34" s="8" t="s">
+      <c r="W34" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V34" s="8" t="s">
+      <c r="X34" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W34" s="8" t="s">
+      <c r="Y34" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="8">
+      <c r="Z34" s="4"/>
+      <c r="AA34" s="8">
         <v>10.74103</v>
       </c>
-      <c r="Z34" s="8">
+      <c r="AB34" s="8">
         <v>13.798742000000001</v>
       </c>
-      <c r="AA34" s="8" t="s">
+      <c r="AC34" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="AB34" s="4"/>
-      <c r="AC34" s="4"/>
       <c r="AD34" s="4"/>
       <c r="AE34" s="4"/>
       <c r="AF34" s="4"/>
@@ -4931,8 +5131,10 @@
       <c r="AH34" s="4"/>
       <c r="AI34" s="4"/>
       <c r="AJ34" s="4"/>
+      <c r="AK34" s="4"/>
+      <c r="AL34" s="4"/>
     </row>
-    <row r="35" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:38" ht="44.25">
       <c r="A35" s="1">
         <v>46203</v>
       </c>
@@ -4960,56 +5162,60 @@
       <c r="I35" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J35" s="3">
+        <v>13868</v>
+      </c>
+      <c r="K35" s="3">
+        <v>106897</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L35" s="3" t="s">
+      <c r="M35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N35" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M35" s="3" t="s">
+      <c r="O35" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="N35" s="8" t="s">
+      <c r="P35" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="O35" s="8" t="s">
+      <c r="Q35" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="P35" s="8" t="s">
+      <c r="R35" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="Q35" s="8" t="s">
+      <c r="S35" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R35" s="8" t="s">
+      <c r="T35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S35" s="8" t="s">
+      <c r="U35" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="T35" s="8" t="s">
+      <c r="V35" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="U35" s="8" t="s">
+      <c r="W35" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V35" s="8" t="s">
+      <c r="X35" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W35" s="8" t="s">
+      <c r="Y35" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="8"/>
-      <c r="Z35" s="8"/>
-      <c r="AA35" s="8" t="s">
+      <c r="Z35" s="4"/>
+      <c r="AA35" s="8"/>
+      <c r="AB35" s="8"/>
+      <c r="AC35" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="AB35" s="4"/>
-      <c r="AC35" s="4"/>
       <c r="AD35" s="4"/>
       <c r="AE35" s="4"/>
       <c r="AF35" s="4"/>
@@ -5017,8 +5223,10 @@
       <c r="AH35" s="4"/>
       <c r="AI35" s="4"/>
       <c r="AJ35" s="4"/>
+      <c r="AK35" s="4"/>
+      <c r="AL35" s="4"/>
     </row>
-    <row r="36" spans="1:36" ht="59" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:38" ht="59">
       <c r="A36" s="1">
         <v>46203</v>
       </c>
@@ -5046,60 +5254,64 @@
       <c r="I36" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="J36" s="3">
+        <v>13487</v>
+      </c>
+      <c r="K36" s="3">
+        <v>106228</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="K36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L36" s="3" t="s">
+      <c r="M36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N36" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M36" s="3" t="s">
+      <c r="O36" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="N36" s="8" t="s">
+      <c r="P36" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="O36" s="8" t="s">
+      <c r="Q36" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="P36" s="8" t="s">
+      <c r="R36" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="Q36" s="8" t="s">
+      <c r="S36" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R36" s="8" t="s">
+      <c r="T36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S36" s="8" t="s">
+      <c r="U36" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="T36" s="8" t="s">
+      <c r="V36" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="U36" s="8" t="s">
+      <c r="W36" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="V36" s="8" t="s">
+      <c r="X36" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W36" s="8" t="s">
+      <c r="Y36" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="8">
+      <c r="Z36" s="4"/>
+      <c r="AA36" s="8">
         <v>11.0484452</v>
       </c>
-      <c r="Z36" s="8">
+      <c r="AB36" s="8">
         <v>14.1342835</v>
       </c>
-      <c r="AA36" s="8" t="s">
+      <c r="AC36" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="AB36" s="4"/>
-      <c r="AC36" s="4"/>
       <c r="AD36" s="4"/>
       <c r="AE36" s="4"/>
       <c r="AF36" s="4"/>
@@ -5107,8 +5319,10 @@
       <c r="AH36" s="4"/>
       <c r="AI36" s="4"/>
       <c r="AJ36" s="4"/>
+      <c r="AK36" s="4"/>
+      <c r="AL36" s="4"/>
     </row>
-    <row r="37" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:38" ht="44.25">
       <c r="A37" s="1">
         <v>46203</v>
       </c>
@@ -5136,60 +5350,64 @@
       <c r="I37" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="J37" s="3">
+        <v>13898</v>
+      </c>
+      <c r="K37" s="3">
+        <v>106976</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="K37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L37" s="3" t="s">
+      <c r="M37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N37" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M37" s="3" t="s">
+      <c r="O37" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="N37" s="8" t="s">
+      <c r="P37" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="O37" s="8" t="s">
+      <c r="Q37" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="P37" s="8" t="s">
+      <c r="R37" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="Q37" s="8" t="s">
+      <c r="S37" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R37" s="8" t="s">
+      <c r="T37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S37" s="8" t="s">
+      <c r="U37" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="T37" s="8" t="s">
+      <c r="V37" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="U37" s="8" t="s">
+      <c r="W37" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="V37" s="8" t="s">
+      <c r="X37" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W37" s="8" t="s">
+      <c r="Y37" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="X37" s="4"/>
-      <c r="Y37" s="8">
+      <c r="Z37" s="4"/>
+      <c r="AA37" s="8">
         <v>11.0484452</v>
       </c>
-      <c r="Z37" s="8">
+      <c r="AB37" s="8">
         <v>14.1342835</v>
       </c>
-      <c r="AA37" s="8" t="s">
+      <c r="AC37" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="AB37" s="4"/>
-      <c r="AC37" s="4"/>
       <c r="AD37" s="4"/>
       <c r="AE37" s="4"/>
       <c r="AF37" s="4"/>
@@ -5197,8 +5415,10 @@
       <c r="AH37" s="4"/>
       <c r="AI37" s="4"/>
       <c r="AJ37" s="4"/>
+      <c r="AK37" s="4"/>
+      <c r="AL37" s="4"/>
     </row>
-    <row r="38" spans="1:36" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:38" ht="73.75">
       <c r="A38" s="1">
         <v>46203</v>
       </c>
@@ -5226,60 +5446,64 @@
       <c r="I38" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="J38" s="3">
+        <v>13760</v>
+      </c>
+      <c r="K38" s="3">
+        <v>106702</v>
+      </c>
+      <c r="L38" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="K38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L38" s="3" t="s">
+      <c r="M38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N38" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M38" s="3" t="s">
+      <c r="O38" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="N38" s="8" t="s">
+      <c r="P38" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="O38" s="8" t="s">
+      <c r="Q38" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="P38" s="8" t="s">
+      <c r="R38" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Q38" s="8" t="s">
+      <c r="S38" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R38" s="8" t="s">
+      <c r="T38" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S38" s="8" t="s">
+      <c r="U38" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="T38" s="8" t="s">
+      <c r="V38" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="U38" s="8" t="s">
+      <c r="W38" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V38" s="8" t="s">
+      <c r="X38" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W38" s="8" t="s">
+      <c r="Y38" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="8">
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="8">
         <v>10.74103</v>
       </c>
-      <c r="Z38" s="8">
+      <c r="AB38" s="8">
         <v>13.798742000000001</v>
       </c>
-      <c r="AA38" s="8" t="s">
+      <c r="AC38" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="AB38" s="4"/>
-      <c r="AC38" s="4"/>
       <c r="AD38" s="4"/>
       <c r="AE38" s="4"/>
       <c r="AF38" s="4"/>
@@ -5287,8 +5511,10 @@
       <c r="AH38" s="4"/>
       <c r="AI38" s="4"/>
       <c r="AJ38" s="4"/>
+      <c r="AK38" s="4"/>
+      <c r="AL38" s="4"/>
     </row>
-    <row r="39" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:38" ht="29.5">
       <c r="A39" s="1">
         <v>46203</v>
       </c>
@@ -5316,60 +5542,64 @@
       <c r="I39" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="J39" s="3">
+        <v>13864</v>
+      </c>
+      <c r="K39" s="3">
+        <v>106889</v>
+      </c>
+      <c r="L39" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="M39" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="N39" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M39" s="3" t="s">
+      <c r="O39" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="N39" s="8" t="s">
+      <c r="P39" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="O39" s="8" t="s">
+      <c r="Q39" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="P39" s="8" t="s">
+      <c r="R39" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="Q39" s="8" t="s">
+      <c r="S39" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="R39" s="8" t="s">
+      <c r="T39" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S39" s="8" t="s">
+      <c r="U39" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="T39" s="8" t="s">
+      <c r="V39" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="U39" s="8" t="s">
+      <c r="W39" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V39" s="8" t="s">
+      <c r="X39" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="W39" s="8" t="s">
+      <c r="Y39" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="X39" s="4"/>
-      <c r="Y39" s="8">
+      <c r="Z39" s="4"/>
+      <c r="AA39" s="8">
         <v>5.7282261999999999</v>
       </c>
-      <c r="Z39" s="8">
+      <c r="AB39" s="8">
         <v>10.897160299999999</v>
       </c>
-      <c r="AA39" s="8" t="s">
+      <c r="AC39" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="AB39" s="4"/>
-      <c r="AC39" s="4"/>
       <c r="AD39" s="4"/>
       <c r="AE39" s="4"/>
       <c r="AF39" s="4"/>
@@ -5377,8 +5607,10 @@
       <c r="AH39" s="4"/>
       <c r="AI39" s="4"/>
       <c r="AJ39" s="4"/>
+      <c r="AK39" s="4"/>
+      <c r="AL39" s="4"/>
     </row>
-    <row r="40" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:38" ht="29.5">
       <c r="A40" s="1">
         <v>46203</v>
       </c>
@@ -5406,60 +5638,64 @@
       <c r="I40" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="J40" s="3">
+        <v>13840</v>
+      </c>
+      <c r="K40" s="3">
+        <v>106832</v>
+      </c>
+      <c r="L40" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L40" s="3" t="s">
+      <c r="M40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N40" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M40" s="3" t="s">
+      <c r="O40" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="N40" s="8" t="s">
+      <c r="P40" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="O40" s="8" t="s">
+      <c r="Q40" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="P40" s="8" t="s">
+      <c r="R40" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="Q40" s="8" t="s">
+      <c r="S40" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R40" s="8" t="s">
+      <c r="T40" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S40" s="8" t="s">
+      <c r="U40" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="T40" s="8" t="s">
+      <c r="V40" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="U40" s="8" t="s">
+      <c r="W40" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V40" s="8" t="s">
+      <c r="X40" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="W40" s="8" t="s">
+      <c r="Y40" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="X40" s="4"/>
-      <c r="Y40" s="8">
+      <c r="Z40" s="4"/>
+      <c r="AA40" s="8">
         <v>11.780627000000001</v>
       </c>
-      <c r="Z40" s="8">
+      <c r="AB40" s="8">
         <v>15.103911999999999</v>
       </c>
-      <c r="AA40" s="8" t="s">
+      <c r="AC40" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="AB40" s="4"/>
-      <c r="AC40" s="4"/>
       <c r="AD40" s="4"/>
       <c r="AE40" s="4"/>
       <c r="AF40" s="4"/>
@@ -5467,8 +5703,10 @@
       <c r="AH40" s="4"/>
       <c r="AI40" s="4"/>
       <c r="AJ40" s="4"/>
+      <c r="AK40" s="4"/>
+      <c r="AL40" s="4"/>
     </row>
-    <row r="41" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:38" ht="44.25">
       <c r="A41" s="1">
         <v>46203</v>
       </c>
@@ -5496,58 +5734,58 @@
       <c r="I41" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="K41" s="3" t="s">
+      <c r="M41" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="L41" s="3" t="s">
+      <c r="N41" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M41" s="3"/>
-      <c r="N41" s="8" t="s">
+      <c r="O41" s="3"/>
+      <c r="P41" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="O41" s="8" t="s">
+      <c r="Q41" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="P41" s="8" t="s">
+      <c r="R41" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="Q41" s="8" t="s">
+      <c r="S41" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="R41" s="8" t="s">
+      <c r="T41" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S41" s="8" t="s">
+      <c r="U41" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="T41" s="8" t="s">
+      <c r="V41" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="U41" s="8" t="s">
+      <c r="W41" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="V41" s="8" t="s">
+      <c r="X41" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W41" s="8" t="s">
+      <c r="Y41" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="X41" s="4"/>
-      <c r="Y41" s="8">
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="8">
         <v>4.6665934</v>
       </c>
-      <c r="Z41" s="8">
+      <c r="AB41" s="8">
         <v>12.3730806</v>
       </c>
-      <c r="AA41" s="8" t="s">
+      <c r="AC41" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="AB41" s="4"/>
-      <c r="AC41" s="4"/>
       <c r="AD41" s="4"/>
       <c r="AE41" s="4"/>
       <c r="AF41" s="4"/>
@@ -5555,8 +5793,10 @@
       <c r="AH41" s="4"/>
       <c r="AI41" s="4"/>
       <c r="AJ41" s="4"/>
+      <c r="AK41" s="4"/>
+      <c r="AL41" s="4"/>
     </row>
-    <row r="42" spans="1:36" ht="59" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:38" ht="59">
       <c r="A42" s="1">
         <v>46203</v>
       </c>
@@ -5584,58 +5824,62 @@
       <c r="I42" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="J42" s="3">
+        <v>13291</v>
+      </c>
+      <c r="K42" s="3">
+        <v>107171</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L42" s="3" t="s">
+      <c r="M42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N42" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M42" s="3" t="s">
+      <c r="O42" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="N42" s="8" t="s">
+      <c r="P42" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="O42" s="8" t="s">
+      <c r="Q42" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="P42" s="8" t="s">
+      <c r="R42" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="Q42" s="8" t="s">
+      <c r="S42" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R42" s="8" t="s">
+      <c r="T42" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S42" s="8" t="s">
+      <c r="U42" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="T42" s="8" t="s">
+      <c r="V42" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="U42" s="8" t="s">
+      <c r="W42" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V42" s="8" t="s">
+      <c r="X42" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W42" s="8"/>
-      <c r="X42" s="4"/>
-      <c r="Y42" s="8">
+      <c r="Y42" s="8"/>
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="8">
         <v>6.0338079999999996</v>
       </c>
-      <c r="Z42" s="8">
+      <c r="AB42" s="8">
         <v>10.579231</v>
       </c>
-      <c r="AA42" s="8" t="s">
+      <c r="AC42" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="AB42" s="4"/>
-      <c r="AC42" s="4"/>
       <c r="AD42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AF42" s="4"/>
@@ -5643,8 +5887,10 @@
       <c r="AH42" s="4"/>
       <c r="AI42" s="4"/>
       <c r="AJ42" s="4"/>
+      <c r="AK42" s="4"/>
+      <c r="AL42" s="4"/>
     </row>
-    <row r="43" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:38" ht="29.5">
       <c r="A43" s="1">
         <v>46203</v>
       </c>
@@ -5672,60 +5918,64 @@
       <c r="I43" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="J43" s="3">
+        <v>14763</v>
+      </c>
+      <c r="K43" s="3">
+        <v>108711</v>
+      </c>
+      <c r="L43" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L43" s="3" t="s">
+      <c r="M43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N43" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M43" s="3" t="s">
+      <c r="O43" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="N43" s="8" t="s">
+      <c r="P43" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="O43" s="8" t="s">
+      <c r="Q43" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="P43" s="8" t="s">
+      <c r="R43" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="Q43" s="8" t="s">
+      <c r="S43" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R43" s="8" t="s">
+      <c r="T43" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S43" s="8" t="s">
+      <c r="U43" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="T43" s="8" t="s">
+      <c r="V43" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="U43" s="8" t="s">
+      <c r="W43" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V43" s="8" t="s">
+      <c r="X43" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="W43" s="8" t="s">
+      <c r="Y43" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="X43" s="4"/>
-      <c r="Y43" s="8">
+      <c r="Z43" s="4"/>
+      <c r="AA43" s="8">
         <v>7.2786650000000002</v>
       </c>
-      <c r="Z43" s="8">
+      <c r="AB43" s="8">
         <v>13.5462694</v>
       </c>
-      <c r="AA43" s="8" t="s">
+      <c r="AC43" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="AB43" s="4"/>
-      <c r="AC43" s="4"/>
       <c r="AD43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AF43" s="4"/>
@@ -5733,8 +5983,10 @@
       <c r="AH43" s="4"/>
       <c r="AI43" s="4"/>
       <c r="AJ43" s="4"/>
+      <c r="AK43" s="4"/>
+      <c r="AL43" s="4"/>
     </row>
-    <row r="44" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:38" ht="44.25">
       <c r="A44" s="1">
         <v>46203</v>
       </c>
@@ -5762,56 +6014,60 @@
       <c r="I44" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="J44" s="3">
+        <v>13351</v>
+      </c>
+      <c r="K44" s="3">
+        <v>107261</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L44" s="3" t="s">
+      <c r="M44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N44" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M44" s="3"/>
-      <c r="N44" s="8" t="s">
+      <c r="O44" s="3"/>
+      <c r="P44" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="O44" s="8" t="s">
+      <c r="Q44" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="P44" s="8" t="s">
+      <c r="R44" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q44" s="8" t="s">
+      <c r="S44" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R44" s="8" t="s">
+      <c r="T44" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S44" s="8" t="s">
+      <c r="U44" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="T44" s="8" t="s">
+      <c r="V44" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="U44" s="8" t="s">
+      <c r="W44" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V44" s="8" t="s">
+      <c r="X44" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W44" s="8"/>
-      <c r="X44" s="4"/>
-      <c r="Y44" s="8">
+      <c r="Y44" s="8"/>
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="8">
         <v>5.7961640000000001</v>
       </c>
-      <c r="Z44" s="8">
+      <c r="AB44" s="8">
         <v>10.162518</v>
       </c>
-      <c r="AA44" s="8" t="s">
+      <c r="AC44" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="AB44" s="4"/>
-      <c r="AC44" s="4"/>
       <c r="AD44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AF44" s="4"/>
@@ -5819,8 +6075,10 @@
       <c r="AH44" s="4"/>
       <c r="AI44" s="4"/>
       <c r="AJ44" s="4"/>
+      <c r="AK44" s="4"/>
+      <c r="AL44" s="4"/>
     </row>
-    <row r="45" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:38" ht="29.5">
       <c r="A45" s="1">
         <v>46203</v>
       </c>
@@ -5848,60 +6106,64 @@
       <c r="I45" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="J45" s="3">
+        <v>12817</v>
+      </c>
+      <c r="K45" s="3">
+        <v>105272</v>
+      </c>
+      <c r="L45" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L45" s="3" t="s">
+      <c r="M45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N45" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M45" s="3" t="s">
+      <c r="O45" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="N45" s="8" t="s">
+      <c r="P45" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="O45" s="8" t="s">
+      <c r="Q45" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="P45" s="8" t="s">
+      <c r="R45" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="Q45" s="8" t="s">
+      <c r="S45" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R45" s="8" t="s">
+      <c r="T45" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S45" s="8" t="s">
+      <c r="U45" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="T45" s="8" t="s">
+      <c r="V45" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="U45" s="8" t="s">
+      <c r="W45" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V45" s="8" t="s">
+      <c r="X45" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="W45" s="8" t="s">
+      <c r="Y45" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="X45" s="4"/>
-      <c r="Y45" s="8">
+      <c r="Z45" s="4"/>
+      <c r="AA45" s="8">
         <v>7.6627729999999996</v>
       </c>
-      <c r="Z45" s="8">
+      <c r="AB45" s="8">
         <v>12.329942000000001</v>
       </c>
-      <c r="AA45" s="8" t="s">
+      <c r="AC45" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="AB45" s="4"/>
-      <c r="AC45" s="4"/>
       <c r="AD45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AF45" s="4"/>
@@ -5909,8 +6171,10 @@
       <c r="AH45" s="4"/>
       <c r="AI45" s="4"/>
       <c r="AJ45" s="4"/>
+      <c r="AK45" s="4"/>
+      <c r="AL45" s="4"/>
     </row>
-    <row r="46" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:38" ht="44.25">
       <c r="A46" s="1">
         <v>46203</v>
       </c>
@@ -5938,60 +6202,64 @@
       <c r="I46" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="J46" s="3">
+        <v>11774</v>
+      </c>
+      <c r="K46" s="3">
+        <v>103079</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="M46" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="L46" s="3" t="s">
+      <c r="N46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M46" s="3" t="s">
+      <c r="O46" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="N46" s="8" t="s">
+      <c r="P46" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="O46" s="8" t="s">
+      <c r="Q46" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="P46" s="8" t="s">
+      <c r="R46" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="Q46" s="8" t="s">
+      <c r="S46" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R46" s="8" t="s">
+      <c r="T46" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S46" s="8" t="s">
+      <c r="U46" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="T46" s="8" t="s">
+      <c r="V46" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="U46" s="8" t="s">
+      <c r="W46" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V46" s="8" t="s">
+      <c r="X46" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W46" s="8" t="s">
+      <c r="Y46" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="X46" s="4"/>
-      <c r="Y46" s="8">
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="8">
         <v>7.2786650000000002</v>
       </c>
-      <c r="Z46" s="8">
+      <c r="AB46" s="8">
         <v>13.5462694</v>
       </c>
-      <c r="AA46" s="8" t="s">
+      <c r="AC46" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="AB46" s="4"/>
-      <c r="AC46" s="4"/>
       <c r="AD46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AF46" s="4"/>
@@ -5999,8 +6267,10 @@
       <c r="AH46" s="4"/>
       <c r="AI46" s="4"/>
       <c r="AJ46" s="4"/>
+      <c r="AK46" s="4"/>
+      <c r="AL46" s="4"/>
     </row>
-    <row r="47" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:38" ht="44.25">
       <c r="A47" s="1">
         <v>46203</v>
       </c>
@@ -6028,60 +6298,64 @@
       <c r="I47" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="J47" s="3">
+        <v>10587</v>
+      </c>
+      <c r="K47" s="3">
+        <v>100811</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L47" s="3" t="s">
+      <c r="M47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N47" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M47" s="3" t="s">
+      <c r="O47" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N47" s="8" t="s">
+      <c r="P47" s="8" t="s">
         <v>310</v>
-      </c>
-      <c r="O47" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P47" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="Q47" s="8" t="s">
         <v>33</v>
       </c>
       <c r="R47" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S47" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="T47" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S47" s="8" t="s">
+      <c r="U47" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="T47" s="8" t="s">
+      <c r="V47" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U47" s="8" t="s">
+      <c r="W47" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V47" s="8" t="s">
+      <c r="X47" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="W47" s="8" t="s">
+      <c r="Y47" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="X47" s="4"/>
-      <c r="Y47" s="8" t="s">
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="Z47" s="8" t="s">
+      <c r="AB47" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="AA47" s="8" t="s">
+      <c r="AC47" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="AB47" s="4"/>
-      <c r="AC47" s="4"/>
       <c r="AD47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AF47" s="4"/>
@@ -6089,8 +6363,10 @@
       <c r="AH47" s="4"/>
       <c r="AI47" s="4"/>
       <c r="AJ47" s="4"/>
+      <c r="AK47" s="4"/>
+      <c r="AL47" s="4"/>
     </row>
-    <row r="48" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:38" ht="29.5">
       <c r="A48" s="1">
         <v>46203</v>
       </c>
@@ -6118,60 +6394,64 @@
       <c r="I48" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="J48" s="3">
+        <v>10587</v>
+      </c>
+      <c r="K48" s="3">
+        <v>100811</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L48" s="3" t="s">
+      <c r="M48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N48" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M48" s="3" t="s">
+      <c r="O48" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N48" s="8" t="s">
+      <c r="P48" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="O48" s="8" t="s">
+      <c r="Q48" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="P48" s="8" t="s">
+      <c r="R48" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="Q48" s="8" t="s">
+      <c r="S48" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="R48" s="8" t="s">
+      <c r="T48" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S48" s="8" t="s">
+      <c r="U48" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="T48" s="8" t="s">
+      <c r="V48" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U48" s="8" t="s">
+      <c r="W48" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V48" s="8" t="s">
+      <c r="X48" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="W48" s="8" t="s">
+      <c r="Y48" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="X48" s="4"/>
-      <c r="Y48" s="8">
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="8">
         <v>3.9884092</v>
       </c>
-      <c r="Z48" s="8">
+      <c r="AB48" s="8">
         <v>13.171723699999999</v>
       </c>
-      <c r="AA48" s="8" t="s">
+      <c r="AC48" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="AB48" s="4"/>
-      <c r="AC48" s="4"/>
       <c r="AD48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AF48" s="4"/>
@@ -6179,8 +6459,10 @@
       <c r="AH48" s="4"/>
       <c r="AI48" s="4"/>
       <c r="AJ48" s="4"/>
+      <c r="AK48" s="4"/>
+      <c r="AL48" s="4"/>
     </row>
-    <row r="49" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:38" ht="29.5">
       <c r="A49" s="1">
         <v>46203</v>
       </c>
@@ -6208,60 +6490,64 @@
       <c r="I49" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="J49" s="3">
+        <v>10587</v>
+      </c>
+      <c r="K49" s="3">
+        <v>100811</v>
+      </c>
+      <c r="L49" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="M49" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="L49" s="3" t="s">
+      <c r="N49" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M49" s="3" t="s">
+      <c r="O49" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N49" s="8" t="s">
+      <c r="P49" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="O49" s="8" t="s">
+      <c r="Q49" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="P49" s="8" t="s">
+      <c r="R49" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="Q49" s="8" t="s">
+      <c r="S49" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="R49" s="8" t="s">
+      <c r="T49" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S49" s="8" t="s">
+      <c r="U49" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="T49" s="8" t="s">
+      <c r="V49" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U49" s="8" t="s">
+      <c r="W49" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V49" s="8" t="s">
+      <c r="X49" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="W49" s="8" t="s">
+      <c r="Y49" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="X49" s="4"/>
-      <c r="Y49" s="8">
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="8">
         <v>4.5496980999999996</v>
       </c>
-      <c r="Z49" s="8">
+      <c r="AB49" s="8">
         <v>13.7259359</v>
       </c>
-      <c r="AA49" s="8" t="s">
+      <c r="AC49" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="AB49" s="4"/>
-      <c r="AC49" s="4"/>
       <c r="AD49" s="4"/>
       <c r="AE49" s="4"/>
       <c r="AF49" s="4"/>
@@ -6269,8 +6555,10 @@
       <c r="AH49" s="4"/>
       <c r="AI49" s="4"/>
       <c r="AJ49" s="4"/>
+      <c r="AK49" s="4"/>
+      <c r="AL49" s="4"/>
     </row>
-    <row r="50" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:38" ht="44.25">
       <c r="A50" s="1">
         <v>46203</v>
       </c>
@@ -6298,60 +6586,64 @@
       <c r="I50" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="J50" s="3">
+        <v>10587</v>
+      </c>
+      <c r="K50" s="3">
+        <v>100811</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="K50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L50" s="3" t="s">
+      <c r="M50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N50" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M50" s="3" t="s">
+      <c r="O50" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N50" s="8" t="s">
+      <c r="P50" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="O50" s="8" t="s">
+      <c r="Q50" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P50" s="8" t="s">
+      <c r="R50" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="Q50" s="8" t="s">
+      <c r="S50" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="R50" s="8" t="s">
+      <c r="T50" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S50" s="8" t="s">
+      <c r="U50" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="T50" s="8" t="s">
+      <c r="V50" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U50" s="8" t="s">
+      <c r="W50" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V50" s="8" t="s">
+      <c r="X50" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="W50" s="8" t="s">
+      <c r="Y50" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="X50" s="4"/>
-      <c r="Y50" s="8" t="s">
+      <c r="Z50" s="4"/>
+      <c r="AA50" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="Z50" s="8" t="s">
+      <c r="AB50" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="AA50" s="8" t="s">
+      <c r="AC50" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="AB50" s="4"/>
-      <c r="AC50" s="4"/>
       <c r="AD50" s="4"/>
       <c r="AE50" s="4"/>
       <c r="AF50" s="4"/>
@@ -6359,8 +6651,10 @@
       <c r="AH50" s="4"/>
       <c r="AI50" s="4"/>
       <c r="AJ50" s="4"/>
+      <c r="AK50" s="4"/>
+      <c r="AL50" s="4"/>
     </row>
-    <row r="51" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:38" ht="44.25">
       <c r="A51" s="1">
         <v>46203</v>
       </c>
@@ -6388,60 +6682,64 @@
       <c r="I51" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="J51" s="3">
+        <v>10587</v>
+      </c>
+      <c r="K51" s="3">
+        <v>100811</v>
+      </c>
+      <c r="L51" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="K51" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L51" s="3" t="s">
+      <c r="M51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N51" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M51" s="3" t="s">
+      <c r="O51" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N51" s="8" t="s">
+      <c r="P51" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="O51" s="8" t="s">
+      <c r="Q51" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="P51" s="8" t="s">
+      <c r="R51" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="Q51" s="8" t="s">
+      <c r="S51" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="R51" s="8" t="s">
+      <c r="T51" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S51" s="8" t="s">
+      <c r="U51" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="T51" s="8" t="s">
+      <c r="V51" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U51" s="8" t="s">
+      <c r="W51" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V51" s="8" t="s">
+      <c r="X51" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="W51" s="8" t="s">
+      <c r="Y51" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="X51" s="4"/>
-      <c r="Y51" s="8">
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="8">
         <v>4.0210837000000001</v>
       </c>
-      <c r="Z51" s="8">
+      <c r="AB51" s="8">
         <v>14.1033954</v>
       </c>
-      <c r="AA51" s="8" t="s">
+      <c r="AC51" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="AB51" s="4"/>
-      <c r="AC51" s="4"/>
       <c r="AD51" s="4"/>
       <c r="AE51" s="4"/>
       <c r="AF51" s="4"/>
@@ -6449,8 +6747,10 @@
       <c r="AH51" s="4"/>
       <c r="AI51" s="4"/>
       <c r="AJ51" s="4"/>
+      <c r="AK51" s="4"/>
+      <c r="AL51" s="4"/>
     </row>
-    <row r="52" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:38" ht="29.5">
       <c r="A52" s="1">
         <v>46203</v>
       </c>
@@ -6478,60 +6778,64 @@
       <c r="I52" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="J52" s="3">
+        <v>10587</v>
+      </c>
+      <c r="K52" s="3">
+        <v>100811</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="M52" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="L52" s="3" t="s">
+      <c r="N52" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M52" s="3" t="s">
+      <c r="O52" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N52" s="8" t="s">
+      <c r="P52" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="O52" s="8" t="s">
+      <c r="Q52" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="P52" s="8" t="s">
+      <c r="R52" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="Q52" s="8" t="s">
+      <c r="S52" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="R52" s="8" t="s">
+      <c r="T52" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S52" s="8" t="s">
+      <c r="U52" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="T52" s="8" t="s">
+      <c r="V52" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U52" s="8" t="s">
+      <c r="W52" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V52" s="8" t="s">
+      <c r="X52" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="W52" s="8" t="s">
+      <c r="Y52" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="X52" s="4"/>
-      <c r="Y52" s="8">
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="8">
         <v>4.0210837000000001</v>
       </c>
-      <c r="Z52" s="8">
+      <c r="AB52" s="8">
         <v>14.1033954</v>
       </c>
-      <c r="AA52" s="8" t="s">
+      <c r="AC52" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="AB52" s="4"/>
-      <c r="AC52" s="4"/>
       <c r="AD52" s="4"/>
       <c r="AE52" s="4"/>
       <c r="AF52" s="4"/>
@@ -6539,8 +6843,10 @@
       <c r="AH52" s="4"/>
       <c r="AI52" s="4"/>
       <c r="AJ52" s="4"/>
+      <c r="AK52" s="4"/>
+      <c r="AL52" s="4"/>
     </row>
-    <row r="53" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:38" ht="29.5">
       <c r="A53" s="1">
         <v>46203</v>
       </c>
@@ -6568,60 +6874,64 @@
       <c r="I53" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="J53" s="3">
+        <v>10587</v>
+      </c>
+      <c r="K53" s="3">
+        <v>100811</v>
+      </c>
+      <c r="L53" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="K53" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L53" s="3" t="s">
+      <c r="M53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N53" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M53" s="3" t="s">
+      <c r="O53" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N53" s="8" t="s">
+      <c r="P53" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="O53" s="8" t="s">
+      <c r="Q53" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="P53" s="8" t="s">
+      <c r="R53" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="Q53" s="8" t="s">
+      <c r="S53" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="R53" s="8" t="s">
+      <c r="T53" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S53" s="8" t="s">
+      <c r="U53" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="T53" s="8" t="s">
+      <c r="V53" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U53" s="8" t="s">
+      <c r="W53" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V53" s="8" t="s">
+      <c r="X53" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="W53" s="8" t="s">
+      <c r="Y53" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="8">
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="8">
         <v>9.7269120000000004</v>
       </c>
-      <c r="Z53" s="8">
+      <c r="AB53" s="8">
         <v>13.997469799999999</v>
       </c>
-      <c r="AA53" s="8" t="s">
+      <c r="AC53" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="AB53" s="4"/>
-      <c r="AC53" s="4"/>
       <c r="AD53" s="4"/>
       <c r="AE53" s="4"/>
       <c r="AF53" s="4"/>
@@ -6629,8 +6939,10 @@
       <c r="AH53" s="4"/>
       <c r="AI53" s="4"/>
       <c r="AJ53" s="4"/>
+      <c r="AK53" s="4"/>
+      <c r="AL53" s="4"/>
     </row>
-    <row r="54" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:38" ht="29.5">
       <c r="A54" s="1">
         <v>46203</v>
       </c>
@@ -6658,60 +6970,64 @@
       <c r="I54" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="J54" s="3">
+        <v>10587</v>
+      </c>
+      <c r="K54" s="3">
+        <v>100811</v>
+      </c>
+      <c r="L54" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L54" s="3" t="s">
+      <c r="M54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M54" s="3" t="s">
+      <c r="O54" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N54" s="8" t="s">
+      <c r="P54" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="O54" s="8" t="s">
+      <c r="Q54" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="P54" s="8" t="s">
+      <c r="R54" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="Q54" s="8" t="s">
+      <c r="S54" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="R54" s="8" t="s">
+      <c r="T54" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S54" s="8" t="s">
+      <c r="U54" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="T54" s="8" t="s">
+      <c r="V54" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U54" s="8" t="s">
+      <c r="W54" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V54" s="8" t="s">
+      <c r="X54" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="W54" s="8" t="s">
+      <c r="Y54" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="X54" s="4"/>
-      <c r="Y54" s="8">
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="8">
         <v>2.6165007</v>
       </c>
-      <c r="Z54" s="8">
+      <c r="AB54" s="8">
         <v>15.3808624</v>
       </c>
-      <c r="AA54" s="8" t="s">
+      <c r="AC54" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="AB54" s="4"/>
-      <c r="AC54" s="4"/>
       <c r="AD54" s="4"/>
       <c r="AE54" s="4"/>
       <c r="AF54" s="4"/>
@@ -6719,8 +7035,10 @@
       <c r="AH54" s="4"/>
       <c r="AI54" s="4"/>
       <c r="AJ54" s="4"/>
+      <c r="AK54" s="4"/>
+      <c r="AL54" s="4"/>
     </row>
-    <row r="55" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:38" ht="44.25">
       <c r="A55" s="1">
         <v>46203</v>
       </c>
@@ -6748,60 +7066,64 @@
       <c r="I55" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="J55" s="3">
+        <v>10587</v>
+      </c>
+      <c r="K55" s="3">
+        <v>100811</v>
+      </c>
+      <c r="L55" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="K55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L55" s="3" t="s">
+      <c r="M55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N55" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M55" s="3" t="s">
+      <c r="O55" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N55" s="8" t="s">
+      <c r="P55" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="O55" s="8" t="s">
+      <c r="Q55" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="P55" s="8" t="s">
+      <c r="R55" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="Q55" s="8" t="s">
+      <c r="S55" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="R55" s="8" t="s">
+      <c r="T55" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S55" s="8" t="s">
+      <c r="U55" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="T55" s="8" t="s">
+      <c r="V55" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U55" s="8" t="s">
+      <c r="W55" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V55" s="8" t="s">
+      <c r="X55" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="W55" s="8" t="s">
+      <c r="Y55" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="X55" s="4"/>
-      <c r="Y55" s="8">
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="8">
         <v>2.6165007</v>
       </c>
-      <c r="Z55" s="8">
+      <c r="AB55" s="8">
         <v>15.3808624</v>
       </c>
-      <c r="AA55" s="8" t="s">
+      <c r="AC55" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="AB55" s="4"/>
-      <c r="AC55" s="4"/>
       <c r="AD55" s="4"/>
       <c r="AE55" s="4"/>
       <c r="AF55" s="4"/>
@@ -6809,8 +7131,10 @@
       <c r="AH55" s="4"/>
       <c r="AI55" s="4"/>
       <c r="AJ55" s="4"/>
+      <c r="AK55" s="4"/>
+      <c r="AL55" s="4"/>
     </row>
-    <row r="56" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:38" ht="29.5">
       <c r="A56" s="1">
         <v>46203</v>
       </c>
@@ -6838,60 +7162,64 @@
       <c r="I56" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="J56" s="3">
+        <v>10587</v>
+      </c>
+      <c r="K56" s="3">
+        <v>100811</v>
+      </c>
+      <c r="L56" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="K56" s="3" t="s">
+      <c r="M56" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="L56" s="3" t="s">
+      <c r="N56" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M56" s="3" t="s">
+      <c r="O56" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N56" s="8" t="s">
+      <c r="P56" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="O56" s="8" t="s">
+      <c r="Q56" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="P56" s="8" t="s">
+      <c r="R56" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="Q56" s="8" t="s">
+      <c r="S56" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="R56" s="8" t="s">
+      <c r="T56" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S56" s="8" t="s">
+      <c r="U56" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="T56" s="8" t="s">
+      <c r="V56" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U56" s="8" t="s">
+      <c r="W56" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V56" s="8" t="s">
+      <c r="X56" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="W56" s="8" t="s">
+      <c r="Y56" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="X56" s="4"/>
-      <c r="Y56" s="8">
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="8">
         <v>3.5152789000000002</v>
       </c>
-      <c r="Z56" s="8">
+      <c r="AB56" s="8">
         <v>15.0510331</v>
       </c>
-      <c r="AA56" s="8" t="s">
+      <c r="AC56" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="AB56" s="4"/>
-      <c r="AC56" s="4"/>
       <c r="AD56" s="4"/>
       <c r="AE56" s="4"/>
       <c r="AF56" s="4"/>
@@ -6899,8 +7227,10 @@
       <c r="AH56" s="4"/>
       <c r="AI56" s="4"/>
       <c r="AJ56" s="4"/>
+      <c r="AK56" s="4"/>
+      <c r="AL56" s="4"/>
     </row>
-    <row r="57" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:38" ht="29.5">
       <c r="A57" s="1">
         <v>46203</v>
       </c>
@@ -6928,58 +7258,62 @@
       <c r="I57" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="J57" s="3">
+        <v>14602</v>
+      </c>
+      <c r="K57" s="3">
+        <v>108460</v>
+      </c>
+      <c r="L57" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L57" s="3" t="s">
+      <c r="M57" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N57" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M57" s="3"/>
-      <c r="N57" s="8" t="s">
+      <c r="O57" s="3"/>
+      <c r="P57" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="O57" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P57" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="Q57" s="8" t="s">
         <v>33</v>
       </c>
       <c r="R57" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S57" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="T57" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S57" s="8" t="s">
+      <c r="U57" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="T57" s="8" t="s">
+      <c r="V57" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="U57" s="8" t="s">
+      <c r="W57" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V57" s="8" t="s">
+      <c r="X57" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W57" s="8" t="s">
+      <c r="Y57" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="X57" s="4"/>
-      <c r="Y57" s="8" t="s">
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="Z57" s="8" t="s">
+      <c r="AB57" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="AA57" s="8" t="s">
+      <c r="AC57" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="AB57" s="4"/>
-      <c r="AC57" s="4"/>
       <c r="AD57" s="4"/>
       <c r="AE57" s="4"/>
       <c r="AF57" s="4"/>
@@ -6987,8 +7321,10 @@
       <c r="AH57" s="4"/>
       <c r="AI57" s="4"/>
       <c r="AJ57" s="4"/>
+      <c r="AK57" s="4"/>
+      <c r="AL57" s="4"/>
     </row>
-    <row r="58" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:38" ht="29.5">
       <c r="A58" s="1">
         <v>46203</v>
       </c>
@@ -7016,58 +7352,62 @@
       <c r="I58" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="J58" s="3">
+        <v>14762</v>
+      </c>
+      <c r="K58" s="3">
+        <v>108710</v>
+      </c>
+      <c r="L58" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L58" s="3" t="s">
+      <c r="M58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N58" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="O58" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="N58" s="8" t="s">
+      <c r="P58" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="O58" s="8" t="s">
+      <c r="Q58" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="P58" s="8" t="s">
+      <c r="R58" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="Q58" s="8" t="s">
+      <c r="S58" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R58" s="8" t="s">
+      <c r="T58" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S58" s="8" t="s">
+      <c r="U58" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="T58" s="8" t="s">
+      <c r="V58" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="U58" s="8" t="s">
+      <c r="W58" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V58" s="8" t="s">
+      <c r="X58" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W58" s="8"/>
-      <c r="X58" s="4"/>
-      <c r="Y58" s="8">
+      <c r="Y58" s="8"/>
+      <c r="Z58" s="4"/>
+      <c r="AA58" s="8">
         <v>11.780627000000001</v>
       </c>
-      <c r="Z58" s="8">
+      <c r="AB58" s="8">
         <v>15.103911999999999</v>
       </c>
-      <c r="AA58" s="8" t="s">
+      <c r="AC58" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="AB58" s="4"/>
-      <c r="AC58" s="4"/>
       <c r="AD58" s="4"/>
       <c r="AE58" s="4"/>
       <c r="AF58" s="4"/>
@@ -7075,8 +7415,10 @@
       <c r="AH58" s="4"/>
       <c r="AI58" s="4"/>
       <c r="AJ58" s="4"/>
+      <c r="AK58" s="4"/>
+      <c r="AL58" s="4"/>
     </row>
-    <row r="59" spans="1:36" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:38" ht="73.75">
       <c r="A59" s="1">
         <v>46203</v>
       </c>
@@ -7104,58 +7446,62 @@
       <c r="I59" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="J59" s="3">
+        <v>11083</v>
+      </c>
+      <c r="K59" s="3">
+        <v>101859</v>
+      </c>
+      <c r="L59" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L59" s="3" t="s">
+      <c r="M59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N59" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M59" s="3" t="s">
+      <c r="O59" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="N59" s="8" t="s">
+      <c r="P59" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="O59" s="8" t="s">
+      <c r="Q59" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="P59" s="8" t="s">
+      <c r="R59" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q59" s="8" t="s">
+      <c r="S59" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R59" s="8" t="s">
+      <c r="T59" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S59" s="8" t="s">
+      <c r="U59" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="T59" s="8" t="s">
+      <c r="V59" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="U59" s="8" t="s">
+      <c r="W59" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V59" s="8" t="s">
+      <c r="X59" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W59" s="8"/>
-      <c r="X59" s="4"/>
-      <c r="Y59" s="8">
+      <c r="Y59" s="8"/>
+      <c r="Z59" s="4"/>
+      <c r="AA59" s="8">
         <v>5.9614117000000002</v>
       </c>
-      <c r="Z59" s="8">
+      <c r="AB59" s="8">
         <v>10.151650500000001</v>
       </c>
-      <c r="AA59" s="8" t="s">
+      <c r="AC59" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="AB59" s="4"/>
-      <c r="AC59" s="4"/>
       <c r="AD59" s="4"/>
       <c r="AE59" s="4"/>
       <c r="AF59" s="4"/>
@@ -7163,8 +7509,10 @@
       <c r="AH59" s="4"/>
       <c r="AI59" s="4"/>
       <c r="AJ59" s="4"/>
+      <c r="AK59" s="4"/>
+      <c r="AL59" s="4"/>
     </row>
-    <row r="60" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:38" ht="29.5">
       <c r="A60" s="1">
         <v>46203</v>
       </c>
@@ -7192,56 +7540,60 @@
       <c r="I60" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="J60" s="3" t="s">
+      <c r="J60" s="3">
+        <v>11558</v>
+      </c>
+      <c r="K60" s="3">
+        <v>102609</v>
+      </c>
+      <c r="L60" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L60" s="3" t="s">
+      <c r="M60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N60" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M60" s="3"/>
-      <c r="N60" s="8" t="s">
+      <c r="O60" s="3"/>
+      <c r="P60" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="O60" s="8" t="s">
+      <c r="Q60" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="P60" s="8" t="s">
+      <c r="R60" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="Q60" s="8" t="s">
+      <c r="S60" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="R60" s="8" t="s">
+      <c r="T60" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S60" s="8" t="s">
+      <c r="U60" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="T60" s="8" t="s">
+      <c r="V60" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="U60" s="8" t="s">
+      <c r="W60" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V60" s="8" t="s">
+      <c r="X60" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W60" s="8"/>
-      <c r="X60" s="4"/>
-      <c r="Y60" s="8">
+      <c r="Y60" s="8"/>
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="8">
         <v>8.3994900000000001</v>
       </c>
-      <c r="Z60" s="8">
+      <c r="AB60" s="8">
         <v>14.16816</v>
       </c>
-      <c r="AA60" s="8" t="s">
+      <c r="AC60" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="AB60" s="4"/>
-      <c r="AC60" s="4"/>
       <c r="AD60" s="4"/>
       <c r="AE60" s="4"/>
       <c r="AF60" s="4"/>
@@ -7249,8 +7601,10 @@
       <c r="AH60" s="4"/>
       <c r="AI60" s="4"/>
       <c r="AJ60" s="4"/>
+      <c r="AK60" s="4"/>
+      <c r="AL60" s="4"/>
     </row>
-    <row r="61" spans="1:36" ht="59" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:38" ht="59">
       <c r="A61" s="1">
         <v>46203</v>
       </c>
@@ -7278,60 +7632,64 @@
       <c r="I61" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="J61" s="3" t="s">
+      <c r="J61" s="3">
+        <v>15614</v>
+      </c>
+      <c r="K61" s="3">
+        <v>110241</v>
+      </c>
+      <c r="L61" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="K61" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L61" s="3" t="s">
+      <c r="M61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N61" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M61" s="3" t="s">
+      <c r="O61" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="N61" s="8" t="s">
+      <c r="P61" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="O61" s="8" t="s">
+      <c r="Q61" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="P61" s="8" t="s">
+      <c r="R61" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="Q61" s="8" t="s">
+      <c r="S61" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="R61" s="8" t="s">
+      <c r="T61" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S61" s="8" t="s">
+      <c r="U61" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="T61" s="8" t="s">
+      <c r="V61" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="U61" s="8" t="s">
+      <c r="W61" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V61" s="8" t="s">
+      <c r="X61" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W61" s="8" t="s">
+      <c r="Y61" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="X61" s="4"/>
-      <c r="Y61" s="8">
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="8">
         <v>10.116539700000001</v>
       </c>
-      <c r="Z61" s="8">
+      <c r="AB61" s="8">
         <v>14.9712175</v>
       </c>
-      <c r="AA61" s="8" t="s">
+      <c r="AC61" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="AB61" s="4"/>
-      <c r="AC61" s="4"/>
       <c r="AD61" s="4"/>
       <c r="AE61" s="4"/>
       <c r="AF61" s="4"/>
@@ -7339,8 +7697,10 @@
       <c r="AH61" s="4"/>
       <c r="AI61" s="4"/>
       <c r="AJ61" s="4"/>
+      <c r="AK61" s="4"/>
+      <c r="AL61" s="4"/>
     </row>
-    <row r="62" spans="1:36" ht="59" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:38" ht="59">
       <c r="A62" s="1">
         <v>46203</v>
       </c>
@@ -7368,58 +7728,62 @@
       <c r="I62" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="J62" s="3">
+        <v>11083</v>
+      </c>
+      <c r="K62" s="3">
+        <v>101859</v>
+      </c>
+      <c r="L62" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L62" s="3" t="s">
+      <c r="M62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M62" s="3" t="s">
+      <c r="O62" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="N62" s="8" t="s">
+      <c r="P62" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="O62" s="8" t="s">
+      <c r="Q62" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="P62" s="8" t="s">
+      <c r="R62" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q62" s="8" t="s">
+      <c r="S62" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R62" s="8" t="s">
+      <c r="T62" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S62" s="8" t="s">
+      <c r="U62" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="T62" s="8" t="s">
+      <c r="V62" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="U62" s="8" t="s">
+      <c r="W62" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V62" s="8" t="s">
+      <c r="X62" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W62" s="8"/>
-      <c r="X62" s="4"/>
-      <c r="Y62" s="8">
+      <c r="Y62" s="8"/>
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="8">
         <v>5.9614117000000002</v>
       </c>
-      <c r="Z62" s="8">
+      <c r="AB62" s="8">
         <v>10.151650500000001</v>
       </c>
-      <c r="AA62" s="8" t="s">
+      <c r="AC62" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="AB62" s="4"/>
-      <c r="AC62" s="4"/>
       <c r="AD62" s="4"/>
       <c r="AE62" s="4"/>
       <c r="AF62" s="4"/>
@@ -7427,8 +7791,10 @@
       <c r="AH62" s="4"/>
       <c r="AI62" s="4"/>
       <c r="AJ62" s="4"/>
+      <c r="AK62" s="4"/>
+      <c r="AL62" s="4"/>
     </row>
-    <row r="63" spans="1:36" ht="59" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:38" ht="59">
       <c r="A63" s="1">
         <v>46203</v>
       </c>
@@ -7456,58 +7822,62 @@
       <c r="I63" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="J63" s="3" t="s">
+      <c r="J63" s="3">
+        <v>11083</v>
+      </c>
+      <c r="K63" s="3">
+        <v>101859</v>
+      </c>
+      <c r="L63" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="K63" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L63" s="3" t="s">
+      <c r="M63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N63" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M63" s="3" t="s">
+      <c r="O63" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="N63" s="8" t="s">
+      <c r="P63" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="O63" s="8" t="s">
+      <c r="Q63" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="P63" s="8" t="s">
+      <c r="R63" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q63" s="8" t="s">
+      <c r="S63" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R63" s="8" t="s">
+      <c r="T63" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S63" s="8" t="s">
+      <c r="U63" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="T63" s="8" t="s">
+      <c r="V63" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="U63" s="8" t="s">
+      <c r="W63" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V63" s="8" t="s">
+      <c r="X63" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W63" s="8"/>
-      <c r="X63" s="4"/>
-      <c r="Y63" s="8">
+      <c r="Y63" s="8"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="8">
         <v>5.9614117000000002</v>
       </c>
-      <c r="Z63" s="8">
+      <c r="AB63" s="8">
         <v>10.151650500000001</v>
       </c>
-      <c r="AA63" s="8" t="s">
+      <c r="AC63" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="AB63" s="4"/>
-      <c r="AC63" s="4"/>
       <c r="AD63" s="4"/>
       <c r="AE63" s="4"/>
       <c r="AF63" s="4"/>
@@ -7515,8 +7885,10 @@
       <c r="AH63" s="4"/>
       <c r="AI63" s="4"/>
       <c r="AJ63" s="4"/>
+      <c r="AK63" s="4"/>
+      <c r="AL63" s="4"/>
     </row>
-    <row r="64" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:38" ht="44.25">
       <c r="A64" s="1">
         <v>46203</v>
       </c>
@@ -7544,60 +7916,60 @@
       <c r="I64" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="J64" s="3" t="s">
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K64" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L64" s="3" t="s">
+      <c r="M64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N64" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M64" s="3" t="s">
+      <c r="O64" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="N64" s="8" t="s">
+      <c r="P64" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="O64" s="8" t="s">
+      <c r="Q64" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="P64" s="8" t="s">
+      <c r="R64" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="Q64" s="8" t="s">
+      <c r="S64" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R64" s="8" t="s">
+      <c r="T64" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S64" s="8" t="s">
+      <c r="U64" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="T64" s="8" t="s">
+      <c r="V64" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="U64" s="8" t="s">
+      <c r="W64" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V64" s="8" t="s">
+      <c r="X64" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W64" s="8" t="s">
+      <c r="Y64" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="X64" s="4"/>
-      <c r="Y64" s="8">
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="8">
         <v>6.0845586999999997</v>
       </c>
-      <c r="Z64" s="8">
+      <c r="AB64" s="8">
         <v>10.638270800000001</v>
       </c>
-      <c r="AA64" s="8" t="s">
+      <c r="AC64" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="AB64" s="4"/>
-      <c r="AC64" s="4"/>
       <c r="AD64" s="4"/>
       <c r="AE64" s="4"/>
       <c r="AF64" s="4"/>
@@ -7605,8 +7977,10 @@
       <c r="AH64" s="4"/>
       <c r="AI64" s="4"/>
       <c r="AJ64" s="4"/>
+      <c r="AK64" s="4"/>
+      <c r="AL64" s="4"/>
     </row>
-    <row r="65" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:38" ht="29.5">
       <c r="A65" s="1">
         <v>46203</v>
       </c>
@@ -7634,60 +8008,64 @@
       <c r="I65" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="J65" s="3">
+        <v>15397</v>
+      </c>
+      <c r="K65" s="3">
+        <v>110825</v>
+      </c>
+      <c r="L65" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="K65" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L65" s="3" t="s">
+      <c r="M65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N65" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M65" s="3" t="s">
+      <c r="O65" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="N65" s="8" t="s">
+      <c r="P65" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="O65" s="8" t="s">
+      <c r="Q65" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="P65" s="8" t="s">
+      <c r="R65" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="Q65" s="8" t="s">
+      <c r="S65" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R65" s="8" t="s">
+      <c r="T65" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S65" s="8" t="s">
+      <c r="U65" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="T65" s="8" t="s">
+      <c r="V65" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="U65" s="8" t="s">
+      <c r="W65" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V65" s="8" t="s">
+      <c r="X65" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W65" s="8" t="s">
+      <c r="Y65" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="X65" s="4"/>
-      <c r="Y65" s="8">
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="8">
         <v>5.9462650000000004</v>
       </c>
-      <c r="Z65" s="8">
+      <c r="AB65" s="8">
         <v>9.6904461000000008</v>
       </c>
-      <c r="AA65" s="8" t="s">
+      <c r="AC65" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="AB65" s="4"/>
-      <c r="AC65" s="4"/>
       <c r="AD65" s="4"/>
       <c r="AE65" s="4"/>
       <c r="AF65" s="4"/>
@@ -7695,8 +8073,10 @@
       <c r="AH65" s="4"/>
       <c r="AI65" s="4"/>
       <c r="AJ65" s="4"/>
+      <c r="AK65" s="4"/>
+      <c r="AL65" s="4"/>
     </row>
-    <row r="66" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:38" ht="29.5">
       <c r="A66" s="1">
         <v>46203</v>
       </c>
@@ -7724,58 +8104,62 @@
       <c r="I66" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="J66" s="3">
+        <v>16111</v>
+      </c>
+      <c r="K66">
+        <v>111192</v>
+      </c>
+      <c r="L66" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L66" s="3" t="s">
+      <c r="M66" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N66" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M66" s="3" t="s">
+      <c r="O66" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="N66" s="8" t="s">
+      <c r="P66" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="O66" s="8" t="s">
+      <c r="Q66" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="P66" s="8" t="s">
+      <c r="R66" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="Q66" s="8" t="s">
+      <c r="S66" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R66" s="8" t="s">
+      <c r="T66" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S66" s="8" t="s">
+      <c r="U66" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="T66" s="8" t="s">
+      <c r="V66" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="U66" s="8" t="s">
+      <c r="W66" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V66" s="8" t="s">
+      <c r="X66" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W66" s="8"/>
-      <c r="X66" s="4"/>
-      <c r="Y66" s="8">
+      <c r="Y66" s="8"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="8">
         <v>4.8673555000000004</v>
       </c>
-      <c r="Z66" s="8">
+      <c r="AB66" s="8">
         <v>11.156444</v>
       </c>
-      <c r="AA66" s="8" t="s">
+      <c r="AC66" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="AB66" s="4"/>
-      <c r="AC66" s="4"/>
       <c r="AD66" s="4"/>
       <c r="AE66" s="4"/>
       <c r="AF66" s="4"/>
@@ -7783,8 +8167,10 @@
       <c r="AH66" s="4"/>
       <c r="AI66" s="4"/>
       <c r="AJ66" s="4"/>
+      <c r="AK66" s="4"/>
+      <c r="AL66" s="4"/>
     </row>
-    <row r="67" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:38" ht="44.25">
       <c r="A67" s="7">
         <v>46203</v>
       </c>
@@ -7810,60 +8196,64 @@
       <c r="I67" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="J67" s="4">
+        <v>10587</v>
+      </c>
+      <c r="K67" s="4">
+        <v>100811</v>
+      </c>
+      <c r="L67" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="K67" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L67" s="3" t="s">
+      <c r="M67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N67" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M67" s="3" t="s">
+      <c r="O67" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N67" s="8" t="s">
+      <c r="P67" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="O67" s="8" t="s">
+      <c r="Q67" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="P67" s="8" t="s">
+      <c r="R67" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="Q67" s="8" t="s">
+      <c r="S67" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="R67" s="8" t="s">
+      <c r="T67" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S67" s="8" t="s">
+      <c r="U67" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="T67" s="8" t="s">
+      <c r="V67" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U67" s="8" t="s">
+      <c r="W67" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V67" s="8" t="s">
+      <c r="X67" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="W67" s="8" t="s">
+      <c r="Y67" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="X67" s="4"/>
-      <c r="Y67" s="8">
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="8">
         <v>3.0779049000000001</v>
       </c>
-      <c r="Z67" s="8">
+      <c r="AB67" s="8">
         <v>10.4112806</v>
       </c>
-      <c r="AA67" s="8" t="s">
+      <c r="AC67" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="AB67" s="4"/>
-      <c r="AC67" s="4"/>
       <c r="AD67" s="4"/>
       <c r="AE67" s="4"/>
       <c r="AF67" s="4"/>
@@ -7871,8 +8261,10 @@
       <c r="AH67" s="4"/>
       <c r="AI67" s="4"/>
       <c r="AJ67" s="4"/>
+      <c r="AK67" s="4"/>
+      <c r="AL67" s="4"/>
     </row>
-    <row r="68" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:38" ht="44.25">
       <c r="A68" s="7">
         <v>46203</v>
       </c>
@@ -7898,60 +8290,64 @@
       <c r="I68" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="J68" s="3" t="s">
+      <c r="J68" s="4">
+        <v>10587</v>
+      </c>
+      <c r="K68" s="4">
+        <v>100811</v>
+      </c>
+      <c r="L68" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="K68" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L68" s="3" t="s">
+      <c r="M68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N68" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M68" s="3" t="s">
+      <c r="O68" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N68" s="8" t="s">
+      <c r="P68" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="O68" s="8" t="s">
+      <c r="Q68" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="P68" s="8" t="s">
+      <c r="R68" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="Q68" s="8" t="s">
+      <c r="S68" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="R68" s="8" t="s">
+      <c r="T68" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S68" s="8" t="s">
+      <c r="U68" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="T68" s="8" t="s">
+      <c r="V68" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U68" s="8" t="s">
+      <c r="W68" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V68" s="8" t="s">
+      <c r="X68" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="W68" s="8" t="s">
+      <c r="Y68" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="X68" s="4"/>
-      <c r="Y68" s="8">
+      <c r="Z68" s="4"/>
+      <c r="AA68" s="8">
         <v>3.2340753000000002</v>
       </c>
-      <c r="Z68" s="8">
+      <c r="AB68" s="8">
         <v>10.727964099999999</v>
       </c>
-      <c r="AA68" s="8" t="s">
+      <c r="AC68" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="AB68" s="4"/>
-      <c r="AC68" s="4"/>
       <c r="AD68" s="4"/>
       <c r="AE68" s="4"/>
       <c r="AF68" s="4"/>
@@ -7959,8 +8355,10 @@
       <c r="AH68" s="4"/>
       <c r="AI68" s="4"/>
       <c r="AJ68" s="4"/>
+      <c r="AK68" s="4"/>
+      <c r="AL68" s="4"/>
     </row>
-    <row r="69" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:38" ht="44.25">
       <c r="A69" s="7">
         <v>46203</v>
       </c>
@@ -7986,60 +8384,64 @@
       <c r="I69" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="J69" s="3" t="s">
+      <c r="J69" s="4">
+        <v>10587</v>
+      </c>
+      <c r="K69" s="4">
+        <v>100811</v>
+      </c>
+      <c r="L69" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="K69" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L69" s="3" t="s">
+      <c r="M69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N69" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M69" s="3" t="s">
+      <c r="O69" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N69" s="8" t="s">
+      <c r="P69" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="O69" s="8" t="s">
+      <c r="Q69" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="P69" s="8" t="s">
+      <c r="R69" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="Q69" s="8" t="s">
+      <c r="S69" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="R69" s="8" t="s">
+      <c r="T69" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S69" s="8" t="s">
+      <c r="U69" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="T69" s="8" t="s">
+      <c r="V69" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="U69" s="8" t="s">
+      <c r="W69" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V69" s="8" t="s">
+      <c r="X69" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="W69" s="8" t="s">
+      <c r="Y69" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="X69" s="4"/>
-      <c r="Y69" s="8">
+      <c r="Z69" s="4"/>
+      <c r="AA69" s="8">
         <v>2.9434098</v>
       </c>
-      <c r="Z69" s="8">
+      <c r="AB69" s="8">
         <v>9.9126989000000005</v>
       </c>
-      <c r="AA69" s="8" t="s">
+      <c r="AC69" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="AB69" s="4"/>
-      <c r="AC69" s="4"/>
       <c r="AD69" s="4"/>
       <c r="AE69" s="4"/>
       <c r="AF69" s="4"/>
@@ -8047,8 +8449,10 @@
       <c r="AH69" s="4"/>
       <c r="AI69" s="4"/>
       <c r="AJ69" s="4"/>
+      <c r="AK69" s="4"/>
+      <c r="AL69" s="4"/>
     </row>
-    <row r="70" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:38" ht="44.25">
       <c r="A70" s="7">
         <v>46203</v>
       </c>
@@ -8074,60 +8478,64 @@
       <c r="I70" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="J70" s="4" t="s">
+      <c r="J70" s="4">
+        <v>10618</v>
+      </c>
+      <c r="K70" s="4">
+        <v>100926</v>
+      </c>
+      <c r="L70" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="K70" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L70" s="3" t="s">
+      <c r="M70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N70" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M70" s="4" t="s">
+      <c r="O70" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="N70" s="8" t="s">
+      <c r="P70" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="O70" s="8" t="s">
+      <c r="Q70" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="P70" s="8" t="s">
+      <c r="R70" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q70" s="8" t="s">
+      <c r="S70" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R70" s="8" t="s">
+      <c r="T70" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S70" s="8" t="s">
+      <c r="U70" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="T70" s="8" t="s">
+      <c r="V70" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="U70" s="8" t="s">
+      <c r="W70" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V70" s="8">
+      <c r="X70" s="8">
         <v>2026</v>
       </c>
-      <c r="W70" s="8" t="s">
+      <c r="Y70" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="X70" s="4"/>
-      <c r="Y70" s="8">
+      <c r="Z70" s="4"/>
+      <c r="AA70" s="8">
         <v>6.0384487</v>
       </c>
-      <c r="Z70" s="8">
+      <c r="AB70" s="8">
         <v>10.2907876</v>
       </c>
-      <c r="AA70" s="8" t="s">
+      <c r="AC70" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="AB70" s="4"/>
-      <c r="AC70" s="4"/>
       <c r="AD70" s="4"/>
       <c r="AE70" s="4"/>
       <c r="AF70" s="4"/>
@@ -8135,8 +8543,10 @@
       <c r="AH70" s="4"/>
       <c r="AI70" s="4"/>
       <c r="AJ70" s="4"/>
+      <c r="AK70" s="4"/>
+      <c r="AL70" s="4"/>
     </row>
-    <row r="71" spans="1:36" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:38" ht="73.75">
       <c r="A71" s="7">
         <v>46203</v>
       </c>
@@ -8162,60 +8572,64 @@
       <c r="I71" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="J71" s="4">
+        <v>11460</v>
+      </c>
+      <c r="K71" s="4">
+        <v>102351</v>
+      </c>
+      <c r="L71" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="K71" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L71" s="3" t="s">
+      <c r="M71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N71" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M71" s="3" t="s">
+      <c r="O71" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="N71" s="8" t="s">
+      <c r="P71" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="O71" s="8" t="s">
+      <c r="Q71" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P71" s="8" t="s">
+      <c r="R71" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="Q71" s="8" t="s">
+      <c r="S71" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="R71" s="8" t="s">
+      <c r="T71" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S71" s="8" t="s">
+      <c r="U71" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="T71" s="8" t="s">
+      <c r="V71" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="U71" s="8" t="s">
+      <c r="W71" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V71" s="8">
+      <c r="X71" s="8">
         <v>2026</v>
       </c>
-      <c r="W71" s="8" t="s">
+      <c r="Y71" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="X71" s="4"/>
-      <c r="Y71" s="8" t="s">
+      <c r="Z71" s="4"/>
+      <c r="AA71" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="Z71" s="8" t="s">
+      <c r="AB71" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="AA71" s="8" t="s">
+      <c r="AC71" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="AB71" s="4"/>
-      <c r="AC71" s="4"/>
       <c r="AD71" s="4"/>
       <c r="AE71" s="4"/>
       <c r="AF71" s="4"/>
@@ -8223,8 +8637,10 @@
       <c r="AH71" s="4"/>
       <c r="AI71" s="4"/>
       <c r="AJ71" s="4"/>
+      <c r="AK71" s="4"/>
+      <c r="AL71" s="4"/>
     </row>
-    <row r="72" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:38" ht="44.25">
       <c r="A72" s="7">
         <v>46203</v>
       </c>
@@ -8250,60 +8666,60 @@
       <c r="I72" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="J72" s="4" t="s">
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L72" s="3" t="s">
+      <c r="M72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N72" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M72" s="4" t="s">
+      <c r="O72" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="N72" s="8" t="s">
+      <c r="P72" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="O72" s="8" t="s">
+      <c r="Q72" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="P72" s="8" t="s">
+      <c r="R72" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="Q72" s="8" t="s">
+      <c r="S72" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R72" s="8" t="s">
+      <c r="T72" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S72" s="8" t="s">
+      <c r="U72" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="T72" s="8" t="s">
+      <c r="V72" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="U72" s="8" t="s">
+      <c r="W72" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V72" s="8">
+      <c r="X72" s="8">
         <v>2026</v>
       </c>
-      <c r="W72" s="8" t="s">
+      <c r="Y72" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="X72" s="4"/>
-      <c r="Y72" s="8">
+      <c r="Z72" s="4"/>
+      <c r="AA72" s="8">
         <v>4.8673555000000004</v>
       </c>
-      <c r="Z72" s="8">
+      <c r="AB72" s="8">
         <v>11.156444</v>
       </c>
-      <c r="AA72" s="8" t="s">
+      <c r="AC72" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="AB72" s="4"/>
-      <c r="AC72" s="4"/>
       <c r="AD72" s="4"/>
       <c r="AE72" s="4"/>
       <c r="AF72" s="4"/>
@@ -8311,8 +8727,10 @@
       <c r="AH72" s="4"/>
       <c r="AI72" s="4"/>
       <c r="AJ72" s="4"/>
+      <c r="AK72" s="4"/>
+      <c r="AL72" s="4"/>
     </row>
-    <row r="73" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:38" ht="29.5">
       <c r="A73" s="7">
         <v>46203</v>
       </c>
@@ -8338,60 +8756,64 @@
       <c r="I73" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="J73" s="4" t="s">
+      <c r="J73" s="4">
+        <v>16111</v>
+      </c>
+      <c r="K73">
+        <v>111192</v>
+      </c>
+      <c r="L73" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="K73" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L73" s="3" t="s">
+      <c r="M73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N73" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M73" s="4" t="s">
+      <c r="O73" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="N73" s="8" t="s">
+      <c r="P73" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="O73" s="8" t="s">
+      <c r="Q73" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="P73" s="8" t="s">
+      <c r="R73" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="Q73" s="8" t="s">
+      <c r="S73" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="R73" s="8" t="s">
+      <c r="T73" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S73" s="8" t="s">
+      <c r="U73" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="T73" s="8" t="s">
+      <c r="V73" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="U73" s="8" t="s">
+      <c r="W73" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V73" s="8">
+      <c r="X73" s="8">
         <v>2026</v>
       </c>
-      <c r="W73" s="8" t="s">
+      <c r="Y73" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="X73" s="4"/>
-      <c r="Y73" s="8">
+      <c r="Z73" s="4"/>
+      <c r="AA73" s="8">
         <v>4.8673555000000004</v>
       </c>
-      <c r="Z73" s="8">
+      <c r="AB73" s="8">
         <v>11.156444</v>
       </c>
-      <c r="AA73" s="8" t="s">
+      <c r="AC73" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="AB73" s="4"/>
-      <c r="AC73" s="4"/>
       <c r="AD73" s="4"/>
       <c r="AE73" s="4"/>
       <c r="AF73" s="4"/>
@@ -8399,8 +8821,10 @@
       <c r="AH73" s="4"/>
       <c r="AI73" s="4"/>
       <c r="AJ73" s="4"/>
+      <c r="AK73" s="4"/>
+      <c r="AL73" s="4"/>
     </row>
-    <row r="74" spans="1:36" ht="88.5" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:38" ht="73.75">
       <c r="A74" s="7">
         <v>46203</v>
       </c>
@@ -8426,58 +8850,58 @@
       <c r="I74" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="J74" s="4" t="s">
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="K74" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L74" s="3" t="s">
+      <c r="M74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N74" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M74" s="4" t="s">
+      <c r="O74" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="N74" s="8" t="s">
+      <c r="P74" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="O74" s="8" t="s">
+      <c r="Q74" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P74" s="8" t="s">
+      <c r="R74" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="Q74" s="8" t="s">
+      <c r="S74" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="R74" s="8" t="s">
+      <c r="T74" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S74" s="8" t="s">
+      <c r="U74" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="T74" s="8" t="s">
+      <c r="V74" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="U74" s="8" t="s">
+      <c r="W74" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V74" s="8">
+      <c r="X74" s="8">
         <v>2026</v>
       </c>
-      <c r="W74" s="8"/>
-      <c r="X74" s="4"/>
-      <c r="Y74" s="8" t="s">
+      <c r="Y74" s="8"/>
+      <c r="Z74" s="4"/>
+      <c r="AA74" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="Z74" s="8" t="s">
+      <c r="AB74" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="AA74" s="8" t="s">
+      <c r="AC74" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="AB74" s="4"/>
-      <c r="AC74" s="4"/>
       <c r="AD74" s="4"/>
       <c r="AE74" s="4"/>
       <c r="AF74" s="4"/>
@@ -8485,8 +8909,10 @@
       <c r="AH74" s="4"/>
       <c r="AI74" s="4"/>
       <c r="AJ74" s="4"/>
+      <c r="AK74" s="4"/>
+      <c r="AL74" s="4"/>
     </row>
-    <row r="75" spans="1:36" ht="88.5" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:38" ht="88.5">
       <c r="A75" s="7">
         <v>46203</v>
       </c>
@@ -8512,58 +8938,58 @@
       <c r="I75" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="J75" s="4" t="s">
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="K75" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L75" s="3" t="s">
+      <c r="M75" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N75" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M75" s="4" t="s">
+      <c r="O75" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="N75" s="8" t="s">
+      <c r="P75" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="O75" s="8" t="s">
+      <c r="Q75" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P75" s="8" t="s">
+      <c r="R75" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="Q75" s="8" t="s">
+      <c r="S75" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="R75" s="8" t="s">
+      <c r="T75" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S75" s="8" t="s">
+      <c r="U75" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="T75" s="8" t="s">
+      <c r="V75" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="U75" s="8" t="s">
+      <c r="W75" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V75" s="8">
+      <c r="X75" s="8">
         <v>2026</v>
       </c>
-      <c r="W75" s="8"/>
-      <c r="X75" s="4"/>
-      <c r="Y75" s="8" t="s">
+      <c r="Y75" s="8"/>
+      <c r="Z75" s="4"/>
+      <c r="AA75" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="Z75" s="8" t="s">
+      <c r="AB75" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="AA75" s="8" t="s">
+      <c r="AC75" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="AB75" s="4"/>
-      <c r="AC75" s="4"/>
       <c r="AD75" s="4"/>
       <c r="AE75" s="4"/>
       <c r="AF75" s="4"/>
@@ -8571,8 +8997,10 @@
       <c r="AH75" s="4"/>
       <c r="AI75" s="4"/>
       <c r="AJ75" s="4"/>
+      <c r="AK75" s="4"/>
+      <c r="AL75" s="4"/>
     </row>
-    <row r="76" spans="1:36" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:38" ht="29.5">
       <c r="A76" s="7">
         <v>46203</v>
       </c>
@@ -8598,58 +9026,58 @@
       <c r="I76" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="J76" s="4" t="s">
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L76" s="3" t="s">
+      <c r="M76" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N76" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M76" s="4" t="s">
+      <c r="O76" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="N76" s="8" t="s">
+      <c r="P76" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="O76" s="8" t="s">
+      <c r="Q76" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="P76" s="8" t="s">
+      <c r="R76" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="Q76" s="8" t="s">
+      <c r="S76" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R76" s="8" t="s">
+      <c r="T76" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S76" s="8" t="s">
+      <c r="U76" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="T76" s="8" t="s">
+      <c r="V76" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="U76" s="8" t="s">
+      <c r="W76" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V76" s="8">
+      <c r="X76" s="8">
         <v>2026</v>
       </c>
-      <c r="W76" s="8"/>
-      <c r="X76" s="4"/>
-      <c r="Y76" s="8">
+      <c r="Y76" s="8"/>
+      <c r="Z76" s="4"/>
+      <c r="AA76" s="8">
         <v>6.0845586999999997</v>
       </c>
-      <c r="Z76" s="8">
+      <c r="AB76" s="8">
         <v>10.638270800000001</v>
       </c>
-      <c r="AA76" s="8" t="s">
+      <c r="AC76" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="AB76" s="4"/>
-      <c r="AC76" s="4"/>
       <c r="AD76" s="4"/>
       <c r="AE76" s="4"/>
       <c r="AF76" s="4"/>
@@ -8657,8 +9085,10 @@
       <c r="AH76" s="4"/>
       <c r="AI76" s="4"/>
       <c r="AJ76" s="4"/>
+      <c r="AK76" s="4"/>
+      <c r="AL76" s="4"/>
     </row>
-    <row r="77" spans="1:36" ht="73.75" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:38" ht="73.75">
       <c r="A77" s="7">
         <v>46203</v>
       </c>
@@ -8684,58 +9114,58 @@
       <c r="I77" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="J77" s="4" t="s">
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="K77" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L77" s="3" t="s">
+      <c r="M77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N77" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M77" s="4" t="s">
+      <c r="O77" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="N77" s="8" t="s">
+      <c r="P77" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="O77" s="8" t="s">
+      <c r="Q77" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="P77" s="8" t="s">
+      <c r="R77" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q77" s="8" t="s">
+      <c r="S77" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R77" s="8" t="s">
+      <c r="T77" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S77" s="8" t="s">
+      <c r="U77" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="T77" s="8" t="s">
+      <c r="V77" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="U77" s="8" t="s">
+      <c r="W77" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V77" s="8">
+      <c r="X77" s="8">
         <v>2026</v>
       </c>
-      <c r="W77" s="8"/>
-      <c r="X77" s="4"/>
-      <c r="Y77" s="8">
+      <c r="Y77" s="8"/>
+      <c r="Z77" s="4"/>
+      <c r="AA77" s="8">
         <v>5.9544699999999997</v>
       </c>
-      <c r="Z77" s="8">
+      <c r="AB77" s="8">
         <v>10.163320000000001</v>
       </c>
-      <c r="AA77" s="8" t="s">
+      <c r="AC77" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="AB77" s="4"/>
-      <c r="AC77" s="4"/>
       <c r="AD77" s="4"/>
       <c r="AE77" s="4"/>
       <c r="AF77" s="4"/>
@@ -8743,8 +9173,10 @@
       <c r="AH77" s="4"/>
       <c r="AI77" s="4"/>
       <c r="AJ77" s="4"/>
+      <c r="AK77" s="4"/>
+      <c r="AL77" s="4"/>
     </row>
-    <row r="78" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:38" ht="44.25">
       <c r="A78" s="7">
         <v>46203</v>
       </c>
@@ -8770,58 +9202,58 @@
       <c r="I78" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="J78" s="4" t="s">
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="K78" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L78" s="3" t="s">
+      <c r="M78" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N78" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M78" s="4" t="s">
+      <c r="O78" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="N78" s="8" t="s">
+      <c r="P78" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="O78" s="8" t="s">
+      <c r="Q78" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="P78" s="8" t="s">
+      <c r="R78" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q78" s="8" t="s">
+      <c r="S78" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R78" s="8" t="s">
+      <c r="T78" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S78" s="8" t="s">
+      <c r="U78" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="T78" s="8" t="s">
+      <c r="V78" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="U78" s="8" t="s">
+      <c r="W78" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V78" s="8">
+      <c r="X78" s="8">
         <v>2026</v>
       </c>
-      <c r="W78" s="8"/>
-      <c r="X78" s="4"/>
-      <c r="Y78" s="8">
+      <c r="Y78" s="8"/>
+      <c r="Z78" s="4"/>
+      <c r="AA78" s="8">
         <v>5.9544699999999997</v>
       </c>
-      <c r="Z78" s="8">
+      <c r="AB78" s="8">
         <v>10.163320000000001</v>
       </c>
-      <c r="AA78" s="8" t="s">
+      <c r="AC78" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="AB78" s="4"/>
-      <c r="AC78" s="4"/>
       <c r="AD78" s="4"/>
       <c r="AE78" s="4"/>
       <c r="AF78" s="4"/>
@@ -8829,8 +9261,10 @@
       <c r="AH78" s="4"/>
       <c r="AI78" s="4"/>
       <c r="AJ78" s="4"/>
+      <c r="AK78" s="4"/>
+      <c r="AL78" s="4"/>
     </row>
-    <row r="79" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:38" ht="44.25">
       <c r="A79" s="7">
         <v>46203</v>
       </c>
@@ -8856,58 +9290,58 @@
       <c r="I79" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="J79" s="4" t="s">
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="K79" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L79" s="3" t="s">
+      <c r="M79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N79" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M79" s="4" t="s">
+      <c r="O79" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="N79" s="8" t="s">
+      <c r="P79" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="O79" s="8" t="s">
+      <c r="Q79" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="P79" s="8" t="s">
+      <c r="R79" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q79" s="8" t="s">
+      <c r="S79" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R79" s="8" t="s">
+      <c r="T79" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S79" s="8" t="s">
+      <c r="U79" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="T79" s="8" t="s">
+      <c r="V79" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="U79" s="8" t="s">
+      <c r="W79" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="V79" s="8">
+      <c r="X79" s="8">
         <v>2026</v>
       </c>
-      <c r="W79" s="8"/>
-      <c r="X79" s="4"/>
-      <c r="Y79" s="8">
+      <c r="Y79" s="8"/>
+      <c r="Z79" s="4"/>
+      <c r="AA79" s="8">
         <v>5.9544699999999997</v>
       </c>
-      <c r="Z79" s="8">
+      <c r="AB79" s="8">
         <v>10.163320000000001</v>
       </c>
-      <c r="AA79" s="8" t="s">
+      <c r="AC79" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="AB79" s="4"/>
-      <c r="AC79" s="4"/>
       <c r="AD79" s="4"/>
       <c r="AE79" s="4"/>
       <c r="AF79" s="4"/>
@@ -8915,8 +9349,10 @@
       <c r="AH79" s="4"/>
       <c r="AI79" s="4"/>
       <c r="AJ79" s="4"/>
+      <c r="AK79" s="4"/>
+      <c r="AL79" s="4"/>
     </row>
-    <row r="80" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:38" ht="44.25">
       <c r="A80" s="7">
         <v>46203</v>
       </c>
@@ -8942,58 +9378,58 @@
       <c r="I80" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="J80" s="4" t="s">
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="K80" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L80" s="3" t="s">
+      <c r="M80" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N80" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M80" s="4" t="s">
+      <c r="O80" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="N80" s="8" t="s">
+      <c r="P80" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="O80" s="8" t="s">
+      <c r="Q80" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="P80" s="8" t="s">
+      <c r="R80" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q80" s="8" t="s">
+      <c r="S80" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R80" s="8" t="s">
+      <c r="T80" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S80" s="8" t="s">
+      <c r="U80" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="T80" s="8" t="s">
+      <c r="V80" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="U80" s="8" t="s">
+      <c r="W80" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="V80" s="8">
+      <c r="X80" s="8">
         <v>2026</v>
       </c>
-      <c r="W80" s="8"/>
-      <c r="X80" s="4"/>
-      <c r="Y80" s="8">
+      <c r="Y80" s="8"/>
+      <c r="Z80" s="4"/>
+      <c r="AA80" s="8">
         <v>5.9544699999999997</v>
       </c>
-      <c r="Z80" s="8">
+      <c r="AB80" s="8">
         <v>10.163320000000001</v>
       </c>
-      <c r="AA80" s="8" t="s">
+      <c r="AC80" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="AB80" s="4"/>
-      <c r="AC80" s="4"/>
       <c r="AD80" s="4"/>
       <c r="AE80" s="4"/>
       <c r="AF80" s="4"/>
@@ -9001,8 +9437,10 @@
       <c r="AH80" s="4"/>
       <c r="AI80" s="4"/>
       <c r="AJ80" s="4"/>
+      <c r="AK80" s="4"/>
+      <c r="AL80" s="4"/>
     </row>
-    <row r="81" spans="1:36" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:38" ht="44.25">
       <c r="A81" s="7">
         <v>46203</v>
       </c>
@@ -9028,58 +9466,58 @@
       <c r="I81" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="J81" s="4" t="s">
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L81" s="3" t="s">
+      <c r="M81" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N81" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M81" s="4" t="s">
+      <c r="O81" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="N81" s="8" t="s">
+      <c r="P81" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="O81" s="8" t="s">
+      <c r="Q81" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="P81" s="8" t="s">
+      <c r="R81" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="Q81" s="8" t="s">
+      <c r="S81" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R81" s="8" t="s">
+      <c r="T81" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S81" s="8" t="s">
+      <c r="U81" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="T81" s="8" t="s">
+      <c r="V81" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="U81" s="8" t="s">
+      <c r="W81" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V81" s="8">
+      <c r="X81" s="8">
         <v>2026</v>
       </c>
-      <c r="W81" s="8"/>
-      <c r="X81" s="4"/>
-      <c r="Y81" s="8">
+      <c r="Y81" s="8"/>
+      <c r="Z81" s="4"/>
+      <c r="AA81" s="8">
         <v>6.0845586999999997</v>
       </c>
-      <c r="Z81" s="8">
+      <c r="AB81" s="8">
         <v>10.638270800000001</v>
       </c>
-      <c r="AA81" s="8" t="s">
+      <c r="AC81" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="AB81" s="4"/>
-      <c r="AC81" s="4"/>
       <c r="AD81" s="4"/>
       <c r="AE81" s="4"/>
       <c r="AF81" s="4"/>
@@ -9087,9 +9525,12 @@
       <c r="AH81" s="4"/>
       <c r="AI81" s="4"/>
       <c r="AJ81" s="4"/>
+      <c r="AK81" s="4"/>
+      <c r="AL81" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/backend/data/With_PGs_infos_completed.xlsx
+++ b/backend/data/With_PGs_infos_completed.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AFC\church-planting-map\backend\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AFC\Desktop\Everywhere\Nouveau dossier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CB753E-EBE9-4FE5-AE03-7313A454F0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6078BF-7E87-46D2-872D-039BBF17B98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="478">
   <si>
     <t>Date</t>
   </si>
@@ -405,9 +405,6 @@
     <t>Fulani Maroua</t>
   </si>
   <si>
-    <t>Fulani</t>
-  </si>
-  <si>
     <t>GRACE</t>
   </si>
   <si>
@@ -489,9 +486,6 @@
     <t>Kanuri Mora</t>
   </si>
   <si>
-    <t>Kanuri</t>
-  </si>
-  <si>
     <t>Zacharie Dibrila</t>
   </si>
   <si>
@@ -630,9 +624,6 @@
     <t>Mandara Mora</t>
   </si>
   <si>
-    <t>Mandara</t>
-  </si>
-  <si>
     <t xml:space="preserve">Taoré Sokréo </t>
   </si>
   <si>
@@ -951,9 +942,6 @@
     <t>Pygmy</t>
   </si>
   <si>
-    <t>Pygmy Baka</t>
-  </si>
-  <si>
     <t>Eric Bahoue</t>
   </si>
   <si>
@@ -1089,9 +1077,6 @@
     <t>Street boys</t>
   </si>
   <si>
-    <t>Pidgin</t>
-  </si>
-  <si>
     <t>Mayeh Elvis Agueh</t>
   </si>
   <si>
@@ -1212,9 +1197,6 @@
     <t>Pygmy Bipindi</t>
   </si>
   <si>
-    <t>Pygmy Bakola</t>
-  </si>
-  <si>
     <t>Bipindi</t>
   </si>
   <si>
@@ -1381,9 +1363,6 @@
   </si>
   <si>
     <t>Rapport DMM : 'Vekovi' (Kingsley Ngwa). | Catégorie linguistique transversale (ministères urbains/jeunesse/rue), pas une ethnie.</t>
-  </si>
-  <si>
-    <t>Master_People_Group</t>
   </si>
   <si>
     <t>Abong-Bang</t>
@@ -1878,25 +1857,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AL81"/>
+  <dimension ref="A1:AK81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.75"/>
   <cols>
-    <col min="13" max="13" width="13.81640625" customWidth="1"/>
-    <col min="16" max="16" width="26" customWidth="1"/>
-    <col min="17" max="17" width="22" customWidth="1"/>
-    <col min="18" max="18" width="16" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
-    <col min="21" max="21" width="24" customWidth="1"/>
-    <col min="22" max="22" width="30" customWidth="1"/>
-    <col min="23" max="23" width="14" customWidth="1"/>
-    <col min="24" max="24" width="12" customWidth="1"/>
-    <col min="25" max="25" width="26" customWidth="1"/>
-    <col min="26" max="28" width="10" customWidth="1"/>
-    <col min="29" max="29" width="60" customWidth="1"/>
+    <col min="12" max="12" width="13.81640625" customWidth="1"/>
+    <col min="15" max="15" width="26" customWidth="1"/>
+    <col min="16" max="16" width="22" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
+    <col min="20" max="20" width="24" customWidth="1"/>
+    <col min="21" max="21" width="30" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
+    <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="26" customWidth="1"/>
+    <col min="25" max="27" width="10" customWidth="1"/>
+    <col min="28" max="28" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38">
+    <row r="1" spans="1:37">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1925,65 +1904,63 @@
         <v>8</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>452</v>
+        <v>9</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC1" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="AC1" s="6"/>
       <c r="AD1" s="6"/>
       <c r="AE1" s="6"/>
       <c r="AF1" s="6"/>
@@ -1992,9 +1969,8 @@
       <c r="AI1" s="6"/>
       <c r="AJ1" s="6"/>
       <c r="AK1" s="6"/>
-      <c r="AL1" s="6"/>
     </row>
-    <row r="2" spans="1:38" ht="73.75">
+    <row r="2" spans="1:37" ht="73.75">
       <c r="A2" s="1">
         <v>46203</v>
       </c>
@@ -2027,17 +2003,17 @@
         <v>104831</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="P2" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="8" t="s">
         <v>33</v>
@@ -2046,32 +2022,30 @@
         <v>33</v>
       </c>
       <c r="S2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="V2" s="8" t="s">
         <v>33</v>
       </c>
       <c r="W2" s="8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="Y2" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="8"/>
       <c r="AA2" s="8"/>
-      <c r="AB2" s="8"/>
-      <c r="AC2" s="8" t="s">
+      <c r="AB2" s="8" t="s">
         <v>37</v>
       </c>
+      <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
@@ -2080,9 +2054,8 @@
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="4"/>
-      <c r="AL2" s="4"/>
     </row>
-    <row r="3" spans="1:38" ht="44.25">
+    <row r="3" spans="1:37" ht="44.25">
       <c r="A3" s="1">
         <v>46203</v>
       </c>
@@ -2115,57 +2088,55 @@
         <v>100198</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="O3" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="P3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="U3" s="8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="Z3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="8">
+        <v>6.8263122000000003</v>
+      </c>
       <c r="AA3" s="8">
-        <v>6.8263122000000003</v>
-      </c>
-      <c r="AB3" s="8">
         <v>10.1854561</v>
       </c>
-      <c r="AC3" s="8" t="s">
+      <c r="AB3" s="8" t="s">
         <v>48</v>
       </c>
+      <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
@@ -2174,9 +2145,8 @@
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="4"/>
-      <c r="AL3" s="4"/>
     </row>
-    <row r="4" spans="1:38" ht="73.75">
+    <row r="4" spans="1:37" ht="73.75">
       <c r="A4" s="1">
         <v>46203</v>
       </c>
@@ -2211,57 +2181,55 @@
         <v>110311</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="O4" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="P4" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y4" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="Z4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="8">
+        <v>12.0831175</v>
+      </c>
       <c r="AA4" s="8">
-        <v>12.0831175</v>
-      </c>
-      <c r="AB4" s="8">
         <v>15.019126200000001</v>
       </c>
-      <c r="AC4" s="8" t="s">
+      <c r="AB4" s="8" t="s">
         <v>60</v>
       </c>
+      <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
@@ -2270,9 +2238,8 @@
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="4"/>
-      <c r="AL4" s="4"/>
     </row>
-    <row r="5" spans="1:38" ht="29.5">
+    <row r="5" spans="1:37" ht="29.5">
       <c r="A5" s="1">
         <v>46203</v>
       </c>
@@ -2307,57 +2274,55 @@
         <v>103088</v>
       </c>
       <c r="L5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="P5" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q5" s="8" t="s">
         <v>62</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="X5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y5" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="Z5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="8">
+        <v>6.0045045000000004</v>
+      </c>
       <c r="AA5" s="8">
-        <v>6.0045045000000004</v>
-      </c>
-      <c r="AB5" s="8">
         <v>10.214104000000001</v>
       </c>
-      <c r="AC5" s="8" t="s">
+      <c r="AB5" s="8" t="s">
         <v>67</v>
       </c>
+      <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
@@ -2366,9 +2331,8 @@
       <c r="AI5" s="4"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="4"/>
-      <c r="AL5" s="4"/>
     </row>
-    <row r="6" spans="1:38" ht="44.25">
+    <row r="6" spans="1:37" ht="44.25">
       <c r="A6" s="1">
         <v>46203</v>
       </c>
@@ -2403,17 +2367,17 @@
         <v>107171</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="P6" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q6" s="8" t="s">
         <v>33</v>
@@ -2422,10 +2386,10 @@
         <v>33</v>
       </c>
       <c r="S6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T6" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="T6" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="U6" s="8" t="s">
         <v>33</v>
@@ -2434,24 +2398,22 @@
         <v>33</v>
       </c>
       <c r="W6" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="X6" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="Z6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="8" t="s">
+        <v>475</v>
+      </c>
       <c r="AA6" s="8" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AB6" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC6" s="8" t="s">
         <v>70</v>
       </c>
+      <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
@@ -2460,9 +2422,8 @@
       <c r="AI6" s="4"/>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="4"/>
-      <c r="AL6" s="4"/>
     </row>
-    <row r="7" spans="1:38" ht="44.25">
+    <row r="7" spans="1:37" ht="44.25">
       <c r="A7" s="1">
         <v>46203</v>
       </c>
@@ -2497,57 +2458,55 @@
         <v>100941</v>
       </c>
       <c r="L7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T7" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="M7" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T7" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="U7" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="X7" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y7" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="Z7" s="4"/>
+        <v>452</v>
+      </c>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="8">
+        <v>10.25075</v>
+      </c>
       <c r="AA7" s="8">
-        <v>10.25075</v>
-      </c>
-      <c r="AB7" s="8">
         <v>13.51033</v>
       </c>
-      <c r="AC7" s="8" t="s">
+      <c r="AB7" s="8" t="s">
         <v>78</v>
       </c>
+      <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
@@ -2556,9 +2515,8 @@
       <c r="AI7" s="4"/>
       <c r="AJ7" s="4"/>
       <c r="AK7" s="4"/>
-      <c r="AL7" s="4"/>
     </row>
-    <row r="8" spans="1:38" ht="44.25">
+    <row r="8" spans="1:37" ht="44.25">
       <c r="A8" s="1">
         <v>46203</v>
       </c>
@@ -2593,57 +2551,55 @@
         <v>100941</v>
       </c>
       <c r="L8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T8" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T8" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="U8" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="W8" s="8" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="X8" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y8" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="Z8" s="4"/>
+        <v>452</v>
+      </c>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="8">
+        <v>10.25075</v>
+      </c>
       <c r="AA8" s="8">
-        <v>10.25075</v>
-      </c>
-      <c r="AB8" s="8">
         <v>13.51033</v>
       </c>
-      <c r="AC8" s="8" t="s">
+      <c r="AB8" s="8" t="s">
         <v>84</v>
       </c>
+      <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
@@ -2652,9 +2608,8 @@
       <c r="AI8" s="4"/>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="4"/>
-      <c r="AL8" s="4"/>
     </row>
-    <row r="9" spans="1:38" ht="59">
+    <row r="9" spans="1:37" ht="59">
       <c r="A9" s="1">
         <v>46203</v>
       </c>
@@ -2689,57 +2644,55 @@
         <v>100941</v>
       </c>
       <c r="L9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T9" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T9" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="U9" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="V9" s="8" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="W9" s="8" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="X9" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y9" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="Z9" s="4"/>
+        <v>452</v>
+      </c>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="8">
+        <v>10.25075</v>
+      </c>
       <c r="AA9" s="8">
-        <v>10.25075</v>
-      </c>
-      <c r="AB9" s="8">
         <v>13.51033</v>
       </c>
-      <c r="AC9" s="8" t="s">
+      <c r="AB9" s="8" t="s">
         <v>88</v>
       </c>
+      <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
@@ -2748,9 +2701,8 @@
       <c r="AI9" s="4"/>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="4"/>
-      <c r="AL9" s="4"/>
     </row>
-    <row r="10" spans="1:38" ht="44.25">
+    <row r="10" spans="1:37" ht="44.25">
       <c r="A10" s="1">
         <v>46203</v>
       </c>
@@ -2781,57 +2733,55 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O10" s="3" t="s">
         <v>90</v>
       </c>
+      <c r="O10" s="8" t="s">
+        <v>91</v>
+      </c>
       <c r="P10" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="U10" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="V10" s="8" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="W10" s="8" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="X10" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y10" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="Z10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="8">
+        <v>6.0338079999999996</v>
+      </c>
       <c r="AA10" s="8">
-        <v>6.0338079999999996</v>
-      </c>
-      <c r="AB10" s="8">
         <v>10.579231</v>
       </c>
-      <c r="AC10" s="8" t="s">
+      <c r="AB10" s="8" t="s">
         <v>97</v>
       </c>
+      <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
@@ -2840,9 +2790,8 @@
       <c r="AI10" s="4"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="4"/>
-      <c r="AL10" s="4"/>
     </row>
-    <row r="11" spans="1:38" ht="29.5">
+    <row r="11" spans="1:37" ht="29.5">
       <c r="A11" s="1">
         <v>46203</v>
       </c>
@@ -2877,57 +2826,55 @@
         <v>110825</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>385</v>
+        <v>30</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O11" s="3" t="s">
         <v>99</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>98</v>
       </c>
       <c r="P11" s="8" t="s">
         <v>98</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="T11" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U11" s="8" t="s">
         <v>33</v>
       </c>
       <c r="V11" s="8" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="W11" s="8" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="X11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y11" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="Z11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="8">
+        <v>5.8382170999999996</v>
+      </c>
       <c r="AA11" s="8">
-        <v>5.8382170999999996</v>
-      </c>
-      <c r="AB11" s="8">
         <v>9.8887873000000006</v>
       </c>
-      <c r="AC11" s="8" t="s">
+      <c r="AB11" s="8" t="s">
         <v>101</v>
       </c>
+      <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
@@ -2936,9 +2883,8 @@
       <c r="AI11" s="4"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="4"/>
-      <c r="AL11" s="4"/>
     </row>
-    <row r="12" spans="1:38" ht="44.25">
+    <row r="12" spans="1:37" ht="44.25">
       <c r="A12" s="1">
         <v>46203</v>
       </c>
@@ -2973,57 +2919,55 @@
         <v>116642</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O12" s="3" t="s">
         <v>103</v>
       </c>
+      <c r="O12" s="8" t="s">
+        <v>451</v>
+      </c>
       <c r="P12" s="8" t="s">
-        <v>458</v>
+        <v>104</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S12" s="8" t="s">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="T12" s="8" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="U12" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="V12" s="8" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="W12" s="8" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="X12" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y12" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="Z12" s="4"/>
+        <v>453</v>
+      </c>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="8">
+        <v>3.8689866999999998</v>
+      </c>
       <c r="AA12" s="8">
-        <v>3.8689866999999998</v>
-      </c>
-      <c r="AB12" s="8">
         <v>11.521334400000001</v>
       </c>
-      <c r="AC12" s="8" t="s">
+      <c r="AB12" s="8" t="s">
         <v>109</v>
       </c>
+      <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
@@ -3032,9 +2976,8 @@
       <c r="AI12" s="4"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="4"/>
-      <c r="AL12" s="4"/>
     </row>
-    <row r="13" spans="1:38" ht="59">
+    <row r="13" spans="1:37" ht="59">
       <c r="A13" s="1">
         <v>46203</v>
       </c>
@@ -3069,57 +3012,55 @@
         <v>102609</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O13" s="3" t="s">
         <v>111</v>
       </c>
+      <c r="O13" s="8" t="s">
+        <v>112</v>
+      </c>
       <c r="P13" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="T13" s="8" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="U13" s="8" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="V13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="W13" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="X13" s="8">
+      <c r="W13" s="8">
         <v>2026</v>
       </c>
-      <c r="Y13" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z13" s="4"/>
+      <c r="X13" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="8">
+        <v>7.3211535999999997</v>
+      </c>
       <c r="AA13" s="8">
-        <v>7.3211535999999997</v>
-      </c>
-      <c r="AB13" s="8">
         <v>13.587821399999999</v>
       </c>
-      <c r="AC13" s="8" t="s">
+      <c r="AB13" s="8" t="s">
         <v>117</v>
       </c>
+      <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
@@ -3128,9 +3069,8 @@
       <c r="AI13" s="4"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="4"/>
-      <c r="AL13" s="4"/>
     </row>
-    <row r="14" spans="1:38" ht="73.75">
+    <row r="14" spans="1:37" ht="73.75">
       <c r="A14" s="1">
         <v>46203</v>
       </c>
@@ -3165,55 +3105,53 @@
         <v>103273</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O14" s="3" t="s">
         <v>111</v>
       </c>
+      <c r="O14" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="P14" s="8" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S14" s="8" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="T14" s="8" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="U14" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="V14" s="8" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="W14" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="X14" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="4"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="8">
+        <v>7.3211535999999997</v>
+      </c>
       <c r="AA14" s="8">
-        <v>7.3211535999999997</v>
-      </c>
-      <c r="AB14" s="8">
         <v>13.587821399999999</v>
       </c>
-      <c r="AC14" s="8" t="s">
+      <c r="AB14" s="8" t="s">
         <v>122</v>
       </c>
+      <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
@@ -3222,9 +3160,8 @@
       <c r="AI14" s="4"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="4"/>
-      <c r="AL14" s="4"/>
     </row>
-    <row r="15" spans="1:38" ht="44.25">
+    <row r="15" spans="1:37" ht="44.25">
       <c r="A15" s="1">
         <v>46203</v>
       </c>
@@ -3259,17 +3196,17 @@
         <v>102997</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="P15" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q15" s="8" t="s">
         <v>33</v>
@@ -3278,34 +3215,32 @@
         <v>33</v>
       </c>
       <c r="S15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T15" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="U15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="V15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="T15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U15" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="V15" s="8" t="s">
-        <v>44</v>
-      </c>
       <c r="W15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="X15" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="4"/>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="8" t="s">
+        <v>475</v>
+      </c>
       <c r="AA15" s="8" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC15" s="8" t="s">
         <v>124</v>
       </c>
+      <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
@@ -3314,9 +3249,8 @@
       <c r="AI15" s="4"/>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="4"/>
-      <c r="AL15" s="4"/>
     </row>
-    <row r="16" spans="1:38" ht="59">
+    <row r="16" spans="1:37" ht="59">
       <c r="A16" s="1">
         <v>46203</v>
       </c>
@@ -3354,12 +3288,12 @@
         <v>126</v>
       </c>
       <c r="M16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="N16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O16" s="3" t="s">
+      <c r="O16" s="8" t="s">
         <v>128</v>
       </c>
       <c r="P16" s="8" t="s">
@@ -3369,39 +3303,37 @@
         <v>130</v>
       </c>
       <c r="R16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T16" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="S16" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T16" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="U16" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="V16" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W16" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="V16" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="W16" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="X16" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="8">
+        <v>10.6033083</v>
+      </c>
+      <c r="AA16" s="8">
+        <v>14.328162499999999</v>
+      </c>
+      <c r="AB16" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="Y16" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="8">
-        <v>10.6033083</v>
-      </c>
-      <c r="AB16" s="8">
-        <v>14.328162499999999</v>
-      </c>
-      <c r="AC16" s="8" t="s">
-        <v>134</v>
-      </c>
+      <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
@@ -3410,9 +3342,8 @@
       <c r="AI16" s="4"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="4"/>
-      <c r="AL16" s="4"/>
     </row>
-    <row r="17" spans="1:38" ht="29.5">
+    <row r="17" spans="1:37" ht="29.5">
       <c r="A17" s="1">
         <v>46203</v>
       </c>
@@ -3438,7 +3369,7 @@
         <v>30</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J17" s="3">
         <v>11846</v>
@@ -3447,57 +3378,55 @@
         <v>103273</v>
       </c>
       <c r="L17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O17" s="3" t="s">
+      <c r="O17" s="8" t="s">
         <v>136</v>
       </c>
       <c r="P17" s="8" t="s">
         <v>137</v>
       </c>
       <c r="Q17" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="S17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T17" s="8" t="s">
         <v>138</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="S17" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="T17" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="U17" s="8" t="s">
         <v>139</v>
       </c>
       <c r="V17" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="X17" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="W17" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="X17" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y17" s="8" t="s">
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="8">
+        <v>7.2786650000000002</v>
+      </c>
+      <c r="AA17" s="8">
+        <v>13.5462694</v>
+      </c>
+      <c r="AB17" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="8">
-        <v>7.2786650000000002</v>
-      </c>
-      <c r="AB17" s="8">
-        <v>13.5462694</v>
-      </c>
-      <c r="AC17" s="8" t="s">
-        <v>142</v>
-      </c>
+      <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
@@ -3506,9 +3435,8 @@
       <c r="AI17" s="4"/>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="4"/>
-      <c r="AL17" s="4"/>
     </row>
-    <row r="18" spans="1:38" ht="29.5">
+    <row r="18" spans="1:37" ht="29.5">
       <c r="A18" s="1">
         <v>46203</v>
       </c>
@@ -3534,7 +3462,7 @@
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J18" s="3">
         <v>11926</v>
@@ -3543,17 +3471,17 @@
         <v>103442</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="P18" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q18" s="8" t="s">
         <v>33</v>
@@ -3562,10 +3490,10 @@
         <v>33</v>
       </c>
       <c r="S18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T18" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="T18" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="U18" s="8" t="s">
         <v>33</v>
@@ -3574,24 +3502,22 @@
         <v>33</v>
       </c>
       <c r="W18" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="X18" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y18" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="Z18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="8" t="s">
+        <v>475</v>
+      </c>
       <c r="AA18" s="8" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AB18" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC18" s="8" t="s">
-        <v>144</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
@@ -3600,9 +3526,8 @@
       <c r="AI18" s="4"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="4"/>
-      <c r="AL18" s="4"/>
     </row>
-    <row r="19" spans="1:38" ht="29.5">
+    <row r="19" spans="1:37" ht="29.5">
       <c r="A19" s="1">
         <v>46203</v>
       </c>
@@ -3628,7 +3553,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J19" s="3">
         <v>15014</v>
@@ -3637,15 +3562,15 @@
         <v>109445</v>
       </c>
       <c r="L19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O19" s="3" t="s">
+      <c r="O19" s="8" t="s">
         <v>146</v>
       </c>
       <c r="P19" s="8" t="s">
@@ -3655,39 +3580,37 @@
         <v>148</v>
       </c>
       <c r="R19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T19" s="8" t="s">
         <v>149</v>
-      </c>
-      <c r="S19" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T19" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="U19" s="8" t="s">
         <v>150</v>
       </c>
       <c r="V19" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W19" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X19" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="8">
+        <v>10.4014393</v>
+      </c>
+      <c r="AA19" s="8">
+        <v>14.4425653</v>
+      </c>
+      <c r="AB19" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="W19" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X19" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y19" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="8">
-        <v>10.4014393</v>
-      </c>
-      <c r="AB19" s="8">
-        <v>14.4425653</v>
-      </c>
-      <c r="AC19" s="8" t="s">
-        <v>152</v>
-      </c>
+      <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
       <c r="AF19" s="4"/>
@@ -3696,9 +3619,8 @@
       <c r="AI19" s="4"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="4"/>
-      <c r="AL19" s="4"/>
     </row>
-    <row r="20" spans="1:38" ht="29.5">
+    <row r="20" spans="1:37" ht="29.5">
       <c r="A20" s="1">
         <v>46203</v>
       </c>
@@ -3724,7 +3646,7 @@
         <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J20" s="3">
         <v>12509</v>
@@ -3733,57 +3655,55 @@
         <v>104605</v>
       </c>
       <c r="L20" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="O20" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O20" s="3" t="s">
+      <c r="P20" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q20" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="P20" s="8" t="s">
+      <c r="R20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S20" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T20" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="Q20" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="R20" s="8" t="s">
+      <c r="U20" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="V20" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="S20" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T20" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U20" s="8" t="s">
+      <c r="W20" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X20" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="8">
+        <v>11.0484452</v>
+      </c>
+      <c r="AA20" s="8">
+        <v>14.1342835</v>
+      </c>
+      <c r="AB20" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="V20" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="W20" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="X20" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y20" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="Z20" s="4"/>
-      <c r="AA20" s="8">
-        <v>11.0484452</v>
-      </c>
-      <c r="AB20" s="8">
-        <v>14.1342835</v>
-      </c>
-      <c r="AC20" s="8" t="s">
-        <v>160</v>
-      </c>
+      <c r="AC20" s="4"/>
       <c r="AD20" s="4"/>
       <c r="AE20" s="4"/>
       <c r="AF20" s="4"/>
@@ -3792,9 +3712,8 @@
       <c r="AI20" s="4"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="4"/>
-      <c r="AL20" s="4"/>
     </row>
-    <row r="21" spans="1:38" ht="29.5">
+    <row r="21" spans="1:37" ht="29.5">
       <c r="A21" s="1">
         <v>46203</v>
       </c>
@@ -3820,7 +3739,7 @@
         <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J21" s="3">
         <v>12517</v>
@@ -3829,57 +3748,55 @@
         <v>104619</v>
       </c>
       <c r="L21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O21" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="P21" s="8" t="s">
+      <c r="Q21" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T21" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="Q21" s="8" t="s">
+      <c r="U21" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="R21" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="S21" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U21" s="8" t="s">
+      <c r="V21" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="W21" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X21" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="V21" s="8" t="s">
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="8">
+        <v>10.74103</v>
+      </c>
+      <c r="AA21" s="8">
+        <v>13.798742000000001</v>
+      </c>
+      <c r="AB21" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="W21" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="X21" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y21" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="Z21" s="4"/>
-      <c r="AA21" s="8">
-        <v>10.74103</v>
-      </c>
-      <c r="AB21" s="8">
-        <v>13.798742000000001</v>
-      </c>
-      <c r="AC21" s="8" t="s">
-        <v>168</v>
-      </c>
+      <c r="AC21" s="4"/>
       <c r="AD21" s="4"/>
       <c r="AE21" s="4"/>
       <c r="AF21" s="4"/>
@@ -3888,9 +3805,8 @@
       <c r="AI21" s="4"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="4"/>
-      <c r="AL21" s="4"/>
     </row>
-    <row r="22" spans="1:38" ht="29.5">
+    <row r="22" spans="1:37" ht="29.5">
       <c r="A22" s="1">
         <v>46203</v>
       </c>
@@ -3916,7 +3832,7 @@
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J22" s="3">
         <v>12517</v>
@@ -3925,57 +3841,55 @@
         <v>104619</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>161</v>
+        <v>30</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O22" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T22" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="U22" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="V22" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="W22" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="X22" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA22" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="AB22" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="P22" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q22" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="S22" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U22" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="V22" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="W22" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="X22" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y22" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="Z22" s="4"/>
-      <c r="AA22" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AB22" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC22" s="8" t="s">
-        <v>172</v>
-      </c>
+      <c r="AC22" s="4"/>
       <c r="AD22" s="4"/>
       <c r="AE22" s="4"/>
       <c r="AF22" s="4"/>
@@ -3984,9 +3898,8 @@
       <c r="AI22" s="4"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="4"/>
-      <c r="AL22" s="4"/>
     </row>
-    <row r="23" spans="1:38" ht="29.5">
+    <row r="23" spans="1:37" ht="29.5">
       <c r="A23" s="1">
         <v>46203</v>
       </c>
@@ -4012,7 +3925,7 @@
         <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J23" s="3">
         <v>10166</v>
@@ -4021,57 +3934,55 @@
         <v>100086</v>
       </c>
       <c r="L23" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q23" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T23" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="P23" s="8" t="s">
+      <c r="U23" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="V23" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W23" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="X23" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="Q23" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="S23" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T23" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U23" s="8" t="s">
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="8">
+        <v>11.780627000000001</v>
+      </c>
+      <c r="AA23" s="8">
+        <v>15.103911999999999</v>
+      </c>
+      <c r="AB23" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="V23" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="W23" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X23" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y23" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z23" s="4"/>
-      <c r="AA23" s="8">
-        <v>11.780627000000001</v>
-      </c>
-      <c r="AB23" s="8">
-        <v>15.103911999999999</v>
-      </c>
-      <c r="AC23" s="8" t="s">
-        <v>177</v>
-      </c>
+      <c r="AC23" s="4"/>
       <c r="AD23" s="4"/>
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
@@ -4080,9 +3991,8 @@
       <c r="AI23" s="4"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="4"/>
-      <c r="AL23" s="4"/>
     </row>
-    <row r="24" spans="1:38" ht="73.75">
+    <row r="24" spans="1:37" ht="73.75">
       <c r="A24" s="1">
         <v>46203</v>
       </c>
@@ -4108,7 +4018,7 @@
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J24" s="3">
         <v>12778</v>
@@ -4117,57 +4027,55 @@
         <v>105185</v>
       </c>
       <c r="L24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="O24" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O24" s="3" t="s">
+      <c r="P24" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="S24" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T24" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="U24" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="V24" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W24" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="P24" s="8" t="s">
+      <c r="X24" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA24" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="AB24" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="Q24" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="R24" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="S24" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="T24" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U24" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="V24" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="W24" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X24" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y24" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="Z24" s="4"/>
-      <c r="AA24" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AB24" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC24" s="8" t="s">
-        <v>182</v>
-      </c>
+      <c r="AC24" s="4"/>
       <c r="AD24" s="4"/>
       <c r="AE24" s="4"/>
       <c r="AF24" s="4"/>
@@ -4176,9 +4084,8 @@
       <c r="AI24" s="4"/>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="4"/>
-      <c r="AL24" s="4"/>
     </row>
-    <row r="25" spans="1:38" ht="29.5">
+    <row r="25" spans="1:37" ht="29.5">
       <c r="A25" s="1">
         <v>46203</v>
       </c>
@@ -4204,7 +4111,7 @@
         <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J25" s="3">
         <v>15614</v>
@@ -4213,55 +4120,53 @@
         <v>110241</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>364</v>
+        <v>30</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="8" t="s">
+        <v>181</v>
+      </c>
       <c r="P25" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q25" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="R25" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="Q25" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="R25" s="8" t="s">
-        <v>184</v>
-      </c>
       <c r="S25" s="8" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="T25" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U25" s="8" t="s">
         <v>33</v>
       </c>
       <c r="V25" s="8" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="W25" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="X25" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="Z25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="8">
+        <v>9.0574802000000005</v>
+      </c>
       <c r="AA25" s="8">
-        <v>9.0574802000000005</v>
-      </c>
-      <c r="AB25" s="8">
         <v>13.6653588</v>
       </c>
-      <c r="AC25" s="8" t="s">
-        <v>186</v>
-      </c>
+      <c r="AB25" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AC25" s="4"/>
       <c r="AD25" s="4"/>
       <c r="AE25" s="4"/>
       <c r="AF25" s="4"/>
@@ -4270,9 +4175,8 @@
       <c r="AI25" s="4"/>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="4"/>
-      <c r="AL25" s="4"/>
     </row>
-    <row r="26" spans="1:38" ht="44.25">
+    <row r="26" spans="1:37" ht="44.25">
       <c r="A26" s="1">
         <v>46203</v>
       </c>
@@ -4298,7 +4202,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J26" s="3">
         <v>13193</v>
@@ -4307,57 +4211,55 @@
         <v>105977</v>
       </c>
       <c r="L26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="O26" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="P26" s="8" t="s">
-        <v>190</v>
+        <v>33</v>
       </c>
       <c r="Q26" s="8" t="s">
         <v>33</v>
       </c>
       <c r="R26" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T26" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="U26" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="V26" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S26" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T26" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U26" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="V26" s="8" t="s">
+      <c r="W26" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="X26" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA26" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="AB26" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="W26" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="X26" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y26" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="Z26" s="4"/>
-      <c r="AA26" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AB26" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC26" s="8" t="s">
-        <v>193</v>
-      </c>
+      <c r="AC26" s="4"/>
       <c r="AD26" s="4"/>
       <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
@@ -4366,9 +4268,8 @@
       <c r="AI26" s="4"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="4"/>
-      <c r="AL26" s="4"/>
     </row>
-    <row r="27" spans="1:38" ht="59">
+    <row r="27" spans="1:37" ht="59">
       <c r="A27" s="1">
         <v>46203</v>
       </c>
@@ -4394,7 +4295,7 @@
         <v>30</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J27" s="3">
         <v>13201</v>
@@ -4403,57 +4304,55 @@
         <v>106001</v>
       </c>
       <c r="L27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="O27" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O27" s="3" t="s">
+      <c r="P27" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q27" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="R27" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S27" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T27" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="U27" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="P27" s="8" t="s">
+      <c r="V27" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="W27" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X27" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="Q27" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="R27" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="S27" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T27" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U27" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="V27" s="8" t="s">
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="8">
+        <v>10.74103</v>
+      </c>
+      <c r="AA27" s="8">
+        <v>13.798742000000001</v>
+      </c>
+      <c r="AB27" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="W27" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="X27" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y27" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z27" s="4"/>
-      <c r="AA27" s="8">
-        <v>10.74103</v>
-      </c>
-      <c r="AB27" s="8">
-        <v>13.798742000000001</v>
-      </c>
-      <c r="AC27" s="8" t="s">
-        <v>199</v>
-      </c>
+      <c r="AC27" s="4"/>
       <c r="AD27" s="4"/>
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
@@ -4462,9 +4361,8 @@
       <c r="AI27" s="4"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="4"/>
-      <c r="AL27" s="4"/>
     </row>
-    <row r="28" spans="1:38" ht="44.25">
+    <row r="28" spans="1:37" ht="44.25">
       <c r="A28" s="1">
         <v>46203</v>
       </c>
@@ -4490,7 +4388,7 @@
         <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J28" s="3">
         <v>13487</v>
@@ -4499,57 +4397,55 @@
         <v>106228</v>
       </c>
       <c r="L28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S28" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T28" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="U28" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="M28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O28" s="3" t="s">
+      <c r="V28" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="W28" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="X28" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="P28" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q28" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="R28" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="S28" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T28" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U28" s="8" t="s">
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="8">
+        <v>11.0484452</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>14.1342835</v>
+      </c>
+      <c r="AB28" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="V28" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="W28" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="X28" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y28" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="Z28" s="4"/>
-      <c r="AA28" s="8">
-        <v>11.0484452</v>
-      </c>
-      <c r="AB28" s="8">
-        <v>14.1342835</v>
-      </c>
-      <c r="AC28" s="8" t="s">
-        <v>206</v>
-      </c>
+      <c r="AC28" s="4"/>
       <c r="AD28" s="4"/>
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
@@ -4558,9 +4454,8 @@
       <c r="AI28" s="4"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="4"/>
-      <c r="AL28" s="4"/>
     </row>
-    <row r="29" spans="1:38" ht="59">
+    <row r="29" spans="1:37" ht="59">
       <c r="A29" s="1">
         <v>46203</v>
       </c>
@@ -4586,7 +4481,7 @@
         <v>30</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J29" s="3">
         <v>13560</v>
@@ -4595,57 +4490,55 @@
         <v>106369</v>
       </c>
       <c r="L29" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="O29" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="P29" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="R29" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S29" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T29" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O29" s="3" t="s">
+      <c r="U29" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="V29" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W29" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X29" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="Y29" s="4"/>
+      <c r="Z29" s="8">
+        <v>12.0831175</v>
+      </c>
+      <c r="AA29" s="8">
+        <v>15.019126200000001</v>
+      </c>
+      <c r="AB29" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="P29" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q29" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="R29" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="S29" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T29" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U29" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="V29" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="W29" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="X29" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y29" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="Z29" s="4"/>
-      <c r="AA29" s="8">
-        <v>12.0831175</v>
-      </c>
-      <c r="AB29" s="8">
-        <v>15.019126200000001</v>
-      </c>
-      <c r="AC29" s="8" t="s">
-        <v>211</v>
-      </c>
+      <c r="AC29" s="4"/>
       <c r="AD29" s="4"/>
       <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
@@ -4654,9 +4547,8 @@
       <c r="AI29" s="4"/>
       <c r="AJ29" s="4"/>
       <c r="AK29" s="4"/>
-      <c r="AL29" s="4"/>
     </row>
-    <row r="30" spans="1:38" ht="29.5">
+    <row r="30" spans="1:37" ht="29.5">
       <c r="A30" s="1">
         <v>46203</v>
       </c>
@@ -4682,7 +4574,7 @@
         <v>30</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J30" s="3">
         <v>13581</v>
@@ -4691,57 +4583,55 @@
         <v>106395</v>
       </c>
       <c r="L30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="M30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O30" s="3" t="s">
+      <c r="Q30" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="P30" s="8" t="s">
+      <c r="R30" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="S30" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T30" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="Q30" s="8" t="s">
+      <c r="U30" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="V30" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W30" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="X30" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="8">
+        <v>4.8673555000000004</v>
+      </c>
+      <c r="AA30" s="8">
+        <v>11.156444</v>
+      </c>
+      <c r="AB30" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="R30" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="S30" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="T30" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U30" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="V30" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="W30" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X30" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y30" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="Z30" s="4"/>
-      <c r="AA30" s="8">
-        <v>4.8673555000000004</v>
-      </c>
-      <c r="AB30" s="8">
-        <v>11.156444</v>
-      </c>
-      <c r="AC30" s="8" t="s">
-        <v>218</v>
-      </c>
+      <c r="AC30" s="4"/>
       <c r="AD30" s="4"/>
       <c r="AE30" s="4"/>
       <c r="AF30" s="4"/>
@@ -4750,9 +4640,8 @@
       <c r="AI30" s="4"/>
       <c r="AJ30" s="4"/>
       <c r="AK30" s="4"/>
-      <c r="AL30" s="4"/>
     </row>
-    <row r="31" spans="1:38" ht="29.5">
+    <row r="31" spans="1:37" ht="29.5">
       <c r="A31" s="1">
         <v>46203</v>
       </c>
@@ -4778,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J31" s="3">
         <v>11774</v>
@@ -4790,54 +4679,52 @@
         <v>126</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O31" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="P31" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q31" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="P31" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q31" s="8" t="s">
-        <v>215</v>
-      </c>
       <c r="R31" s="8" t="s">
-        <v>216</v>
+        <v>115</v>
       </c>
       <c r="S31" s="8" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="T31" s="8" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="U31" s="8" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="V31" s="8" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="W31" s="8" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="X31" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y31" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="Z31" s="4"/>
+        <v>454</v>
+      </c>
+      <c r="Y31" s="4"/>
+      <c r="Z31" s="8">
+        <v>4.8673555000000004</v>
+      </c>
       <c r="AA31" s="8">
-        <v>4.8673555000000004</v>
-      </c>
-      <c r="AB31" s="8">
         <v>11.156444</v>
       </c>
-      <c r="AC31" s="8" t="s">
-        <v>220</v>
-      </c>
+      <c r="AB31" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="AC31" s="4"/>
       <c r="AD31" s="4"/>
       <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
@@ -4846,9 +4733,8 @@
       <c r="AI31" s="4"/>
       <c r="AJ31" s="4"/>
       <c r="AK31" s="4"/>
-      <c r="AL31" s="4"/>
     </row>
-    <row r="32" spans="1:38" ht="59">
+    <row r="32" spans="1:37" ht="59">
       <c r="A32" s="1">
         <v>46203</v>
       </c>
@@ -4874,7 +4760,7 @@
         <v>30</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J32" s="3">
         <v>13642</v>
@@ -4883,57 +4769,55 @@
         <v>106494</v>
       </c>
       <c r="L32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="P32" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O32" s="3" t="s">
+      <c r="Q32" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="P32" s="8" t="s">
+      <c r="R32" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="S32" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T32" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="Q32" s="8" t="s">
+      <c r="U32" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="V32" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="W32" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="X32" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="R32" s="8" t="s">
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="8">
+        <v>6.5172122999999997</v>
+      </c>
+      <c r="AA32" s="8">
+        <v>14.294787899999999</v>
+      </c>
+      <c r="AB32" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="S32" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="T32" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U32" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="V32" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="W32" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="X32" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y32" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="Z32" s="4"/>
-      <c r="AA32" s="8">
-        <v>6.5172122999999997</v>
-      </c>
-      <c r="AB32" s="8">
-        <v>14.294787899999999</v>
-      </c>
-      <c r="AC32" s="8" t="s">
-        <v>228</v>
-      </c>
+      <c r="AC32" s="4"/>
       <c r="AD32" s="4"/>
       <c r="AE32" s="4"/>
       <c r="AF32" s="4"/>
@@ -4942,9 +4826,8 @@
       <c r="AI32" s="4"/>
       <c r="AJ32" s="4"/>
       <c r="AK32" s="4"/>
-      <c r="AL32" s="4"/>
     </row>
-    <row r="33" spans="1:38" ht="88.5">
+    <row r="33" spans="1:37" ht="88.5">
       <c r="A33" s="1">
         <v>46203</v>
       </c>
@@ -4970,7 +4853,7 @@
         <v>30</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J33" s="3">
         <v>13676</v>
@@ -4979,55 +4862,53 @@
         <v>106547</v>
       </c>
       <c r="L33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N33" s="3"/>
+      <c r="O33" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q33" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="R33" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S33" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T33" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O33" s="3"/>
-      <c r="P33" s="8" t="s">
+      <c r="U33" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="Q33" s="8" t="s">
+      <c r="V33" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="W33" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="X33" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="R33" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="S33" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T33" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U33" s="8" t="s">
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="8">
+        <v>5.7961640000000001</v>
+      </c>
+      <c r="AA33" s="8">
+        <v>10.162518</v>
+      </c>
+      <c r="AB33" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="V33" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="W33" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="X33" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y33" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="8">
-        <v>5.7961640000000001</v>
-      </c>
-      <c r="AB33" s="8">
-        <v>10.162518</v>
-      </c>
-      <c r="AC33" s="8" t="s">
-        <v>235</v>
-      </c>
+      <c r="AC33" s="4"/>
       <c r="AD33" s="4"/>
       <c r="AE33" s="4"/>
       <c r="AF33" s="4"/>
@@ -5036,9 +4917,8 @@
       <c r="AI33" s="4"/>
       <c r="AJ33" s="4"/>
       <c r="AK33" s="4"/>
-      <c r="AL33" s="4"/>
     </row>
-    <row r="34" spans="1:38" ht="73.75">
+    <row r="34" spans="1:37" ht="73.75">
       <c r="A34" s="1">
         <v>46203</v>
       </c>
@@ -5064,7 +4944,7 @@
         <v>30</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J34" s="3">
         <v>13760</v>
@@ -5073,57 +4953,55 @@
         <v>106702</v>
       </c>
       <c r="L34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="P34" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q34" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="R34" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S34" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T34" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="M34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O34" s="3" t="s">
+      <c r="U34" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="P34" s="8" t="s">
+      <c r="V34" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="W34" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X34" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="8">
+        <v>10.74103</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>13.798742000000001</v>
+      </c>
+      <c r="AB34" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="Q34" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="R34" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="S34" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T34" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U34" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="V34" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="W34" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="X34" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y34" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="8">
-        <v>10.74103</v>
-      </c>
-      <c r="AB34" s="8">
-        <v>13.798742000000001</v>
-      </c>
-      <c r="AC34" s="8" t="s">
-        <v>241</v>
-      </c>
+      <c r="AC34" s="4"/>
       <c r="AD34" s="4"/>
       <c r="AE34" s="4"/>
       <c r="AF34" s="4"/>
@@ -5132,9 +5010,8 @@
       <c r="AI34" s="4"/>
       <c r="AJ34" s="4"/>
       <c r="AK34" s="4"/>
-      <c r="AL34" s="4"/>
     </row>
-    <row r="35" spans="1:38" ht="44.25">
+    <row r="35" spans="1:37" ht="44.25">
       <c r="A35" s="1">
         <v>46203</v>
       </c>
@@ -5160,7 +5037,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J35" s="3">
         <v>13868</v>
@@ -5169,53 +5046,51 @@
         <v>106897</v>
       </c>
       <c r="L35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="O35" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="P35" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O35" s="3" t="s">
+      <c r="Q35" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="R35" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S35" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T35" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="P35" s="8" t="s">
+      <c r="U35" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="V35" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W35" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X35" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="8"/>
+      <c r="AA35" s="8"/>
+      <c r="AB35" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="Q35" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="R35" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="S35" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T35" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U35" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="V35" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="W35" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X35" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y35" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="8"/>
-      <c r="AB35" s="8"/>
-      <c r="AC35" s="8" t="s">
-        <v>247</v>
-      </c>
+      <c r="AC35" s="4"/>
       <c r="AD35" s="4"/>
       <c r="AE35" s="4"/>
       <c r="AF35" s="4"/>
@@ -5224,9 +5099,8 @@
       <c r="AI35" s="4"/>
       <c r="AJ35" s="4"/>
       <c r="AK35" s="4"/>
-      <c r="AL35" s="4"/>
     </row>
-    <row r="36" spans="1:38" ht="59">
+    <row r="36" spans="1:37" ht="59">
       <c r="A36" s="1">
         <v>46203</v>
       </c>
@@ -5252,7 +5126,7 @@
         <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J36" s="3">
         <v>13487</v>
@@ -5261,57 +5135,55 @@
         <v>106228</v>
       </c>
       <c r="L36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="O36" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="P36" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q36" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="R36" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S36" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T36" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="U36" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="M36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="P36" s="8" t="s">
+      <c r="V36" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="W36" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="X36" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="8">
+        <v>11.0484452</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>14.1342835</v>
+      </c>
+      <c r="AB36" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="Q36" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="R36" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="S36" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T36" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U36" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="V36" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="W36" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="X36" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y36" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="8">
-        <v>11.0484452</v>
-      </c>
-      <c r="AB36" s="8">
-        <v>14.1342835</v>
-      </c>
-      <c r="AC36" s="8" t="s">
-        <v>252</v>
-      </c>
+      <c r="AC36" s="4"/>
       <c r="AD36" s="4"/>
       <c r="AE36" s="4"/>
       <c r="AF36" s="4"/>
@@ -5320,9 +5192,8 @@
       <c r="AI36" s="4"/>
       <c r="AJ36" s="4"/>
       <c r="AK36" s="4"/>
-      <c r="AL36" s="4"/>
     </row>
-    <row r="37" spans="1:38" ht="44.25">
+    <row r="37" spans="1:37" ht="44.25">
       <c r="A37" s="1">
         <v>46203</v>
       </c>
@@ -5348,7 +5219,7 @@
         <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J37" s="3">
         <v>13898</v>
@@ -5357,57 +5228,55 @@
         <v>106976</v>
       </c>
       <c r="L37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="O37" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="P37" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q37" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="R37" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S37" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T37" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="U37" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="V37" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="W37" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="X37" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="8">
+        <v>11.0484452</v>
+      </c>
+      <c r="AA37" s="8">
+        <v>14.1342835</v>
+      </c>
+      <c r="AB37" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="M37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="P37" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q37" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="R37" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="S37" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T37" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U37" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="V37" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="W37" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="X37" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y37" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="Z37" s="4"/>
-      <c r="AA37" s="8">
-        <v>11.0484452</v>
-      </c>
-      <c r="AB37" s="8">
-        <v>14.1342835</v>
-      </c>
-      <c r="AC37" s="8" t="s">
-        <v>256</v>
-      </c>
+      <c r="AC37" s="4"/>
       <c r="AD37" s="4"/>
       <c r="AE37" s="4"/>
       <c r="AF37" s="4"/>
@@ -5416,9 +5285,8 @@
       <c r="AI37" s="4"/>
       <c r="AJ37" s="4"/>
       <c r="AK37" s="4"/>
-      <c r="AL37" s="4"/>
     </row>
-    <row r="38" spans="1:38" ht="73.75">
+    <row r="38" spans="1:37" ht="73.75">
       <c r="A38" s="1">
         <v>46203</v>
       </c>
@@ -5444,7 +5312,7 @@
         <v>30</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J38" s="3">
         <v>13760</v>
@@ -5453,57 +5321,55 @@
         <v>106702</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>257</v>
+        <v>30</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
+      </c>
+      <c r="O38" s="8" t="s">
+        <v>235</v>
       </c>
       <c r="P38" s="8" t="s">
-        <v>238</v>
+        <v>162</v>
       </c>
       <c r="Q38" s="8" t="s">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="R38" s="8" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="S38" s="8" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="T38" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U38" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V38" s="8" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="W38" s="8" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="X38" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y38" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="Z38" s="4"/>
+        <v>463</v>
+      </c>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="8">
+        <v>10.74103</v>
+      </c>
       <c r="AA38" s="8">
-        <v>10.74103</v>
-      </c>
-      <c r="AB38" s="8">
         <v>13.798742000000001</v>
       </c>
-      <c r="AC38" s="8" t="s">
-        <v>258</v>
-      </c>
+      <c r="AB38" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="AC38" s="4"/>
       <c r="AD38" s="4"/>
       <c r="AE38" s="4"/>
       <c r="AF38" s="4"/>
@@ -5512,9 +5378,8 @@
       <c r="AI38" s="4"/>
       <c r="AJ38" s="4"/>
       <c r="AK38" s="4"/>
-      <c r="AL38" s="4"/>
     </row>
-    <row r="39" spans="1:38" ht="29.5">
+    <row r="39" spans="1:37" ht="29.5">
       <c r="A39" s="1">
         <v>46203</v>
       </c>
@@ -5540,7 +5405,7 @@
         <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="J39" s="3">
         <v>13864</v>
@@ -5549,57 +5414,55 @@
         <v>106889</v>
       </c>
       <c r="L39" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="O39" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="P39" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q39" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="M39" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O39" s="3" t="s">
+      <c r="R39" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="P39" s="8" t="s">
+      <c r="S39" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T39" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="Q39" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="R39" s="8" t="s">
+      <c r="U39" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="S39" s="8" t="s">
+      <c r="V39" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W39" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="X39" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="8">
+        <v>5.7282261999999999</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>10.897160299999999</v>
+      </c>
+      <c r="AB39" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="T39" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U39" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="V39" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="W39" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="X39" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y39" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="8">
-        <v>5.7282261999999999</v>
-      </c>
-      <c r="AB39" s="8">
-        <v>10.897160299999999</v>
-      </c>
-      <c r="AC39" s="8" t="s">
-        <v>266</v>
-      </c>
+      <c r="AC39" s="4"/>
       <c r="AD39" s="4"/>
       <c r="AE39" s="4"/>
       <c r="AF39" s="4"/>
@@ -5608,9 +5471,8 @@
       <c r="AI39" s="4"/>
       <c r="AJ39" s="4"/>
       <c r="AK39" s="4"/>
-      <c r="AL39" s="4"/>
     </row>
-    <row r="40" spans="1:38" ht="29.5">
+    <row r="40" spans="1:37" ht="29.5">
       <c r="A40" s="1">
         <v>46203</v>
       </c>
@@ -5636,7 +5498,7 @@
         <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J40" s="3">
         <v>13840</v>
@@ -5645,57 +5507,55 @@
         <v>106832</v>
       </c>
       <c r="L40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="O40" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="P40" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q40" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="R40" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S40" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T40" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="M40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O40" s="3" t="s">
+      <c r="U40" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="P40" s="8" t="s">
+      <c r="V40" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W40" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="X40" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="8">
+        <v>11.780627000000001</v>
+      </c>
+      <c r="AA40" s="8">
+        <v>15.103911999999999</v>
+      </c>
+      <c r="AB40" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="Q40" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="R40" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="S40" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T40" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U40" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="V40" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="W40" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X40" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y40" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z40" s="4"/>
-      <c r="AA40" s="8">
-        <v>11.780627000000001</v>
-      </c>
-      <c r="AB40" s="8">
-        <v>15.103911999999999</v>
-      </c>
-      <c r="AC40" s="8" t="s">
-        <v>272</v>
-      </c>
+      <c r="AC40" s="4"/>
       <c r="AD40" s="4"/>
       <c r="AE40" s="4"/>
       <c r="AF40" s="4"/>
@@ -5704,9 +5564,8 @@
       <c r="AI40" s="4"/>
       <c r="AJ40" s="4"/>
       <c r="AK40" s="4"/>
-      <c r="AL40" s="4"/>
     </row>
-    <row r="41" spans="1:38" ht="44.25">
+    <row r="41" spans="1:37" ht="44.25">
       <c r="A41" s="1">
         <v>46203</v>
       </c>
@@ -5732,60 +5591,58 @@
         <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N41" s="3"/>
+      <c r="O41" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="P41" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q41" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O41" s="3"/>
-      <c r="P41" s="8" t="s">
+      <c r="R41" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="S41" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T41" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="Q41" s="8" t="s">
+      <c r="U41" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="R41" s="8" t="s">
+      <c r="V41" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="W41" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X41" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="8">
+        <v>4.6665934</v>
+      </c>
+      <c r="AA41" s="8">
+        <v>12.3730806</v>
+      </c>
+      <c r="AB41" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="S41" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="T41" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U41" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="V41" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="W41" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="X41" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y41" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="8">
-        <v>4.6665934</v>
-      </c>
-      <c r="AB41" s="8">
-        <v>12.3730806</v>
-      </c>
-      <c r="AC41" s="8" t="s">
-        <v>279</v>
-      </c>
+      <c r="AC41" s="4"/>
       <c r="AD41" s="4"/>
       <c r="AE41" s="4"/>
       <c r="AF41" s="4"/>
@@ -5794,9 +5651,8 @@
       <c r="AI41" s="4"/>
       <c r="AJ41" s="4"/>
       <c r="AK41" s="4"/>
-      <c r="AL41" s="4"/>
     </row>
-    <row r="42" spans="1:38" ht="59">
+    <row r="42" spans="1:37" ht="59">
       <c r="A42" s="1">
         <v>46203</v>
       </c>
@@ -5822,7 +5678,7 @@
         <v>30</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J42" s="3">
         <v>13291</v>
@@ -5831,55 +5687,53 @@
         <v>107171</v>
       </c>
       <c r="L42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="O42" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="P42" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O42" s="3" t="s">
+      <c r="Q42" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="R42" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S42" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T42" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="P42" s="8" t="s">
+      <c r="U42" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="V42" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="W42" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X42" s="8"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="8">
+        <v>6.0338079999999996</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>10.579231</v>
+      </c>
+      <c r="AB42" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="Q42" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="R42" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="S42" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T42" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U42" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="V42" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="W42" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="X42" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y42" s="8"/>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="8">
-        <v>6.0338079999999996</v>
-      </c>
-      <c r="AB42" s="8">
-        <v>10.579231</v>
-      </c>
-      <c r="AC42" s="8" t="s">
-        <v>285</v>
-      </c>
+      <c r="AC42" s="4"/>
       <c r="AD42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AF42" s="4"/>
@@ -5888,9 +5742,8 @@
       <c r="AI42" s="4"/>
       <c r="AJ42" s="4"/>
       <c r="AK42" s="4"/>
-      <c r="AL42" s="4"/>
     </row>
-    <row r="43" spans="1:38" ht="29.5">
+    <row r="43" spans="1:37" ht="29.5">
       <c r="A43" s="1">
         <v>46203</v>
       </c>
@@ -5916,7 +5769,7 @@
         <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="J43" s="3">
         <v>14763</v>
@@ -5925,57 +5778,55 @@
         <v>108711</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>286</v>
+        <v>30</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
+      </c>
+      <c r="O43" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="P43" s="8" t="s">
         <v>137</v>
       </c>
       <c r="Q43" s="8" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="R43" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S43" s="8" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="T43" s="8" t="s">
-        <v>34</v>
+        <v>285</v>
       </c>
       <c r="U43" s="8" t="s">
-        <v>288</v>
+        <v>189</v>
       </c>
       <c r="V43" s="8" t="s">
-        <v>191</v>
+        <v>57</v>
       </c>
       <c r="W43" s="8" t="s">
-        <v>57</v>
+        <v>286</v>
       </c>
       <c r="X43" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="Y43" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="Z43" s="4"/>
+        <v>469</v>
+      </c>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="8">
+        <v>7.2786650000000002</v>
+      </c>
       <c r="AA43" s="8">
-        <v>7.2786650000000002</v>
-      </c>
-      <c r="AB43" s="8">
         <v>13.5462694</v>
       </c>
-      <c r="AC43" s="8" t="s">
-        <v>290</v>
-      </c>
+      <c r="AB43" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="AC43" s="4"/>
       <c r="AD43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AF43" s="4"/>
@@ -5984,9 +5835,8 @@
       <c r="AI43" s="4"/>
       <c r="AJ43" s="4"/>
       <c r="AK43" s="4"/>
-      <c r="AL43" s="4"/>
     </row>
-    <row r="44" spans="1:38" ht="44.25">
+    <row r="44" spans="1:37" ht="44.25">
       <c r="A44" s="1">
         <v>46203</v>
       </c>
@@ -6012,7 +5862,7 @@
         <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J44" s="3">
         <v>13351</v>
@@ -6021,53 +5871,51 @@
         <v>107261</v>
       </c>
       <c r="L44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N44" s="3"/>
+      <c r="O44" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="P44" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q44" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="R44" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S44" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T44" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="U44" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="V44" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="W44" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="X44" s="8"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="8">
+        <v>5.7961640000000001</v>
+      </c>
+      <c r="AA44" s="8">
+        <v>10.162518</v>
+      </c>
+      <c r="AB44" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O44" s="3"/>
-      <c r="P44" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q44" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="R44" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="S44" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T44" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U44" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="V44" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="W44" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="X44" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y44" s="8"/>
-      <c r="Z44" s="4"/>
-      <c r="AA44" s="8">
-        <v>5.7961640000000001</v>
-      </c>
-      <c r="AB44" s="8">
-        <v>10.162518</v>
-      </c>
-      <c r="AC44" s="8" t="s">
-        <v>294</v>
-      </c>
+      <c r="AC44" s="4"/>
       <c r="AD44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AF44" s="4"/>
@@ -6076,9 +5924,8 @@
       <c r="AI44" s="4"/>
       <c r="AJ44" s="4"/>
       <c r="AK44" s="4"/>
-      <c r="AL44" s="4"/>
     </row>
-    <row r="45" spans="1:38" ht="29.5">
+    <row r="45" spans="1:37" ht="29.5">
       <c r="A45" s="1">
         <v>46203</v>
       </c>
@@ -6104,7 +5951,7 @@
         <v>30</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="J45" s="3">
         <v>12817</v>
@@ -6113,57 +5960,55 @@
         <v>105272</v>
       </c>
       <c r="L45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="O45" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="P45" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O45" s="3" t="s">
+      <c r="Q45" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="P45" s="8" t="s">
+      <c r="R45" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="S45" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T45" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="Q45" s="8" t="s">
+      <c r="U45" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="V45" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W45" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="R45" s="8" t="s">
+      <c r="X45" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="8">
+        <v>7.6627729999999996</v>
+      </c>
+      <c r="AA45" s="8">
+        <v>12.329942000000001</v>
+      </c>
+      <c r="AB45" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="S45" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="T45" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U45" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="V45" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="W45" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X45" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y45" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="Z45" s="4"/>
-      <c r="AA45" s="8">
-        <v>7.6627729999999996</v>
-      </c>
-      <c r="AB45" s="8">
-        <v>12.329942000000001</v>
-      </c>
-      <c r="AC45" s="8" t="s">
-        <v>302</v>
-      </c>
+      <c r="AC45" s="4"/>
       <c r="AD45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AF45" s="4"/>
@@ -6172,9 +6017,8 @@
       <c r="AI45" s="4"/>
       <c r="AJ45" s="4"/>
       <c r="AK45" s="4"/>
-      <c r="AL45" s="4"/>
     </row>
-    <row r="46" spans="1:38" ht="44.25">
+    <row r="46" spans="1:37" ht="44.25">
       <c r="A46" s="1">
         <v>46203</v>
       </c>
@@ -6200,7 +6044,7 @@
         <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="J46" s="3">
         <v>11774</v>
@@ -6212,54 +6056,52 @@
         <v>126</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
+      </c>
+      <c r="O46" s="8" t="s">
+        <v>302</v>
       </c>
       <c r="P46" s="8" t="s">
-        <v>305</v>
+        <v>137</v>
       </c>
       <c r="Q46" s="8" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="R46" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="T46" s="8" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="U46" s="8" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="V46" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W46" s="8" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="X46" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y46" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="Z46" s="4"/>
+        <v>454</v>
+      </c>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="8">
+        <v>7.2786650000000002</v>
+      </c>
       <c r="AA46" s="8">
-        <v>7.2786650000000002</v>
-      </c>
-      <c r="AB46" s="8">
         <v>13.5462694</v>
       </c>
-      <c r="AC46" s="8" t="s">
-        <v>306</v>
-      </c>
+      <c r="AB46" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC46" s="4"/>
       <c r="AD46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AF46" s="4"/>
@@ -6268,9 +6110,8 @@
       <c r="AI46" s="4"/>
       <c r="AJ46" s="4"/>
       <c r="AK46" s="4"/>
-      <c r="AL46" s="4"/>
     </row>
-    <row r="47" spans="1:38" ht="44.25">
+    <row r="47" spans="1:37" ht="44.25">
       <c r="A47" s="1">
         <v>46203</v>
       </c>
@@ -6296,7 +6137,7 @@
         <v>30</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="J47" s="3">
         <v>10587</v>
@@ -6305,19 +6146,19 @@
         <v>100811</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>308</v>
+        <v>30</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
+      </c>
+      <c r="O47" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="P47" s="8" t="s">
-        <v>310</v>
+        <v>33</v>
       </c>
       <c r="Q47" s="8" t="s">
         <v>33</v>
@@ -6326,36 +6167,34 @@
         <v>33</v>
       </c>
       <c r="S47" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T47" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="U47" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="V47" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="T47" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U47" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="V47" s="8" t="s">
-        <v>312</v>
-      </c>
       <c r="W47" s="8" t="s">
-        <v>33</v>
+        <v>309</v>
       </c>
       <c r="X47" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="Y47" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z47" s="4"/>
+        <v>471</v>
+      </c>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="8" t="s">
+        <v>475</v>
+      </c>
       <c r="AA47" s="8" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AB47" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC47" s="8" t="s">
-        <v>314</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AC47" s="4"/>
       <c r="AD47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AF47" s="4"/>
@@ -6364,9 +6203,8 @@
       <c r="AI47" s="4"/>
       <c r="AJ47" s="4"/>
       <c r="AK47" s="4"/>
-      <c r="AL47" s="4"/>
     </row>
-    <row r="48" spans="1:38" ht="29.5">
+    <row r="48" spans="1:37" ht="29.5">
       <c r="A48" s="1">
         <v>46203</v>
       </c>
@@ -6392,7 +6230,7 @@
         <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="J48" s="3">
         <v>10587</v>
@@ -6401,57 +6239,55 @@
         <v>100811</v>
       </c>
       <c r="L48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="O48" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="P48" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q48" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="R48" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="S48" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T48" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="U48" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="P48" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q48" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="R48" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="S48" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="T48" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U48" s="8" t="s">
-        <v>311</v>
-      </c>
       <c r="V48" s="8" t="s">
-        <v>312</v>
+        <v>65</v>
       </c>
       <c r="W48" s="8" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="X48" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y48" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z48" s="4"/>
+        <v>471</v>
+      </c>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="8">
+        <v>3.9884092</v>
+      </c>
       <c r="AA48" s="8">
-        <v>3.9884092</v>
-      </c>
-      <c r="AB48" s="8">
         <v>13.171723699999999</v>
       </c>
-      <c r="AC48" s="8" t="s">
-        <v>456</v>
-      </c>
+      <c r="AB48" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="AC48" s="4"/>
       <c r="AD48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AF48" s="4"/>
@@ -6460,9 +6296,8 @@
       <c r="AI48" s="4"/>
       <c r="AJ48" s="4"/>
       <c r="AK48" s="4"/>
-      <c r="AL48" s="4"/>
     </row>
-    <row r="49" spans="1:38" ht="29.5">
+    <row r="49" spans="1:37" ht="29.5">
       <c r="A49" s="1">
         <v>46203</v>
       </c>
@@ -6488,7 +6323,7 @@
         <v>30</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J49" s="3">
         <v>10587</v>
@@ -6497,57 +6332,55 @@
         <v>100811</v>
       </c>
       <c r="L49" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="O49" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="P49" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q49" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="R49" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="S49" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T49" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="U49" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="P49" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q49" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="R49" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="S49" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="T49" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U49" s="8" t="s">
-        <v>311</v>
-      </c>
       <c r="V49" s="8" t="s">
-        <v>312</v>
+        <v>57</v>
       </c>
       <c r="W49" s="8" t="s">
-        <v>57</v>
+        <v>298</v>
       </c>
       <c r="X49" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y49" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z49" s="4"/>
+        <v>471</v>
+      </c>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="8">
+        <v>4.5496980999999996</v>
+      </c>
       <c r="AA49" s="8">
-        <v>4.5496980999999996</v>
-      </c>
-      <c r="AB49" s="8">
         <v>13.7259359</v>
       </c>
-      <c r="AC49" s="8" t="s">
-        <v>321</v>
-      </c>
+      <c r="AB49" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="AC49" s="4"/>
       <c r="AD49" s="4"/>
       <c r="AE49" s="4"/>
       <c r="AF49" s="4"/>
@@ -6556,9 +6389,8 @@
       <c r="AI49" s="4"/>
       <c r="AJ49" s="4"/>
       <c r="AK49" s="4"/>
-      <c r="AL49" s="4"/>
     </row>
-    <row r="50" spans="1:38" ht="44.25">
+    <row r="50" spans="1:37" ht="44.25">
       <c r="A50" s="1">
         <v>46203</v>
       </c>
@@ -6584,7 +6416,7 @@
         <v>30</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J50" s="3">
         <v>10587</v>
@@ -6593,57 +6425,55 @@
         <v>100811</v>
       </c>
       <c r="L50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="O50" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="P50" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q50" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="R50" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="S50" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T50" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="U50" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="M50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O50" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="P50" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q50" s="8" t="s">
+      <c r="V50" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="R50" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="S50" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="T50" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U50" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="V50" s="8" t="s">
-        <v>312</v>
-      </c>
       <c r="W50" s="8" t="s">
-        <v>33</v>
+        <v>190</v>
       </c>
       <c r="X50" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y50" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z50" s="4"/>
+        <v>471</v>
+      </c>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="8" t="s">
+        <v>475</v>
+      </c>
       <c r="AA50" s="8" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AB50" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC50" s="8" t="s">
-        <v>325</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="AC50" s="4"/>
       <c r="AD50" s="4"/>
       <c r="AE50" s="4"/>
       <c r="AF50" s="4"/>
@@ -6652,9 +6482,8 @@
       <c r="AI50" s="4"/>
       <c r="AJ50" s="4"/>
       <c r="AK50" s="4"/>
-      <c r="AL50" s="4"/>
     </row>
-    <row r="51" spans="1:38" ht="44.25">
+    <row r="51" spans="1:37" ht="44.25">
       <c r="A51" s="1">
         <v>46203</v>
       </c>
@@ -6680,7 +6509,7 @@
         <v>30</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="J51" s="3">
         <v>10587</v>
@@ -6689,57 +6518,55 @@
         <v>100811</v>
       </c>
       <c r="L51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="O51" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="P51" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q51" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="R51" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="S51" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T51" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="U51" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="M51" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O51" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="P51" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q51" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="R51" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="S51" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="T51" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U51" s="8" t="s">
-        <v>311</v>
-      </c>
       <c r="V51" s="8" t="s">
-        <v>312</v>
+        <v>45</v>
       </c>
       <c r="W51" s="8" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="X51" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y51" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z51" s="4"/>
+        <v>471</v>
+      </c>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="8">
+        <v>4.0210837000000001</v>
+      </c>
       <c r="AA51" s="8">
-        <v>4.0210837000000001</v>
-      </c>
-      <c r="AB51" s="8">
         <v>14.1033954</v>
       </c>
-      <c r="AC51" s="8" t="s">
-        <v>330</v>
-      </c>
+      <c r="AB51" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC51" s="4"/>
       <c r="AD51" s="4"/>
       <c r="AE51" s="4"/>
       <c r="AF51" s="4"/>
@@ -6748,9 +6575,8 @@
       <c r="AI51" s="4"/>
       <c r="AJ51" s="4"/>
       <c r="AK51" s="4"/>
-      <c r="AL51" s="4"/>
     </row>
-    <row r="52" spans="1:38" ht="29.5">
+    <row r="52" spans="1:37" ht="29.5">
       <c r="A52" s="1">
         <v>46203</v>
       </c>
@@ -6776,7 +6602,7 @@
         <v>30</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J52" s="3">
         <v>10587</v>
@@ -6785,57 +6611,55 @@
         <v>100811</v>
       </c>
       <c r="L52" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="O52" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="P52" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q52" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="R52" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="S52" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T52" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="U52" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="P52" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q52" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="R52" s="8" t="s">
+      <c r="V52" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W52" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="X52" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="8">
+        <v>4.0210837000000001</v>
+      </c>
+      <c r="AA52" s="8">
+        <v>14.1033954</v>
+      </c>
+      <c r="AB52" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="S52" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="T52" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U52" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="V52" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="W52" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X52" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y52" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z52" s="4"/>
-      <c r="AA52" s="8">
-        <v>4.0210837000000001</v>
-      </c>
-      <c r="AB52" s="8">
-        <v>14.1033954</v>
-      </c>
-      <c r="AC52" s="8" t="s">
-        <v>333</v>
-      </c>
+      <c r="AC52" s="4"/>
       <c r="AD52" s="4"/>
       <c r="AE52" s="4"/>
       <c r="AF52" s="4"/>
@@ -6844,9 +6668,8 @@
       <c r="AI52" s="4"/>
       <c r="AJ52" s="4"/>
       <c r="AK52" s="4"/>
-      <c r="AL52" s="4"/>
     </row>
-    <row r="53" spans="1:38" ht="29.5">
+    <row r="53" spans="1:37" ht="29.5">
       <c r="A53" s="1">
         <v>46203</v>
       </c>
@@ -6872,7 +6695,7 @@
         <v>30</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="J53" s="3">
         <v>10587</v>
@@ -6881,57 +6704,55 @@
         <v>100811</v>
       </c>
       <c r="L53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="O53" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="P53" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q53" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="R53" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="S53" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T53" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="U53" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="M53" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="P53" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q53" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="R53" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="S53" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="T53" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U53" s="8" t="s">
-        <v>311</v>
-      </c>
       <c r="V53" s="8" t="s">
-        <v>312</v>
+        <v>45</v>
       </c>
       <c r="W53" s="8" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="X53" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y53" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z53" s="4"/>
+        <v>471</v>
+      </c>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="8">
+        <v>9.7269120000000004</v>
+      </c>
       <c r="AA53" s="8">
-        <v>9.7269120000000004</v>
-      </c>
-      <c r="AB53" s="8">
         <v>13.997469799999999</v>
       </c>
-      <c r="AC53" s="8" t="s">
-        <v>338</v>
-      </c>
+      <c r="AB53" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="AC53" s="4"/>
       <c r="AD53" s="4"/>
       <c r="AE53" s="4"/>
       <c r="AF53" s="4"/>
@@ -6940,9 +6761,8 @@
       <c r="AI53" s="4"/>
       <c r="AJ53" s="4"/>
       <c r="AK53" s="4"/>
-      <c r="AL53" s="4"/>
     </row>
-    <row r="54" spans="1:38" ht="29.5">
+    <row r="54" spans="1:37" ht="29.5">
       <c r="A54" s="1">
         <v>46203</v>
       </c>
@@ -6968,7 +6788,7 @@
         <v>30</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="J54" s="3">
         <v>10587</v>
@@ -6977,57 +6797,55 @@
         <v>100811</v>
       </c>
       <c r="L54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="O54" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="P54" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q54" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="R54" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="S54" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T54" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="U54" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="P54" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q54" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="R54" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="S54" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="T54" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U54" s="8" t="s">
-        <v>311</v>
-      </c>
       <c r="V54" s="8" t="s">
-        <v>312</v>
+        <v>45</v>
       </c>
       <c r="W54" s="8" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="X54" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y54" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z54" s="4"/>
+        <v>471</v>
+      </c>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="8">
+        <v>2.6165007</v>
+      </c>
       <c r="AA54" s="8">
-        <v>2.6165007</v>
-      </c>
-      <c r="AB54" s="8">
         <v>15.3808624</v>
       </c>
-      <c r="AC54" s="8" t="s">
-        <v>342</v>
-      </c>
+      <c r="AB54" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="AC54" s="4"/>
       <c r="AD54" s="4"/>
       <c r="AE54" s="4"/>
       <c r="AF54" s="4"/>
@@ -7036,9 +6854,8 @@
       <c r="AI54" s="4"/>
       <c r="AJ54" s="4"/>
       <c r="AK54" s="4"/>
-      <c r="AL54" s="4"/>
     </row>
-    <row r="55" spans="1:38" ht="44.25">
+    <row r="55" spans="1:37" ht="44.25">
       <c r="A55" s="1">
         <v>46203</v>
       </c>
@@ -7064,7 +6881,7 @@
         <v>30</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J55" s="3">
         <v>10587</v>
@@ -7073,57 +6890,55 @@
         <v>100811</v>
       </c>
       <c r="L55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="O55" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="P55" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q55" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="R55" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="S55" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T55" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="U55" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="M55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O55" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="P55" s="8" t="s">
+      <c r="V55" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W55" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="X55" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="8">
+        <v>2.6165007</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>15.3808624</v>
+      </c>
+      <c r="AB55" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="Q55" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="R55" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="S55" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="T55" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U55" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="V55" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="W55" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X55" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y55" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z55" s="4"/>
-      <c r="AA55" s="8">
-        <v>2.6165007</v>
-      </c>
-      <c r="AB55" s="8">
-        <v>15.3808624</v>
-      </c>
-      <c r="AC55" s="8" t="s">
-        <v>344</v>
-      </c>
+      <c r="AC55" s="4"/>
       <c r="AD55" s="4"/>
       <c r="AE55" s="4"/>
       <c r="AF55" s="4"/>
@@ -7132,9 +6947,8 @@
       <c r="AI55" s="4"/>
       <c r="AJ55" s="4"/>
       <c r="AK55" s="4"/>
-      <c r="AL55" s="4"/>
     </row>
-    <row r="56" spans="1:38" ht="29.5">
+    <row r="56" spans="1:37" ht="29.5">
       <c r="A56" s="1">
         <v>46203</v>
       </c>
@@ -7160,7 +6974,7 @@
         <v>30</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="J56" s="3">
         <v>10587</v>
@@ -7169,57 +6983,55 @@
         <v>100811</v>
       </c>
       <c r="L56" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="O56" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="P56" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q56" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="R56" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="S56" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T56" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="U56" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="M56" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O56" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="P56" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q56" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="R56" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="S56" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="T56" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U56" s="8" t="s">
-        <v>311</v>
-      </c>
       <c r="V56" s="8" t="s">
-        <v>312</v>
+        <v>65</v>
       </c>
       <c r="W56" s="8" t="s">
-        <v>65</v>
+        <v>298</v>
       </c>
       <c r="X56" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y56" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="Z56" s="4"/>
+        <v>471</v>
+      </c>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="8">
+        <v>3.5152789000000002</v>
+      </c>
       <c r="AA56" s="8">
-        <v>3.5152789000000002</v>
-      </c>
-      <c r="AB56" s="8">
         <v>15.0510331</v>
       </c>
-      <c r="AC56" s="8" t="s">
-        <v>347</v>
-      </c>
+      <c r="AB56" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="AC56" s="4"/>
       <c r="AD56" s="4"/>
       <c r="AE56" s="4"/>
       <c r="AF56" s="4"/>
@@ -7228,9 +7040,8 @@
       <c r="AI56" s="4"/>
       <c r="AJ56" s="4"/>
       <c r="AK56" s="4"/>
-      <c r="AL56" s="4"/>
     </row>
-    <row r="57" spans="1:38" ht="29.5">
+    <row r="57" spans="1:37" ht="29.5">
       <c r="A57" s="1">
         <v>46203</v>
       </c>
@@ -7256,7 +7067,7 @@
         <v>30</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="J57" s="3">
         <v>14602</v>
@@ -7265,17 +7076,17 @@
         <v>108460</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>348</v>
+        <v>30</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N57" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="P57" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q57" s="8" t="s">
         <v>33</v>
@@ -7284,36 +7095,34 @@
         <v>33</v>
       </c>
       <c r="S57" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T57" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U57" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="T57" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U57" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="V57" s="8" t="s">
         <v>33</v>
       </c>
       <c r="W57" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="X57" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y57" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="Z57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="8" t="s">
+        <v>475</v>
+      </c>
       <c r="AA57" s="8" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AB57" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC57" s="8" t="s">
-        <v>349</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="AC57" s="4"/>
       <c r="AD57" s="4"/>
       <c r="AE57" s="4"/>
       <c r="AF57" s="4"/>
@@ -7322,9 +7131,8 @@
       <c r="AI57" s="4"/>
       <c r="AJ57" s="4"/>
       <c r="AK57" s="4"/>
-      <c r="AL57" s="4"/>
     </row>
-    <row r="58" spans="1:38" ht="29.5">
+    <row r="58" spans="1:37" ht="29.5">
       <c r="A58" s="1">
         <v>46203</v>
       </c>
@@ -7350,7 +7158,7 @@
         <v>30</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J58" s="3">
         <v>14762</v>
@@ -7359,55 +7167,53 @@
         <v>108710</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>350</v>
+        <v>30</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O58" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="O58" s="8" t="s">
+        <v>172</v>
+      </c>
       <c r="P58" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Q58" s="8" t="s">
-        <v>174</v>
+        <v>53</v>
       </c>
       <c r="R58" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S58" s="8" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="T58" s="8" t="s">
-        <v>34</v>
+        <v>347</v>
       </c>
       <c r="U58" s="8" t="s">
-        <v>351</v>
+        <v>189</v>
       </c>
       <c r="V58" s="8" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="W58" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X58" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="Y58" s="8"/>
-      <c r="Z58" s="4"/>
+      <c r="X58" s="8"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="8">
+        <v>11.780627000000001</v>
+      </c>
       <c r="AA58" s="8">
-        <v>11.780627000000001</v>
-      </c>
-      <c r="AB58" s="8">
         <v>15.103911999999999</v>
       </c>
-      <c r="AC58" s="8" t="s">
-        <v>352</v>
-      </c>
+      <c r="AB58" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="AC58" s="4"/>
       <c r="AD58" s="4"/>
       <c r="AE58" s="4"/>
       <c r="AF58" s="4"/>
@@ -7416,9 +7222,8 @@
       <c r="AI58" s="4"/>
       <c r="AJ58" s="4"/>
       <c r="AK58" s="4"/>
-      <c r="AL58" s="4"/>
     </row>
-    <row r="59" spans="1:38" ht="73.75">
+    <row r="59" spans="1:37" ht="73.75">
       <c r="A59" s="1">
         <v>46203</v>
       </c>
@@ -7444,7 +7249,7 @@
         <v>30</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="J59" s="3">
         <v>11083</v>
@@ -7453,55 +7258,53 @@
         <v>101859</v>
       </c>
       <c r="L59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="O59" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="P59" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q59" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="R59" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S59" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T59" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="U59" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O59" s="3" t="s">
+      <c r="V59" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W59" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X59" s="8"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="8">
+        <v>5.9614117000000002</v>
+      </c>
+      <c r="AA59" s="8">
+        <v>10.151650500000001</v>
+      </c>
+      <c r="AB59" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="P59" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q59" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="R59" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="S59" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T59" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U59" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="V59" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="W59" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="X59" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y59" s="8"/>
-      <c r="Z59" s="4"/>
-      <c r="AA59" s="8">
-        <v>5.9614117000000002</v>
-      </c>
-      <c r="AB59" s="8">
-        <v>10.151650500000001</v>
-      </c>
-      <c r="AC59" s="8" t="s">
-        <v>360</v>
-      </c>
+      <c r="AC59" s="4"/>
       <c r="AD59" s="4"/>
       <c r="AE59" s="4"/>
       <c r="AF59" s="4"/>
@@ -7510,9 +7313,8 @@
       <c r="AI59" s="4"/>
       <c r="AJ59" s="4"/>
       <c r="AK59" s="4"/>
-      <c r="AL59" s="4"/>
     </row>
-    <row r="60" spans="1:38" ht="29.5">
+    <row r="60" spans="1:37" ht="29.5">
       <c r="A60" s="1">
         <v>46203</v>
       </c>
@@ -7538,7 +7340,7 @@
         <v>30</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="J60" s="3">
         <v>11558</v>
@@ -7547,53 +7349,51 @@
         <v>102609</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N60" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="8" t="s">
+        <v>356</v>
+      </c>
       <c r="P60" s="8" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="Q60" s="8" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="R60" s="8" t="s">
-        <v>362</v>
+        <v>183</v>
       </c>
       <c r="S60" s="8" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="T60" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U60" s="8" t="s">
         <v>33</v>
       </c>
       <c r="V60" s="8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="W60" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X60" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="Y60" s="8"/>
-      <c r="Z60" s="4"/>
+      <c r="X60" s="8"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="8">
+        <v>8.3994900000000001</v>
+      </c>
       <c r="AA60" s="8">
-        <v>8.3994900000000001</v>
-      </c>
-      <c r="AB60" s="8">
         <v>14.16816</v>
       </c>
-      <c r="AC60" s="8" t="s">
-        <v>363</v>
-      </c>
+      <c r="AB60" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="AC60" s="4"/>
       <c r="AD60" s="4"/>
       <c r="AE60" s="4"/>
       <c r="AF60" s="4"/>
@@ -7602,9 +7402,8 @@
       <c r="AI60" s="4"/>
       <c r="AJ60" s="4"/>
       <c r="AK60" s="4"/>
-      <c r="AL60" s="4"/>
     </row>
-    <row r="61" spans="1:38" ht="59">
+    <row r="61" spans="1:37" ht="59">
       <c r="A61" s="1">
         <v>46203</v>
       </c>
@@ -7630,7 +7429,7 @@
         <v>30</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="J61" s="3">
         <v>15614</v>
@@ -7639,57 +7438,55 @@
         <v>110241</v>
       </c>
       <c r="L61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="O61" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="P61" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q61" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="R61" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S61" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T61" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="M61" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O61" s="3" t="s">
+      <c r="U61" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="P61" s="8" t="s">
+      <c r="V61" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W61" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X61" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="8">
+        <v>10.116539700000001</v>
+      </c>
+      <c r="AA61" s="8">
+        <v>14.9712175</v>
+      </c>
+      <c r="AB61" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="Q61" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="R61" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="S61" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T61" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U61" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="V61" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="W61" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X61" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y61" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="Z61" s="4"/>
-      <c r="AA61" s="8">
-        <v>10.116539700000001</v>
-      </c>
-      <c r="AB61" s="8">
-        <v>14.9712175</v>
-      </c>
-      <c r="AC61" s="8" t="s">
-        <v>371</v>
-      </c>
+      <c r="AC61" s="4"/>
       <c r="AD61" s="4"/>
       <c r="AE61" s="4"/>
       <c r="AF61" s="4"/>
@@ -7698,9 +7495,8 @@
       <c r="AI61" s="4"/>
       <c r="AJ61" s="4"/>
       <c r="AK61" s="4"/>
-      <c r="AL61" s="4"/>
     </row>
-    <row r="62" spans="1:38" ht="59">
+    <row r="62" spans="1:37" ht="59">
       <c r="A62" s="1">
         <v>46203</v>
       </c>
@@ -7726,7 +7522,7 @@
         <v>30</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="J62" s="3">
         <v>11083</v>
@@ -7735,55 +7531,53 @@
         <v>101859</v>
       </c>
       <c r="L62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="O62" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="P62" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q62" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="R62" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S62" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T62" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="U62" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="P62" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q62" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="R62" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="S62" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T62" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U62" s="8" t="s">
-        <v>358</v>
-      </c>
       <c r="V62" s="8" t="s">
-        <v>359</v>
+        <v>57</v>
       </c>
       <c r="W62" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="X62" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="Y62" s="8"/>
-      <c r="Z62" s="4"/>
+      <c r="X62" s="8"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="8">
+        <v>5.9614117000000002</v>
+      </c>
       <c r="AA62" s="8">
-        <v>5.9614117000000002</v>
-      </c>
-      <c r="AB62" s="8">
         <v>10.151650500000001</v>
       </c>
-      <c r="AC62" s="8" t="s">
-        <v>374</v>
-      </c>
+      <c r="AB62" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="AC62" s="4"/>
       <c r="AD62" s="4"/>
       <c r="AE62" s="4"/>
       <c r="AF62" s="4"/>
@@ -7792,9 +7586,8 @@
       <c r="AI62" s="4"/>
       <c r="AJ62" s="4"/>
       <c r="AK62" s="4"/>
-      <c r="AL62" s="4"/>
     </row>
-    <row r="63" spans="1:38" ht="59">
+    <row r="63" spans="1:37" ht="59">
       <c r="A63" s="1">
         <v>46203</v>
       </c>
@@ -7820,7 +7613,7 @@
         <v>30</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="J63" s="3">
         <v>11083</v>
@@ -7829,55 +7622,53 @@
         <v>101859</v>
       </c>
       <c r="L63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="O63" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="P63" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q63" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="R63" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S63" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T63" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="U63" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="M63" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O63" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="P63" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q63" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="R63" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="S63" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T63" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U63" s="8" t="s">
-        <v>358</v>
-      </c>
       <c r="V63" s="8" t="s">
-        <v>359</v>
+        <v>57</v>
       </c>
       <c r="W63" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="X63" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="Y63" s="8"/>
-      <c r="Z63" s="4"/>
+      <c r="X63" s="8"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="8">
+        <v>5.9614117000000002</v>
+      </c>
       <c r="AA63" s="8">
-        <v>5.9614117000000002</v>
-      </c>
-      <c r="AB63" s="8">
         <v>10.151650500000001</v>
       </c>
-      <c r="AC63" s="8" t="s">
-        <v>376</v>
-      </c>
+      <c r="AB63" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="AC63" s="4"/>
       <c r="AD63" s="4"/>
       <c r="AE63" s="4"/>
       <c r="AF63" s="4"/>
@@ -7886,9 +7677,8 @@
       <c r="AI63" s="4"/>
       <c r="AJ63" s="4"/>
       <c r="AK63" s="4"/>
-      <c r="AL63" s="4"/>
     </row>
-    <row r="64" spans="1:38" ht="44.25">
+    <row r="64" spans="1:37" ht="44.25">
       <c r="A64" s="1">
         <v>46203</v>
       </c>
@@ -7914,62 +7704,60 @@
         <v>30</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="O64" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="P64" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q64" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="R64" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S64" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T64" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="U64" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="M64" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O64" s="3" t="s">
+      <c r="V64" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W64" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="X64" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="P64" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q64" s="8" t="s">
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="8">
+        <v>6.0845586999999997</v>
+      </c>
+      <c r="AA64" s="8">
+        <v>10.638270800000001</v>
+      </c>
+      <c r="AB64" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="R64" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="S64" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T64" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U64" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="V64" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="W64" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X64" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y64" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="Z64" s="4"/>
-      <c r="AA64" s="8">
-        <v>6.0845586999999997</v>
-      </c>
-      <c r="AB64" s="8">
-        <v>10.638270800000001</v>
-      </c>
-      <c r="AC64" s="8" t="s">
-        <v>384</v>
-      </c>
+      <c r="AC64" s="4"/>
       <c r="AD64" s="4"/>
       <c r="AE64" s="4"/>
       <c r="AF64" s="4"/>
@@ -7978,9 +7766,8 @@
       <c r="AI64" s="4"/>
       <c r="AJ64" s="4"/>
       <c r="AK64" s="4"/>
-      <c r="AL64" s="4"/>
     </row>
-    <row r="65" spans="1:38" ht="29.5">
+    <row r="65" spans="1:37" ht="29.5">
       <c r="A65" s="1">
         <v>46203</v>
       </c>
@@ -8006,7 +7793,7 @@
         <v>30</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="J65" s="3">
         <v>15397</v>
@@ -8015,57 +7802,55 @@
         <v>110825</v>
       </c>
       <c r="L65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="O65" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="P65" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q65" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="R65" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S65" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T65" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="U65" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="V65" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="W65" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="X65" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="8">
+        <v>5.9462650000000004</v>
+      </c>
+      <c r="AA65" s="8">
+        <v>9.6904461000000008</v>
+      </c>
+      <c r="AB65" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="M65" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O65" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="P65" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q65" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="R65" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="S65" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T65" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U65" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="V65" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="W65" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="X65" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y65" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="Z65" s="4"/>
-      <c r="AA65" s="8">
-        <v>5.9462650000000004</v>
-      </c>
-      <c r="AB65" s="8">
-        <v>9.6904461000000008</v>
-      </c>
-      <c r="AC65" s="8" t="s">
-        <v>390</v>
-      </c>
+      <c r="AC65" s="4"/>
       <c r="AD65" s="4"/>
       <c r="AE65" s="4"/>
       <c r="AF65" s="4"/>
@@ -8074,9 +7859,8 @@
       <c r="AI65" s="4"/>
       <c r="AJ65" s="4"/>
       <c r="AK65" s="4"/>
-      <c r="AL65" s="4"/>
     </row>
-    <row r="66" spans="1:38" ht="29.5">
+    <row r="66" spans="1:37" ht="29.5">
       <c r="A66" s="1">
         <v>46203</v>
       </c>
@@ -8102,7 +7886,7 @@
         <v>30</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="J66" s="3">
         <v>16111</v>
@@ -8111,55 +7895,53 @@
         <v>111192</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>391</v>
+        <v>30</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O66" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O66" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="P66" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q66" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="P66" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q66" s="8" t="s">
-        <v>215</v>
-      </c>
       <c r="R66" s="8" t="s">
-        <v>216</v>
+        <v>115</v>
       </c>
       <c r="S66" s="8" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="T66" s="8" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="U66" s="8" t="s">
-        <v>392</v>
+        <v>189</v>
       </c>
       <c r="V66" s="8" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="W66" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X66" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="Y66" s="8"/>
-      <c r="Z66" s="4"/>
+      <c r="X66" s="8"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="8">
+        <v>4.8673555000000004</v>
+      </c>
       <c r="AA66" s="8">
-        <v>4.8673555000000004</v>
-      </c>
-      <c r="AB66" s="8">
         <v>11.156444</v>
       </c>
-      <c r="AC66" s="8" t="s">
-        <v>393</v>
-      </c>
+      <c r="AB66" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="AC66" s="4"/>
       <c r="AD66" s="4"/>
       <c r="AE66" s="4"/>
       <c r="AF66" s="4"/>
@@ -8168,9 +7950,8 @@
       <c r="AI66" s="4"/>
       <c r="AJ66" s="4"/>
       <c r="AK66" s="4"/>
-      <c r="AL66" s="4"/>
     </row>
-    <row r="67" spans="1:38" ht="44.25">
+    <row r="67" spans="1:37" ht="44.25">
       <c r="A67" s="7">
         <v>46203</v>
       </c>
@@ -8194,7 +7975,7 @@
         <v>30</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="J67" s="4">
         <v>10587</v>
@@ -8203,57 +7984,55 @@
         <v>100811</v>
       </c>
       <c r="L67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="O67" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="P67" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q67" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="R67" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="S67" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T67" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="U67" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="V67" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W67" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="X67" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="8">
+        <v>3.0779049000000001</v>
+      </c>
+      <c r="AA67" s="8">
+        <v>10.4112806</v>
+      </c>
+      <c r="AB67" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="M67" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="P67" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q67" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="R67" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="S67" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="T67" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U67" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="V67" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="W67" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X67" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="Y67" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="Z67" s="4"/>
-      <c r="AA67" s="8">
-        <v>3.0779049000000001</v>
-      </c>
-      <c r="AB67" s="8">
-        <v>10.4112806</v>
-      </c>
-      <c r="AC67" s="8" t="s">
-        <v>401</v>
-      </c>
+      <c r="AC67" s="4"/>
       <c r="AD67" s="4"/>
       <c r="AE67" s="4"/>
       <c r="AF67" s="4"/>
@@ -8262,9 +8041,8 @@
       <c r="AI67" s="4"/>
       <c r="AJ67" s="4"/>
       <c r="AK67" s="4"/>
-      <c r="AL67" s="4"/>
     </row>
-    <row r="68" spans="1:38" ht="44.25">
+    <row r="68" spans="1:37" ht="44.25">
       <c r="A68" s="7">
         <v>46203</v>
       </c>
@@ -8288,7 +8066,7 @@
         <v>30</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="J68" s="4">
         <v>10587</v>
@@ -8297,57 +8075,55 @@
         <v>100811</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>395</v>
+        <v>30</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O68" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="O68" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="P68" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q68" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="R68" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="S68" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T68" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="U68" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="V68" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W68" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="P68" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="Q68" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="R68" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="S68" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="T68" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U68" s="8" t="s">
+      <c r="X68" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="8">
+        <v>3.2340753000000002</v>
+      </c>
+      <c r="AA68" s="8">
+        <v>10.727964099999999</v>
+      </c>
+      <c r="AB68" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="V68" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="W68" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X68" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="Y68" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="Z68" s="4"/>
-      <c r="AA68" s="8">
-        <v>3.2340753000000002</v>
-      </c>
-      <c r="AB68" s="8">
-        <v>10.727964099999999</v>
-      </c>
-      <c r="AC68" s="8" t="s">
-        <v>405</v>
-      </c>
+      <c r="AC68" s="4"/>
       <c r="AD68" s="4"/>
       <c r="AE68" s="4"/>
       <c r="AF68" s="4"/>
@@ -8356,9 +8132,8 @@
       <c r="AI68" s="4"/>
       <c r="AJ68" s="4"/>
       <c r="AK68" s="4"/>
-      <c r="AL68" s="4"/>
     </row>
-    <row r="69" spans="1:38" ht="44.25">
+    <row r="69" spans="1:37" ht="44.25">
       <c r="A69" s="7">
         <v>46203</v>
       </c>
@@ -8382,7 +8157,7 @@
         <v>30</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="J69" s="4">
         <v>10587</v>
@@ -8391,57 +8166,55 @@
         <v>100811</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>395</v>
+        <v>30</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O69" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="O69" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="P69" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="Q69" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="R69" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="S69" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T69" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="U69" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="V69" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W69" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="P69" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="Q69" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="R69" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="S69" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="T69" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U69" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="V69" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="W69" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="X69" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="Y69" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="Z69" s="4"/>
+        <v>394</v>
+      </c>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="8">
+        <v>2.9434098</v>
+      </c>
       <c r="AA69" s="8">
-        <v>2.9434098</v>
-      </c>
-      <c r="AB69" s="8">
         <v>9.9126989000000005</v>
       </c>
-      <c r="AC69" s="8" t="s">
-        <v>409</v>
-      </c>
+      <c r="AB69" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="AC69" s="4"/>
       <c r="AD69" s="4"/>
       <c r="AE69" s="4"/>
       <c r="AF69" s="4"/>
@@ -8450,9 +8223,8 @@
       <c r="AI69" s="4"/>
       <c r="AJ69" s="4"/>
       <c r="AK69" s="4"/>
-      <c r="AL69" s="4"/>
     </row>
-    <row r="70" spans="1:38" ht="44.25">
+    <row r="70" spans="1:37" ht="44.25">
       <c r="A70" s="7">
         <v>46203</v>
       </c>
@@ -8476,7 +8248,7 @@
         <v>30</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="J70" s="4">
         <v>10618</v>
@@ -8484,58 +8256,56 @@
       <c r="K70" s="4">
         <v>100926</v>
       </c>
-      <c r="L70" s="4" t="s">
-        <v>410</v>
+      <c r="L70" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N70" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O70" s="4" t="s">
-        <v>411</v>
+      <c r="N70" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="O70" s="8" t="s">
+        <v>404</v>
       </c>
       <c r="P70" s="8" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="Q70" s="8" t="s">
-        <v>412</v>
+        <v>62</v>
       </c>
       <c r="R70" s="8" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="S70" s="8" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="T70" s="8" t="s">
-        <v>34</v>
+        <v>407</v>
       </c>
       <c r="U70" s="8" t="s">
-        <v>413</v>
+        <v>44</v>
       </c>
       <c r="V70" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="W70" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="X70" s="8">
+      <c r="W70" s="8">
         <v>2026</v>
       </c>
-      <c r="Y70" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="Z70" s="4"/>
+      <c r="X70" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="8">
+        <v>6.0384487</v>
+      </c>
       <c r="AA70" s="8">
-        <v>6.0384487</v>
-      </c>
-      <c r="AB70" s="8">
         <v>10.2907876</v>
       </c>
-      <c r="AC70" s="8" t="s">
-        <v>415</v>
-      </c>
+      <c r="AB70" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC70" s="4"/>
       <c r="AD70" s="4"/>
       <c r="AE70" s="4"/>
       <c r="AF70" s="4"/>
@@ -8544,9 +8314,8 @@
       <c r="AI70" s="4"/>
       <c r="AJ70" s="4"/>
       <c r="AK70" s="4"/>
-      <c r="AL70" s="4"/>
     </row>
-    <row r="71" spans="1:38" ht="73.75">
+    <row r="71" spans="1:37" ht="73.75">
       <c r="A71" s="7">
         <v>46203</v>
       </c>
@@ -8570,7 +8339,7 @@
         <v>30</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="J71" s="4">
         <v>11460</v>
@@ -8579,57 +8348,55 @@
         <v>102351</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>417</v>
+        <v>30</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O71" s="3" t="s">
-        <v>418</v>
+        <v>412</v>
+      </c>
+      <c r="O71" s="8" t="s">
+        <v>413</v>
       </c>
       <c r="P71" s="8" t="s">
-        <v>419</v>
+        <v>33</v>
       </c>
       <c r="Q71" s="8" t="s">
         <v>33</v>
       </c>
       <c r="R71" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="S71" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T71" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="U71" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="V71" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S71" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="T71" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U71" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="V71" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="W71" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="X71" s="8">
+      <c r="W71" s="8">
         <v>2026</v>
       </c>
-      <c r="Y71" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="Z71" s="4"/>
+      <c r="X71" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="8" t="s">
+        <v>475</v>
+      </c>
       <c r="AA71" s="8" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AB71" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC71" s="8" t="s">
-        <v>421</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="AC71" s="4"/>
       <c r="AD71" s="4"/>
       <c r="AE71" s="4"/>
       <c r="AF71" s="4"/>
@@ -8638,9 +8405,8 @@
       <c r="AI71" s="4"/>
       <c r="AJ71" s="4"/>
       <c r="AK71" s="4"/>
-      <c r="AL71" s="4"/>
     </row>
-    <row r="72" spans="1:38" ht="44.25">
+    <row r="72" spans="1:37" ht="44.25">
       <c r="A72" s="7">
         <v>46203</v>
       </c>
@@ -8664,62 +8430,60 @@
         <v>30</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
-      <c r="L72" s="4" t="s">
-        <v>422</v>
+      <c r="L72" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N72" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O72" s="4" t="s">
+      <c r="N72" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="O72" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="P72" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q72" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="P72" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q72" s="8" t="s">
-        <v>215</v>
-      </c>
       <c r="R72" s="8" t="s">
-        <v>216</v>
+        <v>115</v>
       </c>
       <c r="S72" s="8" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="T72" s="8" t="s">
-        <v>34</v>
+        <v>417</v>
       </c>
       <c r="U72" s="8" t="s">
-        <v>423</v>
+        <v>189</v>
       </c>
       <c r="V72" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="W72" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="X72" s="8">
+      <c r="W72" s="8">
         <v>2026</v>
       </c>
-      <c r="Y72" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="Z72" s="4"/>
+      <c r="X72" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="8">
+        <v>4.8673555000000004</v>
+      </c>
       <c r="AA72" s="8">
-        <v>4.8673555000000004</v>
-      </c>
-      <c r="AB72" s="8">
         <v>11.156444</v>
       </c>
-      <c r="AC72" s="8" t="s">
-        <v>424</v>
-      </c>
+      <c r="AB72" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="AC72" s="4"/>
       <c r="AD72" s="4"/>
       <c r="AE72" s="4"/>
       <c r="AF72" s="4"/>
@@ -8728,9 +8492,8 @@
       <c r="AI72" s="4"/>
       <c r="AJ72" s="4"/>
       <c r="AK72" s="4"/>
-      <c r="AL72" s="4"/>
     </row>
-    <row r="73" spans="1:38" ht="29.5">
+    <row r="73" spans="1:37" ht="29.5">
       <c r="A73" s="7">
         <v>46203</v>
       </c>
@@ -8754,7 +8517,7 @@
         <v>30</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="J73" s="4">
         <v>16111</v>
@@ -8762,58 +8525,56 @@
       <c r="K73">
         <v>111192</v>
       </c>
-      <c r="L73" s="4" t="s">
-        <v>425</v>
+      <c r="L73" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N73" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O73" s="4" t="s">
+      <c r="N73" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="O73" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="P73" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q73" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="P73" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q73" s="8" t="s">
-        <v>215</v>
-      </c>
       <c r="R73" s="8" t="s">
-        <v>216</v>
+        <v>115</v>
       </c>
       <c r="S73" s="8" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="T73" s="8" t="s">
-        <v>34</v>
+        <v>417</v>
       </c>
       <c r="U73" s="8" t="s">
-        <v>423</v>
+        <v>189</v>
       </c>
       <c r="V73" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="W73" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="X73" s="8">
+      <c r="W73" s="8">
         <v>2026</v>
       </c>
-      <c r="Y73" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="Z73" s="4"/>
+      <c r="X73" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="8">
+        <v>4.8673555000000004</v>
+      </c>
       <c r="AA73" s="8">
-        <v>4.8673555000000004</v>
-      </c>
-      <c r="AB73" s="8">
         <v>11.156444</v>
       </c>
-      <c r="AC73" s="8" t="s">
-        <v>426</v>
-      </c>
+      <c r="AB73" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="AC73" s="4"/>
       <c r="AD73" s="4"/>
       <c r="AE73" s="4"/>
       <c r="AF73" s="4"/>
@@ -8822,9 +8583,8 @@
       <c r="AI73" s="4"/>
       <c r="AJ73" s="4"/>
       <c r="AK73" s="4"/>
-      <c r="AL73" s="4"/>
     </row>
-    <row r="74" spans="1:38" ht="73.75">
+    <row r="74" spans="1:37" ht="73.75">
       <c r="A74" s="7">
         <v>46203</v>
       </c>
@@ -8848,60 +8608,58 @@
         <v>30</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
-      <c r="L74" s="4" t="s">
-        <v>427</v>
+      <c r="L74" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N74" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O74" s="4" t="s">
+      <c r="N74" s="4" t="s">
         <v>99</v>
       </c>
+      <c r="O74" s="8" t="s">
+        <v>422</v>
+      </c>
       <c r="P74" s="8" t="s">
-        <v>428</v>
+        <v>33</v>
       </c>
       <c r="Q74" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="R74" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="S74" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T74" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U74" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="R74" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="S74" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="T74" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U74" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="V74" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="W74" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="X74" s="8">
+      <c r="W74" s="8">
         <v>2026</v>
       </c>
-      <c r="Y74" s="8"/>
-      <c r="Z74" s="4"/>
+      <c r="X74" s="8"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="8" t="s">
+        <v>475</v>
+      </c>
       <c r="AA74" s="8" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AB74" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC74" s="8" t="s">
-        <v>431</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="AC74" s="4"/>
       <c r="AD74" s="4"/>
       <c r="AE74" s="4"/>
       <c r="AF74" s="4"/>
@@ -8910,9 +8668,8 @@
       <c r="AI74" s="4"/>
       <c r="AJ74" s="4"/>
       <c r="AK74" s="4"/>
-      <c r="AL74" s="4"/>
     </row>
-    <row r="75" spans="1:38" ht="88.5">
+    <row r="75" spans="1:37" ht="88.5">
       <c r="A75" s="7">
         <v>46203</v>
       </c>
@@ -8936,60 +8693,58 @@
         <v>30</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
-      <c r="L75" s="4" t="s">
-        <v>432</v>
+      <c r="L75" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N75" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O75" s="4" t="s">
+      <c r="N75" s="4" t="s">
         <v>99</v>
       </c>
+      <c r="O75" s="8" t="s">
+        <v>427</v>
+      </c>
       <c r="P75" s="8" t="s">
-        <v>433</v>
+        <v>33</v>
       </c>
       <c r="Q75" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="R75" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="S75" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T75" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="U75" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="R75" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="S75" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="T75" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U75" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="V75" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="W75" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="X75" s="8">
+      <c r="W75" s="8">
         <v>2026</v>
       </c>
-      <c r="Y75" s="8"/>
-      <c r="Z75" s="4"/>
+      <c r="X75" s="8"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="8" t="s">
+        <v>475</v>
+      </c>
       <c r="AA75" s="8" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AB75" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="AC75" s="8" t="s">
-        <v>434</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="AC75" s="4"/>
       <c r="AD75" s="4"/>
       <c r="AE75" s="4"/>
       <c r="AF75" s="4"/>
@@ -8998,9 +8753,8 @@
       <c r="AI75" s="4"/>
       <c r="AJ75" s="4"/>
       <c r="AK75" s="4"/>
-      <c r="AL75" s="4"/>
     </row>
-    <row r="76" spans="1:38" ht="29.5">
+    <row r="76" spans="1:37" ht="29.5">
       <c r="A76" s="7">
         <v>46203</v>
       </c>
@@ -9024,60 +8778,58 @@
         <v>30</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
-      <c r="L76" s="4" t="s">
-        <v>435</v>
+      <c r="L76" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N76" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O76" s="4" t="s">
-        <v>378</v>
+      <c r="N76" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="O76" s="8" t="s">
+        <v>374</v>
       </c>
       <c r="P76" s="8" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="Q76" s="8" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="R76" s="8" t="s">
-        <v>380</v>
+        <v>43</v>
       </c>
       <c r="S76" s="8" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="T76" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U76" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V76" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="W76" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="X76" s="8">
+      <c r="W76" s="8">
         <v>2026</v>
       </c>
-      <c r="Y76" s="8"/>
-      <c r="Z76" s="4"/>
+      <c r="X76" s="8"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="8">
+        <v>6.0845586999999997</v>
+      </c>
       <c r="AA76" s="8">
-        <v>6.0845586999999997</v>
-      </c>
-      <c r="AB76" s="8">
         <v>10.638270800000001</v>
       </c>
-      <c r="AC76" s="8" t="s">
-        <v>436</v>
-      </c>
+      <c r="AB76" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC76" s="4"/>
       <c r="AD76" s="4"/>
       <c r="AE76" s="4"/>
       <c r="AF76" s="4"/>
@@ -9086,9 +8838,8 @@
       <c r="AI76" s="4"/>
       <c r="AJ76" s="4"/>
       <c r="AK76" s="4"/>
-      <c r="AL76" s="4"/>
     </row>
-    <row r="77" spans="1:38" ht="73.75">
+    <row r="77" spans="1:37" ht="73.75">
       <c r="A77" s="7">
         <v>46203</v>
       </c>
@@ -9112,60 +8863,58 @@
         <v>30</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
-      <c r="L77" s="4" t="s">
+      <c r="L77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="O77" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="P77" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q77" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="R77" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S77" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T77" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="U77" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="M77" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O77" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="P77" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q77" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="R77" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="S77" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T77" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U77" s="8" t="s">
-        <v>358</v>
-      </c>
       <c r="V77" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="W77" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="X77" s="8">
+      <c r="W77" s="8">
         <v>2026</v>
       </c>
-      <c r="Y77" s="8"/>
-      <c r="Z77" s="4"/>
+      <c r="X77" s="8"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="8">
+        <v>5.9544699999999997</v>
+      </c>
       <c r="AA77" s="8">
-        <v>5.9544699999999997</v>
-      </c>
-      <c r="AB77" s="8">
         <v>10.163320000000001</v>
       </c>
-      <c r="AC77" s="8" t="s">
-        <v>441</v>
-      </c>
+      <c r="AB77" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="AC77" s="4"/>
       <c r="AD77" s="4"/>
       <c r="AE77" s="4"/>
       <c r="AF77" s="4"/>
@@ -9174,9 +8923,8 @@
       <c r="AI77" s="4"/>
       <c r="AJ77" s="4"/>
       <c r="AK77" s="4"/>
-      <c r="AL77" s="4"/>
     </row>
-    <row r="78" spans="1:38" ht="44.25">
+    <row r="78" spans="1:37" ht="44.25">
       <c r="A78" s="7">
         <v>46203</v>
       </c>
@@ -9200,60 +8948,58 @@
         <v>30</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
-      <c r="L78" s="4" t="s">
+      <c r="L78" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="O78" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="P78" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q78" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="R78" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S78" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T78" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="U78" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="M78" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O78" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="P78" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q78" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="R78" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="S78" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T78" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U78" s="8" t="s">
-        <v>358</v>
-      </c>
       <c r="V78" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="W78" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="X78" s="8">
+      <c r="W78" s="8">
         <v>2026</v>
       </c>
-      <c r="Y78" s="8"/>
-      <c r="Z78" s="4"/>
+      <c r="X78" s="8"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="8">
+        <v>5.9544699999999997</v>
+      </c>
       <c r="AA78" s="8">
-        <v>5.9544699999999997</v>
-      </c>
-      <c r="AB78" s="8">
         <v>10.163320000000001</v>
       </c>
-      <c r="AC78" s="8" t="s">
-        <v>443</v>
-      </c>
+      <c r="AB78" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="AC78" s="4"/>
       <c r="AD78" s="4"/>
       <c r="AE78" s="4"/>
       <c r="AF78" s="4"/>
@@ -9262,9 +9008,8 @@
       <c r="AI78" s="4"/>
       <c r="AJ78" s="4"/>
       <c r="AK78" s="4"/>
-      <c r="AL78" s="4"/>
     </row>
-    <row r="79" spans="1:38" ht="44.25">
+    <row r="79" spans="1:37" ht="44.25">
       <c r="A79" s="7">
         <v>46203</v>
       </c>
@@ -9288,60 +9033,58 @@
         <v>30</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
-      <c r="L79" s="4" t="s">
+      <c r="L79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N79" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="O79" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="P79" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q79" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="R79" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S79" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T79" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="U79" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="M79" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O79" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="P79" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="Q79" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="R79" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="S79" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T79" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U79" s="8" t="s">
-        <v>358</v>
-      </c>
       <c r="V79" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="W79" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="X79" s="8">
+      <c r="W79" s="8">
         <v>2026</v>
       </c>
-      <c r="Y79" s="8"/>
-      <c r="Z79" s="4"/>
+      <c r="X79" s="8"/>
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="8">
+        <v>5.9544699999999997</v>
+      </c>
       <c r="AA79" s="8">
-        <v>5.9544699999999997</v>
-      </c>
-      <c r="AB79" s="8">
         <v>10.163320000000001</v>
       </c>
-      <c r="AC79" s="8" t="s">
-        <v>445</v>
-      </c>
+      <c r="AB79" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="AC79" s="4"/>
       <c r="AD79" s="4"/>
       <c r="AE79" s="4"/>
       <c r="AF79" s="4"/>
@@ -9350,9 +9093,8 @@
       <c r="AI79" s="4"/>
       <c r="AJ79" s="4"/>
       <c r="AK79" s="4"/>
-      <c r="AL79" s="4"/>
     </row>
-    <row r="80" spans="1:38" ht="44.25">
+    <row r="80" spans="1:37" ht="44.25">
       <c r="A80" s="7">
         <v>46203</v>
       </c>
@@ -9376,60 +9118,58 @@
         <v>30</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
-      <c r="L80" s="4" t="s">
+      <c r="L80" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N80" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="O80" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="P80" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q80" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="R80" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S80" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T80" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="U80" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="M80" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O80" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="P80" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q80" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="R80" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="S80" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T80" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U80" s="8" t="s">
-        <v>358</v>
-      </c>
       <c r="V80" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="W80" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="X80" s="8">
+      <c r="W80" s="8">
         <v>2026</v>
       </c>
-      <c r="Y80" s="8"/>
-      <c r="Z80" s="4"/>
+      <c r="X80" s="8"/>
+      <c r="Y80" s="4"/>
+      <c r="Z80" s="8">
+        <v>5.9544699999999997</v>
+      </c>
       <c r="AA80" s="8">
-        <v>5.9544699999999997</v>
-      </c>
-      <c r="AB80" s="8">
         <v>10.163320000000001</v>
       </c>
-      <c r="AC80" s="8" t="s">
-        <v>449</v>
-      </c>
+      <c r="AB80" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="AC80" s="4"/>
       <c r="AD80" s="4"/>
       <c r="AE80" s="4"/>
       <c r="AF80" s="4"/>
@@ -9438,9 +9178,8 @@
       <c r="AI80" s="4"/>
       <c r="AJ80" s="4"/>
       <c r="AK80" s="4"/>
-      <c r="AL80" s="4"/>
     </row>
-    <row r="81" spans="1:38" ht="44.25">
+    <row r="81" spans="1:37" ht="44.25">
       <c r="A81" s="7">
         <v>46203</v>
       </c>
@@ -9464,60 +9203,58 @@
         <v>30</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
-      <c r="L81" s="4" t="s">
+      <c r="L81" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N81" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="O81" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="P81" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q81" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="R81" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S81" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T81" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="U81" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O81" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="P81" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="Q81" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="R81" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="S81" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T81" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="U81" s="8" t="s">
-        <v>358</v>
-      </c>
       <c r="V81" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="W81" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="X81" s="8">
+      <c r="W81" s="8">
         <v>2026</v>
       </c>
-      <c r="Y81" s="8"/>
-      <c r="Z81" s="4"/>
+      <c r="X81" s="8"/>
+      <c r="Y81" s="4"/>
+      <c r="Z81" s="8">
+        <v>6.0845586999999997</v>
+      </c>
       <c r="AA81" s="8">
-        <v>6.0845586999999997</v>
-      </c>
-      <c r="AB81" s="8">
         <v>10.638270800000001</v>
       </c>
-      <c r="AC81" s="8" t="s">
-        <v>451</v>
-      </c>
+      <c r="AB81" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="AC81" s="4"/>
       <c r="AD81" s="4"/>
       <c r="AE81" s="4"/>
       <c r="AF81" s="4"/>
@@ -9526,7 +9263,6 @@
       <c r="AI81" s="4"/>
       <c r="AJ81" s="4"/>
       <c r="AK81" s="4"/>
-      <c r="AL81" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
